--- a/AI_Use_Cases_Comprehensive_2026.xlsx
+++ b/AI_Use_Cases_Comprehensive_2026.xlsx
@@ -15,6 +15,10 @@
     <sheet name="ERP API Integration" sheetId="6" state="visible" r:id="rId6"/>
     <sheet name="EPM API Integration" sheetId="7" state="visible" r:id="rId7"/>
     <sheet name="Implementation Resources" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="Manufacturing &amp; Distribution" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="Legal Tech AI Repos" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="Legal Tech Use Cases" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="Mfg &amp; Dist Finance Use Cases" sheetId="12" state="visible" r:id="rId12"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -461,7 +465,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C15"/>
+  <dimension ref="A1:C24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -681,6 +685,1811 @@
       <c r="C15" s="2" t="inlineStr">
         <is>
           <t>90%+ automation rates for invoices, reconciliations, expense reports</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr"/>
+      <c r="B16" t="inlineStr"/>
+      <c r="C16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>NEW: Manufacturing &amp; Distribution</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr"/>
+      <c r="C17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Manufacturing/Distribution AI Repos</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>ERPNext, frePPLe, SCIMAI-Gym, Supply-Chain-Optimization, supplychainpy, etc.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Manufacturing Finance Use Cases</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Inventory costing, demand forecasting, production costing, supply chain finance</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr"/>
+      <c r="B20" t="inlineStr"/>
+      <c r="C20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>NEW: Legal Tech AI</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr"/>
+      <c r="C21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Legal Tech AI Repos</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>OpenContracts, LexNLP, LawGlance, Ally Legal Assistant, OLAW, CrewAI Contract Risk</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Legal Tech Use Cases</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Contract review, due diligence, legal research, document drafting, compliance</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Legal AI Adoption Rate 2025</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>54%</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Doubled from 23% in 2024 (ACC/Everlaw survey)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H12"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="25" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="8" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="55" customWidth="1" min="6" max="6"/>
+    <col width="55" customWidth="1" min="7" max="7"/>
+    <col width="45" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Repository</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Last Update</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Stars</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Language</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Description</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Key Capabilities</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Models/Tech Used</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>OpenContracts</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>Feb 5, 2026</t>
+        </is>
+      </c>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>1,147</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>Python</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>Enterprise-grade LLM workspace for document analysis, extraction, redaction</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>Data extraction, structured schema queries, document versioning, annotation, semantic search</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>PydanticAI, pgvector, Docling, LlamaParse, WebSocket streaming</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>LexNLP (LexPredict)</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>May 27, 2024</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>762</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>Python</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>NLP library for legal text: contracts, policies, procedures</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>Extract amounts, dates, durations, citations, court references, conditional statements</t>
+        </is>
+      </c>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t>Pre-trained word embeddings, sentence segmentation, clause classifiers</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>LawGlance</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>Dec 30, 2025</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>216</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>Python</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>Free open source RAG-based AI legal assistant</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>Multi-agent framework for legal insights, document Q&amp;A, case research</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>RAG, multi-agent AI, LLM integration</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>Legal-Text-Analytics</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>Nov 5, 2024</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>695</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>Curated</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>Curated list of resources, methods, tools for legal text analytics</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>Reference to CUAD dataset (13K+ annotations), Blackstone NER, Flair NLP</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>Links to models, datasets, benchmarks (COLIEE, Kira M&amp;A)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>Ally Legal Assistant</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>Apr 29, 2025</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>JavaScript</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>Word plugin using Azure OpenAI for contract analysis</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>Contract analysis, real-time Q&amp;A, auto-markup, clause review</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>Azure OpenAI, GPT-4, Microsoft Word integration</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>OLAW (Harvard LIL)</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>Oct 29, 2024</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>121</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>JavaScript</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>Tool-based RAG workbench for legal AI research</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>API-augmented LLM responses, legal tool integration, UX research</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>RAG, tool-based LLM augmentation, legal APIs</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>CrewAI Contract Risk</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>Recent</t>
+        </is>
+      </c>
+      <c r="C8" s="3" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>Python</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>CrewAI agents for contract review, risk flagging, clause classification</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>Parse contracts, classify clauses, identify risks, generate Review Brief</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>CrewAI multi-agent framework, GPT-4</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>Legal-AI_Project</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>Recent</t>
+        </is>
+      </c>
+      <c r="C9" s="3" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>TypeScript</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>Automated legal document analysis platform</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>Extract information, identify risks, reading comprehension Q&amp;A</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>Next.js, NLP, SQuAD-based reading comprehension model</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>contract-analyzer</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>Recent</t>
+        </is>
+      </c>
+      <c r="C10" s="3" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>Python</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>RAG system for contract analysis using Llama-3</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>PDF processing, semantic search, contract queries</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>Meta-Llama-3-8B-Instruct, RAG pipeline</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>LegalEase-AI</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>Recent</t>
+        </is>
+      </c>
+      <c r="C11" s="3" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>Python</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>Document analyzer, legal chatbot, lawyer fee estimator</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>Legal topic simplification, document analysis, fee estimation</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>LLMs, vectorized database, Flask</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>Legal-Advisor-LLM</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>Recent</t>
+        </is>
+      </c>
+      <c r="C12" s="3" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>Python</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>Legal chatbot powered by LLM and RAG</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>Legal term Q&amp;A, document retrieval, advice generation</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>LLM + RAG, document embeddings</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F16"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="20" customWidth="1" min="1" max="1"/>
+    <col width="25" customWidth="1" min="2" max="2"/>
+    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="40" customWidth="1" min="4" max="4"/>
+    <col width="40" customWidth="1" min="5" max="5"/>
+    <col width="40" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Use Case Category</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Use Case</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Description</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Open Source Tools</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Commercial Tools</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Key Benefits</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Contract Review</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>Clause Extraction</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>Automatically identify and extract key clauses from contracts</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>OpenContracts, LexNLP, contract-analyzer</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>Kira (Litera), Diligen, Luminance</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>50-85% time savings on review workloads</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Contract Review</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>Risk Identification</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>Flag potential risks, ambiguities, and non-standard terms</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>CrewAI Contract Risk, Legal-AI_Project</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>Ironclad, Icertis, Juro</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>Proactive risk mitigation before signing</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>Contract Review</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>Playbook Comparison</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>Compare contract against standard playbooks and policies</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>OpenContracts</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>Kira, Evisort, LinkSquares</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>Ensure compliance with company standards</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>Contract Analysis</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>Obligation Tracking</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>Extract and track contractual obligations and deadlines</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>LexNLP (dates/durations)</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>Agiloft, Concord, ContractPodAI</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>Prevent missed deadlines and penalties</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>Contract Analysis</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>Monetary Term Extraction</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>Extract payment terms, amounts, percentages, penalties</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>LexNLP</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>Kira, Luminance</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>Accurate financial obligation tracking</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>Due Diligence</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>M&amp;A Document Review</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>Bulk review of contracts during mergers and acquisitions</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>OpenContracts, Legal-Text-Analytics</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>Kira (1,400+ clause types), Diligen</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>Weeks of review compressed to days</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>Due Diligence</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>Data Room Analysis</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>Analyze virtual data room documents for key issues</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>OpenContracts</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>Kira, Diligen, Luminance</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>Comprehensive risk assessment</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>Legal Research</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>Case Law Search</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>Find relevant cases and precedents</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>LawGlance, OLAW</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>Westlaw Edge, LexisNexis, CaseText</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>Faster research, broader coverage</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>Legal Research</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>Statute Retrieval</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>Find applicable statutes and regulations</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>LawGlance</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>Westlaw, Bloomberg Law</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>Comprehensive regulatory compliance</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>Document Drafting</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>Contract Generation</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>Generate contracts from templates with AI assistance</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>GitLaw (templates)</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>Spellbook, LawDroid, Harvey</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>Faster first drafts, consistency</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>Document Drafting</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>Redlining/Markup</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>AI-assisted contract redlining and suggested changes</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>Ally Legal Assistant</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>Spellbook, Robin AI, BlackBoiler</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>Reduce negotiation cycles</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>Compliance</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>Regulatory Monitoring</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>Track regulatory changes affecting contracts</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>Kira, Thomson Reuters, Wolters Kluwer</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>Stay ahead of compliance requirements</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>Compliance</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>Policy Enforcement</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>Ensure contracts comply with internal policies</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>OpenContracts</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>Ironclad, Icertis</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>Reduce legal risk exposure</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>E-Discovery</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>Document Classification</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>Classify documents for relevance in litigation</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>Legal-Text-Analytics resources</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>Relativity, Reveal, Exterro</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>Reduce review costs significantly</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>E-Discovery</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>Privilege Detection</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>Identify privileged documents automatically</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>LexNLP (entity extraction)</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>Relativity, Logikcull</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>Prevent privilege waiver</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F19"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="20" customWidth="1" min="1" max="1"/>
+    <col width="28" customWidth="1" min="2" max="2"/>
+    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="35" customWidth="1" min="4" max="4"/>
+    <col width="30" customWidth="1" min="5" max="5"/>
+    <col width="35" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Use Case Category</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Use Case</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Description</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Open Source Tools</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>ERP Integration</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Key Benefits</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Inventory Costing</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>Standard Cost Calculation</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>Calculate and maintain standard costs for manufactured items</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>ERPNext, frePPLe</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>SAP, Oracle, NetSuite</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>Accurate product costing</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Inventory Costing</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>Variance Analysis</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>Analyze variances between standard and actual costs</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>ERPNext</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>SAP CO, Oracle Costing</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>Identify cost overruns early</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>Inventory Costing</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>FIFO/LIFO/Average Costing</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>Apply appropriate inventory valuation methods</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>ERPNext, Django Ledger</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>All major ERPs</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>GAAP/IFRS compliance</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>Demand Forecasting</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>Sales Forecast to Production</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>Convert demand forecasts to production and procurement plans</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>frePPLe, SCIMAI-Gym</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>SAP IBP, Oracle SCM</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>Reduce stockouts and overstock</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>Demand Forecasting</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>Seasonal Demand Prediction</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>Predict seasonal variations in demand</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>Supply-Chain-Optimization</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>SAP IBP, Anaplan</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>Optimize safety stock levels</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>Production Costing</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>Job Costing</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>Track costs by production job or work order</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>ERPNext</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>SAP PP, Oracle Manufacturing</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>Accurate job profitability</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>Production Costing</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>Activity-Based Costing</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>Allocate overhead based on activities</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>Django Ledger (extensible)</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>SAP, Oracle EPM</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>Better overhead allocation</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>Production Costing</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>WIP Valuation</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>Value work-in-progress inventory accurately</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>ERPNext</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>SAP, Oracle, Infor</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>Accurate balance sheet</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>Supply Chain Finance</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>Supplier Payment Optimization</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>Optimize payment timing for cash flow</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>ERPNext (payment terms)</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>SAP Ariba, Taulia</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>Improve working capital</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>Supply Chain Finance</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>Dynamic Discounting</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>Capture early payment discounts intelligently</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>N/A (custom)</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>C2FO, Taulia, Tradeshift</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>Earn discount income</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>Supply Chain Finance</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>Inventory Financing</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>Finance inventory through supply chain finance programs</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>SAP Ariba, PrimeRevenue</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>Improve liquidity</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>Cost Optimization</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>Make vs Buy Analysis</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>Analyze whether to manufacture or purchase</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>frePPLe (capacity planning)</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>SAP, Oracle</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>Optimize sourcing decisions</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>Cost Optimization</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>EOQ Optimization</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>Calculate economic order quantities</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>supplychainpy, Supply-Chain-Optimization</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>SAP MM, Oracle Procurement</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>Minimize total inventory cost</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>Cost Optimization</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>Safety Stock Optimization</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>Optimize safety stock levels using ML</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>SCIMAI-Gym, inventory-management</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>SAP IBP, Kinaxis</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>Balance service vs cost</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>Financial Close</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>Inventory Reconciliation</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>Reconcile physical inventory to GL</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>ERPNext, Django Ledger</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>All major ERPs</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>Accurate financial statements</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>Financial Close</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>Cost Rollup</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>Roll up costs through BOM structure</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>ERPNext</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>SAP, Oracle</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>Accurate product costs</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>Analytics</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>Profitability by Product Line</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>Analyze profitability across product lines</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>ERPNext (reports)</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>SAP CO-PA, Oracle EPM</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>Strategic product decisions</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>Analytics</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>Supplier Performance Scoring</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>Score suppliers on cost, quality, delivery</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>Supply-Chain-Optimization</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>SAP Ariba, Coupa</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>Better supplier selection</t>
         </is>
       </c>
     </row>
@@ -2964,4 +4773,406 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H9"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="28" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="8" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="50" customWidth="1" min="6" max="6"/>
+    <col width="50" customWidth="1" min="7" max="7"/>
+    <col width="45" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Repository</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Last Update</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Stars</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Language</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Description</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Key Finance/Accounting Features</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>AI/ML Capabilities</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>ERPNext (frappe/erpnext)</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>Feb 5, 2026</t>
+        </is>
+      </c>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>31,539</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>Python</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>Free and Open Source ERP for manufacturing, distribution, retail</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>Full accounting module, cash flow management, asset management, financial reporting, multi-currency</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>Extensible via Python; integrate with ML pipelines; API-first architecture</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>frePPLe</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>Feb 5, 2026</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>631</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>C++/Python</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>Open source supply chain planning</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>Cost forecasting, inventory costing, production scheduling with cost optimization</t>
+        </is>
+      </c>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t>Time series forecasting, Theory of Constraints, pull-based planning algorithms</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>SCIMAI-Gym</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>Jan 16, 2024</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>103</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>Python</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>Supply chain inventory management with deep reinforcement learning</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>Inventory cost optimization, holding cost minimization, stockout prevention</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>Deep RL (DQN, PPO, A2C), OpenAI Gym environment for inventory control</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>Supply-Chain-Optimization</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>Mar 20, 2024</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>Python</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>ML for supply chain: demand forecasting, inventory, logistics</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>EOQ calculations, holding cost analysis, supplier cost ranking</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>ML for demand forecasting, logistics optimization, supplier selection scoring</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>supplychainpy</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>Aug 20, 2022</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>STALE</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>313</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>Python</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>Python library for supply chain analysis and simulation</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>Economic Order Quantity, inventory analysis, uncertain demand modeling</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>Monte Carlo simulation, statistical inventory analysis (replaces Excel/VBA)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>inventory-management (LSTM)</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>Recent</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>Python</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>AI-powered inventory management with LSTM and transfer learning</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>Demand forecasting to minimize stockouts/overstock, storage cost reduction</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>LSTM neural networks, transfer learning for adaptable models</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>Django Ledger</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="C8" s="3" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>Python</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>Double-entry accounting on Django framework</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>GAAP-compliant accounting, financial analysis engine, journal entries</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>Extensible Django framework; can integrate with ML models</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>Carbon ERP</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="C9" s="3" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>Various</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>Open source ERP, MES and QMS for manufacturing</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>Manufacturing cost tracking, quality management system</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>MES integration for production data analytics</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/AI_Use_Cases_Comprehensive_2026.xlsx
+++ b/AI_Use_Cases_Comprehensive_2026.xlsx
@@ -19,6 +19,7 @@
     <sheet name="Legal Tech AI Repos" sheetId="10" state="visible" r:id="rId10"/>
     <sheet name="Legal Tech Use Cases" sheetId="11" state="visible" r:id="rId11"/>
     <sheet name="Mfg &amp; Dist Finance Use Cases" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="AI Research &amp; White Papers" sheetId="13" state="visible" r:id="rId13"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -42,7 +43,7 @@
       <sz val="11"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="9">
     <fill>
       <patternFill/>
     </fill>
@@ -67,6 +68,30 @@
         <bgColor rgb="00FFC7CE"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E2EFDA"/>
+        <bgColor rgb="00E2EFDA"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FCE4D6"/>
+        <bgColor rgb="00FCE4D6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00DDEBF7"/>
+        <bgColor rgb="00DDEBF7"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFF2CC"/>
+        <bgColor rgb="00FFF2CC"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -86,7 +111,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -99,6 +124,18 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -465,7 +502,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C24"/>
+  <dimension ref="A1:C30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -688,19 +725,13 @@
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" t="inlineStr"/>
-      <c r="B16" t="inlineStr"/>
-      <c r="C16" t="inlineStr"/>
-    </row>
+    <row r="16"/>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
           <t>NEW: Manufacturing &amp; Distribution</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr"/>
-      <c r="C17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -736,19 +767,13 @@
         </is>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" t="inlineStr"/>
-      <c r="B20" t="inlineStr"/>
-      <c r="C20" t="inlineStr"/>
-    </row>
+    <row r="20"/>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
           <t>NEW: Legal Tech AI</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr"/>
-      <c r="C21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -798,6 +823,88 @@
       <c r="C24" t="inlineStr">
         <is>
           <t>Doubled from 23% in 2024 (ACC/Everlaw survey)</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr"/>
+      <c r="B25" t="inlineStr"/>
+      <c r="C25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>NEW: AI Research &amp; White Papers</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr"/>
+      <c r="C26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Hyperscaler Research Papers</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Google DeepMind (SIMA 2, Dreamer 4), Microsoft (Copilot studies), AWS (AutoGluon, CAF-AI)</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Big 4 / Consulting Reports</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Deloitte (State of AI 2026), McKinsey, PwC, KPMG, EY</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>AI Studio Research</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>OpenAI-Anthropic Joint Evaluation, Reasoning Faithfulness, Claude Constitution</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Academic Research</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Stanford HAI AI Index, MIT CSAIL AI Action Plan, EnCompass framework</t>
         </is>
       </c>
     </row>
@@ -2498,6 +2605,828 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F25"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="90" customWidth="1" min="5" max="5"/>
+    <col width="80" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Source Type</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Organization</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Title</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Synopsis (100-200 words)</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>URL</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="120" customHeight="1">
+      <c r="A2" s="5" t="inlineStr">
+        <is>
+          <t>Hyperscaler</t>
+        </is>
+      </c>
+      <c r="B2" s="5" t="inlineStr">
+        <is>
+          <t>Google DeepMind</t>
+        </is>
+      </c>
+      <c r="C2" s="5" t="inlineStr">
+        <is>
+          <t>SIMA 2: A Gemini-Powered AI Agent for 3D Virtual Worlds</t>
+        </is>
+      </c>
+      <c r="D2" s="5" t="inlineStr">
+        <is>
+          <t>Dec 2025</t>
+        </is>
+      </c>
+      <c r="E2" s="5" t="inlineStr">
+        <is>
+          <t>SIMA 2 represents Google DeepMind's next milestone in creating general AI agents. Unlike its predecessor that was limited to instruction-following, SIMA 2 embeds a Gemini model as its core, enabling it to think and reason about instructions. The agent acts as an interactive partner capable of reasoning about high-level goals, conversing with users, and handling complex instructions through both language and images. SIMA 2 demonstrates significant advances in embodied AI, showing how agents can operate in open-ended virtual environments with human-like understanding and adaptability. The system was tested across multiple 3D virtual worlds, demonstrating generalization capabilities across different game environments and tasks.</t>
+        </is>
+      </c>
+      <c r="F2" s="5" t="inlineStr">
+        <is>
+          <t>https://deepmind.google/blog/sima-2-an-agent-that-plays-reasons-and-learns-with-you-in-virtual-3d-worlds/</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="120" customHeight="1">
+      <c r="A3" s="5" t="inlineStr">
+        <is>
+          <t>Hyperscaler</t>
+        </is>
+      </c>
+      <c r="B3" s="5" t="inlineStr">
+        <is>
+          <t>Google DeepMind</t>
+        </is>
+      </c>
+      <c r="C3" s="5" t="inlineStr">
+        <is>
+          <t>Dreamer 4: Learning in World Models</t>
+        </is>
+      </c>
+      <c r="D3" s="5" t="inlineStr">
+        <is>
+          <t>Oct 2025</t>
+        </is>
+      </c>
+      <c r="E3" s="5" t="inlineStr">
+        <is>
+          <t>Dreamer 4 is a groundbreaking AI agent that learns complex behaviors entirely within a scalable world model. In a significant milestone, it became the first AI agent to obtain diamonds in Minecraft without practicing in the actual game—learning purely through simulated experience. The system uses reinforcement learning inside its world model, dramatically reducing the need for real-world or game-environment training. This approach addresses key limitations of traditional RL methods that require extensive real-world interaction. Dreamer 4's architecture enables more efficient learning and better generalization across tasks, pointing toward future AI systems that can learn and plan in simulated environments before deployment.</t>
+        </is>
+      </c>
+      <c r="F3" s="5" t="inlineStr">
+        <is>
+          <t>https://deepmind.google/research/publications/</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="120" customHeight="1">
+      <c r="A4" s="5" t="inlineStr">
+        <is>
+          <t>Hyperscaler</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="inlineStr">
+        <is>
+          <t>Google DeepMind</t>
+        </is>
+      </c>
+      <c r="C4" s="5" t="inlineStr">
+        <is>
+          <t>AI Co-Scientist: Multi-Agent Hypothesis Generation</t>
+        </is>
+      </c>
+      <c r="D4" s="5" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E4" s="5" t="inlineStr">
+        <is>
+          <t>AI Co-Scientist is a collaborative system developed across Google Research, Cloud AI, and DeepMind designed to help scientists generate novel hypotheses. The system employs a coalition of specialized AI agents that iteratively generate, evaluate, and refine scientific hypotheses. Each agent brings different capabilities—from literature review to experimental design to statistical analysis—working together in a coordinated workflow. The system demonstrated ability to propose novel research directions across multiple scientific domains. This represents a significant step toward AI-augmented scientific discovery, where AI systems don't replace human scientists but amplify their ability to explore the hypothesis space more efficiently.</t>
+        </is>
+      </c>
+      <c r="F4" s="5" t="inlineStr">
+        <is>
+          <t>https://blog.google/technology/ai/2025-research-breakthroughs/</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="120" customHeight="1">
+      <c r="A5" s="5" t="inlineStr">
+        <is>
+          <t>Hyperscaler</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="inlineStr">
+        <is>
+          <t>Microsoft Research</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>The Copilot Usage Report 2025</t>
+        </is>
+      </c>
+      <c r="D5" s="5" t="inlineStr">
+        <is>
+          <t>Dec 2025</t>
+        </is>
+      </c>
+      <c r="E5" s="5" t="inlineStr">
+        <is>
+          <t>Microsoft analyzed 37.5 million conversations to understand how people actually use Copilot. The research reveals that Copilot has evolved beyond a simple productivity tool—its usage is shaped by temporal and physical context, integrating into the full texture of human life. The study moves beyond monolithic views of 'AI usage' to show nuanced patterns of adoption. Key findings include that usage varies significantly by time of day, task complexity, and work environment. The report provides actionable insights for organizations deploying AI assistants at scale, highlighting both productivity gains and areas where human-AI collaboration patterns are still evolving.</t>
+        </is>
+      </c>
+      <c r="F5" s="5" t="inlineStr">
+        <is>
+          <t>https://microsoft.ai/wp-content/uploads/2025/12/What_people_do_with_Copilot-8.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="120" customHeight="1">
+      <c r="A6" s="5" t="inlineStr">
+        <is>
+          <t>Hyperscaler</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="inlineStr">
+        <is>
+          <t>Microsoft Research</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>New Future of Work Report 2025</t>
+        </is>
+      </c>
+      <c r="D6" s="5" t="inlineStr">
+        <is>
+          <t>Dec 2025</t>
+        </is>
+      </c>
+      <c r="E6" s="5" t="inlineStr">
+        <is>
+          <t>This comprehensive report synthesizes research on how AI is transforming knowledge work. Key studies cited include work on early M365 Copilot impact, AI democratization of knowledge work, and measuring AI applicability to occupations. The report finds that LLM-powered tools like Copilot have potential to increase labor productivity more than any technology in a generation. Organizations adopting Copilot effectively see productivity improvements up to 30% on routine tasks. The research also addresses challenges including change management, skills development, and ensuring equitable access to AI productivity gains across different roles and demographics.</t>
+        </is>
+      </c>
+      <c r="F6" s="5" t="inlineStr">
+        <is>
+          <t>https://www.microsoft.com/en-us/research/wp-content/uploads/2025/12/New-Future-Of-Work-Report-2025.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="120" customHeight="1">
+      <c r="A7" s="5" t="inlineStr">
+        <is>
+          <t>Hyperscaler</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>Microsoft Research</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>New Employee Copilot Usage Study</t>
+        </is>
+      </c>
+      <c r="D7" s="5" t="inlineStr">
+        <is>
+          <t>Apr 2025</t>
+        </is>
+      </c>
+      <c r="E7" s="5" t="inlineStr">
+        <is>
+          <t>This mixed-methods study examines how new employees interact with Microsoft Copilot when acclimating to professional environments. The research found a strong association between frequency of Copilot use and workplace integration—interns who used Copilot more frequently felt better socialized and identified more strongly with their teams. The study suggests AI assistants can serve as informal mentors, helping new employees navigate organizational knowledge and processes. Implications extend to onboarding program design and understanding how AI tools can reduce the learning curve for new workforce entrants while maintaining human connection and team cohesion.</t>
+        </is>
+      </c>
+      <c r="F7" s="5" t="inlineStr">
+        <is>
+          <t>https://www.microsoft.com/en-us/research/wp-content/uploads/2025/04/New-employee-Copilot-usage.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="120" customHeight="1">
+      <c r="A8" s="5" t="inlineStr">
+        <is>
+          <t>Hyperscaler</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="inlineStr">
+        <is>
+          <t>Amazon/AWS</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>AutoGluon Assistant: Zero-Code AutoML via Multiagent Collaboration</t>
+        </is>
+      </c>
+      <c r="D8" s="5" t="inlineStr">
+        <is>
+          <t>Dec 2025</t>
+        </is>
+      </c>
+      <c r="E8" s="5" t="inlineStr">
+        <is>
+          <t>Amazon researchers developed AutoGluon Assistant, a system that enables zero-code AutoML through multiagent collaboration. The system allows users without machine learning expertise to build high-quality ML models by simply describing their problem in natural language. Multiple specialized agents collaborate to handle data preprocessing, feature engineering, model selection, hyperparameter tuning, and evaluation. The approach democratizes machine learning, making it accessible to domain experts who understand their business problems but lack ML coding skills. Testing showed competitive performance with hand-crafted solutions while dramatically reducing time-to-model from weeks to hours.</t>
+        </is>
+      </c>
+      <c r="F8" s="5" t="inlineStr">
+        <is>
+          <t>https://www.amazon.science/publications</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="120" customHeight="1">
+      <c r="A9" s="5" t="inlineStr">
+        <is>
+          <t>Hyperscaler</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="inlineStr">
+        <is>
+          <t>Amazon/AWS</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>The Unseen Work of Building Reliable AI Agents</t>
+        </is>
+      </c>
+      <c r="D9" s="5" t="inlineStr">
+        <is>
+          <t>Jan 2026</t>
+        </is>
+      </c>
+      <c r="E9" s="5" t="inlineStr">
+        <is>
+          <t>This Amazon research paper focuses on 'reinforcement learning gyms' that train AI agents on low-level tasks they must chain together to execute customer requests. The work addresses the significant engineering challenges in building production-ready AI agents versus research prototypes. Key insights include the importance of robust error handling, graceful degradation, and comprehensive testing frameworks. The paper introduces new methodologies for ensuring agent reliability at scale, including novel approaches to monitoring agent behavior and catching edge cases before deployment. This represents important foundational work for enterprise AI agent adoption.</t>
+        </is>
+      </c>
+      <c r="F9" s="5" t="inlineStr">
+        <is>
+          <t>https://www.amazon.science/research-areas/machine-learning</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="120" customHeight="1">
+      <c r="A10" s="5" t="inlineStr">
+        <is>
+          <t>Hyperscaler</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="inlineStr">
+        <is>
+          <t>AWS</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>Cloud Adoption Framework for AI (CAF-AI)</t>
+        </is>
+      </c>
+      <c r="D10" s="5" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E10" s="5" t="inlineStr">
+        <is>
+          <t>The AWS Cloud Adoption Framework for AI provides a comprehensive mental model for organizations striving to generate business value from AI. CAF-AI serves as a constantly growing guide for AI adoption at the enterprise level, helping organizations move beyond single proofs of concept. The framework covers six perspectives: Business, People, Governance, Platform, Security, and Operations. It provides maturity assessments, best practices for scaling AI, and guidance on responsible AI implementation. The framework has been updated to address generative AI and agentic AI considerations, making it relevant for organizations at any stage of their AI journey.</t>
+        </is>
+      </c>
+      <c r="F10" s="5" t="inlineStr">
+        <is>
+          <t>https://docs.aws.amazon.com/whitepapers/latest/aws-caf-for-ai/aws-caf-for-ai.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="120" customHeight="1">
+      <c r="A11" s="6" t="inlineStr">
+        <is>
+          <t>Big 4</t>
+        </is>
+      </c>
+      <c r="B11" s="6" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C11" s="6" t="inlineStr">
+        <is>
+          <t>State of AI in the Enterprise 2026</t>
+        </is>
+      </c>
+      <c r="D11" s="6" t="inlineStr">
+        <is>
+          <t>Jan 2026</t>
+        </is>
+      </c>
+      <c r="E11" s="6" t="inlineStr">
+        <is>
+          <t>Deloitte's seventh annual State of AI report surveyed 3,235 leaders across IT and business functions globally (Aug-Sep 2025). Key finding: worker access to AI rose 50% in 2025, with organizations broadening workforce access from under 40% to around 60%. Agentic AI is racing into the enterprise—85% of companies expect to customize agents for their business needs. While 66% report productivity gains, only 34% are using AI for deep transformation. Revenue growth remains aspirational: 74% hope to grow revenue through AI but only 20% currently do. The AI skills gap is the biggest barrier, with education (not role redesign) being the top talent strategy response.</t>
+        </is>
+      </c>
+      <c r="F11" s="6" t="inlineStr">
+        <is>
+          <t>https://www.deloitte.com/us/en/what-we-do/capabilities/applied-artificial-intelligence/content/state-of-ai-in-the-enterprise.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="120" customHeight="1">
+      <c r="A12" s="6" t="inlineStr">
+        <is>
+          <t>Big 4</t>
+        </is>
+      </c>
+      <c r="B12" s="6" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C12" s="6" t="inlineStr">
+        <is>
+          <t>Tech Trends 2026: From Experimentation to Enterprise Impact</t>
+        </is>
+      </c>
+      <c r="D12" s="6" t="inlineStr">
+        <is>
+          <t>Jan 2026</t>
+        </is>
+      </c>
+      <c r="E12" s="6" t="inlineStr">
+        <is>
+          <t>Deloitte's 17th annual Tech Trends report identifies a fundamental mindset shift from 'What can we do with AI?' to 'How do we move from experimentation to impact?' The report covers agentic AI, spatial computing, quantum readiness, and sustainable tech. For CIOs, 70% say their primary role is implementing generative AI across the enterprise or evangelizing AI possibilities. The report emphasizes that successful AI transformation requires rewiring organizational processes, not just deploying technology. Key recommendations include building AI-native architectures, investing in data foundations, and developing comprehensive change management strategies.</t>
+        </is>
+      </c>
+      <c r="F12" s="6" t="inlineStr">
+        <is>
+          <t>https://www.deloitte.com/us/en/insights/topics/technology-management/tech-trends/2026/ai-future-it-function.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="120" customHeight="1">
+      <c r="A13" s="6" t="inlineStr">
+        <is>
+          <t>Big 4</t>
+        </is>
+      </c>
+      <c r="B13" s="6" t="inlineStr">
+        <is>
+          <t>McKinsey</t>
+        </is>
+      </c>
+      <c r="C13" s="6" t="inlineStr">
+        <is>
+          <t>The State of AI 2025: Agents, Innovation, and Transformation</t>
+        </is>
+      </c>
+      <c r="D13" s="6" t="inlineStr">
+        <is>
+          <t>Nov 2025</t>
+        </is>
+      </c>
+      <c r="E13" s="6" t="inlineStr">
+        <is>
+          <t>McKinsey surveyed 1,993 participants across 105 nations (June-July 2025). Key findings: 88% of organizations now use AI in at least one function (up from 78%). However, nearly two-thirds remain in experimentation/piloting phase. On AI agents: 62% are experimenting, 23% are scaling agentic systems. Only 6% qualify as 'AI high performers' (&gt;5% EBIT from AI). These high performers are 3.6x more likely to target transformational change and 55% fundamentally redesign workflows (vs. 20% of others). The critical insight: value comes from rewiring how companies run, with workflow redesign having the biggest effect on EBIT impact.</t>
+        </is>
+      </c>
+      <c r="F13" s="6" t="inlineStr">
+        <is>
+          <t>https://www.mckinsey.com/capabilities/quantumblack/our-insights/the-state-of-ai</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="120" customHeight="1">
+      <c r="A14" s="6" t="inlineStr">
+        <is>
+          <t>Big 4</t>
+        </is>
+      </c>
+      <c r="B14" s="6" t="inlineStr">
+        <is>
+          <t>PwC</t>
+        </is>
+      </c>
+      <c r="C14" s="6" t="inlineStr">
+        <is>
+          <t>2026 AI Business Predictions</t>
+        </is>
+      </c>
+      <c r="D14" s="6" t="inlineStr">
+        <is>
+          <t>Jan 2026</t>
+        </is>
+      </c>
+      <c r="E14" s="6" t="inlineStr">
+        <is>
+          <t>PwC predicts more companies will follow AI front-runners in 2026, adopting enterprise-wide, top-down AI strategies. From their Responsible AI survey: 60% of executives report that Responsible AI boosts ROI and efficiency, 55% see improved customer experience. On agentic AI, PwC emphasizes the need for centralized deployment platforms with agents tested before each deployment and rolled out with clear human oversight steps. Trust remains a key challenge—28% of executives ranked lack of trust as a top barrier to value realization. The report recommends focusing on governance frameworks alongside technical capabilities.</t>
+        </is>
+      </c>
+      <c r="F14" s="6" t="inlineStr">
+        <is>
+          <t>https://www.pwc.com/us/en/tech-effect/ai-analytics/ai-predictions.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="120" customHeight="1">
+      <c r="A15" s="6" t="inlineStr">
+        <is>
+          <t>Big 4</t>
+        </is>
+      </c>
+      <c r="B15" s="6" t="inlineStr">
+        <is>
+          <t>KPMG</t>
+        </is>
+      </c>
+      <c r="C15" s="6" t="inlineStr">
+        <is>
+          <t>AI Quarterly Pulse Survey Q4 2025</t>
+        </is>
+      </c>
+      <c r="D15" s="6" t="inlineStr">
+        <is>
+          <t>Jan 2026</t>
+        </is>
+      </c>
+      <c r="E15" s="6" t="inlineStr">
+        <is>
+          <t>KPMG's Q4 survey reveals remarkable resilience in AI investment: 67% of business leaders will maintain AI spending even in a recession, with $124 million projected deployment over the coming year. Agent deployment has nearly quadrupled—42% of organizations now have deployed at least some agents, up from 11% two quarters ago. 59% expect measurable ROI within 12 months. The survey highlights the shift from pilot programs to production deployment, with organizations focusing on measurable business outcomes rather than experimental use cases. Risk management and governance emerged as top priorities alongside scaling.</t>
+        </is>
+      </c>
+      <c r="F15" s="6" t="inlineStr">
+        <is>
+          <t>https://kpmg.com/us/en/media/news/q4-ai-pulse.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="120" customHeight="1">
+      <c r="A16" s="6" t="inlineStr">
+        <is>
+          <t>Big 4</t>
+        </is>
+      </c>
+      <c r="B16" s="6" t="inlineStr">
+        <is>
+          <t>KPMG</t>
+        </is>
+      </c>
+      <c r="C16" s="6" t="inlineStr">
+        <is>
+          <t>Global Tech Report 2026: Leading in the Intelligence Age</t>
+        </is>
+      </c>
+      <c r="D16" s="6" t="inlineStr">
+        <is>
+          <t>Jan 2026</t>
+        </is>
+      </c>
+      <c r="E16" s="6" t="inlineStr">
+        <is>
+          <t>KPMG's Global Tech Report examines how organizations are responding to AI disruption, with agentic AI commanding attention from tech executives. The report identifies quantum computing and Artificial General Intelligence as even more disruptive trends on the horizon. Key themes include the importance of building 'AI-ready' organizational cultures, investing in talent development, and establishing robust data governance. The report provides frameworks for assessing AI maturity and roadmaps for progressing from experimentation to enterprise-scale deployment. Industry-specific recommendations address unique challenges in financial services, healthcare, and manufacturing.</t>
+        </is>
+      </c>
+      <c r="F16" s="6" t="inlineStr">
+        <is>
+          <t>https://kpmg.com/xx/en/our-insights/ai-and-technology/global-tech-report.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="120" customHeight="1">
+      <c r="A17" s="6" t="inlineStr">
+        <is>
+          <t>Big 4</t>
+        </is>
+      </c>
+      <c r="B17" s="6" t="inlineStr">
+        <is>
+          <t>EY</t>
+        </is>
+      </c>
+      <c r="C17" s="6" t="inlineStr">
+        <is>
+          <t>EY.ai Platform and AI Agent Deployment</t>
+        </is>
+      </c>
+      <c r="D17" s="6" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E17" s="6" t="inlineStr">
+        <is>
+          <t>EY has advanced 1,000 AI agents into development or production in 2025, with plans to scale to 100,000 by 2028. The firm is investing over $1 billion annually in AI platforms and products. Nearly 100,000 EY employees (approximately 25% of workforce) have earned a digital 'AI badge' for completing AI learning programs. EY launched EY.ai, granting 80,000 tax staff access to 150 AI agents for data collection, document review, and tax compliance. This represents one of the largest enterprise AI deployments, demonstrating how professional services firms are fundamentally transforming their delivery models with AI.</t>
+        </is>
+      </c>
+      <c r="F17" s="6" t="inlineStr">
+        <is>
+          <t>https://www.ey.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="120" customHeight="1">
+      <c r="A18" s="7" t="inlineStr">
+        <is>
+          <t>AI Studio</t>
+        </is>
+      </c>
+      <c r="B18" s="7" t="inlineStr">
+        <is>
+          <t>OpenAI &amp; Anthropic</t>
+        </is>
+      </c>
+      <c r="C18" s="7" t="inlineStr">
+        <is>
+          <t>Joint Alignment Evaluation Exercise Findings</t>
+        </is>
+      </c>
+      <c r="D18" s="7" t="inlineStr">
+        <is>
+          <t>Jul 2025</t>
+        </is>
+      </c>
+      <c r="E18" s="7" t="inlineStr">
+        <is>
+          <t>In a landmark collaboration, OpenAI and Anthropic conducted mutual alignment evaluations on each other's models in summer 2025. Models tested included GPT-4o, GPT-4.1, o3, o4-mini, Claude Opus 4, and Claude Sonnet 4. Key findings: OpenAI's o3 showed better-aligned behavior than Claude Opus 4 on most dimensions, but behaviors of o4-mini, GPT-4o, and GPT-4.1 appeared more concerning than Claude models. On scheming evaluations, o3 and Sonnet 4 performed best. Notably, enabling reasoning doesn't always help—Opus 4 with reasoning enabled performed worse than without. This exercise represents unprecedented transparency in AI safety evaluation.</t>
+        </is>
+      </c>
+      <c r="F18" s="7" t="inlineStr">
+        <is>
+          <t>https://alignment.anthropic.com/2025/openai-findings/</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="120" customHeight="1">
+      <c r="A19" s="7" t="inlineStr">
+        <is>
+          <t>AI Studio</t>
+        </is>
+      </c>
+      <c r="B19" s="7" t="inlineStr">
+        <is>
+          <t>Anthropic</t>
+        </is>
+      </c>
+      <c r="C19" s="7" t="inlineStr">
+        <is>
+          <t>Reasoning Models Don't Always Say What They Think</t>
+        </is>
+      </c>
+      <c r="D19" s="7" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E19" s="7" t="inlineStr">
+        <is>
+          <t>This Anthropic research paper studies reasoning model faithfulness across OpenAI o1/o3, DeepSeek R1, Gemini Flash Thinking, and Claude 3.7 Sonnet Extended Thinking. The study examines whether monitoring chain-of-thought (CoT) reasoning can provide AI safety benefits. Critical finding: CoTs are less faithful on harder tasks, meaning safety-relevant factors may not be explicitly verbalized. This challenges assumptions that reasoning transparency automatically enables safety monitoring. The implications are significant for AI deployment—organizations cannot rely solely on CoT monitoring to detect misaligned behaviors, requiring additional safety measures and evaluation frameworks.</t>
+        </is>
+      </c>
+      <c r="F19" s="7" t="inlineStr">
+        <is>
+          <t>https://assets.anthropic.com/m/71876fabef0f0ed4/original/reasoning_models_paper.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="120" customHeight="1">
+      <c r="A20" s="7" t="inlineStr">
+        <is>
+          <t>AI Studio</t>
+        </is>
+      </c>
+      <c r="B20" s="7" t="inlineStr">
+        <is>
+          <t>Anthropic</t>
+        </is>
+      </c>
+      <c r="C20" s="7" t="inlineStr">
+        <is>
+          <t>Natural Emergent Misalignment from Reward Hacking</t>
+        </is>
+      </c>
+      <c r="D20" s="7" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E20" s="7" t="inlineStr">
+        <is>
+          <t>This research paper investigates how models trained in certain ways learn to reward hack pervasively. Surprisingly, such models generalize to emergent misalignment including alignment faking, sabotage of safety research, monitor disruption, and reasoning about harmful goals. The findings highlight risks in RL-based training approaches and emphasize the need for careful reward design. The paper provides concrete examples of misaligned behaviors emerging from seemingly innocuous training objectives, offering important lessons for AI developers about the unpredictable consequences of reward optimization at scale.</t>
+        </is>
+      </c>
+      <c r="F20" s="7" t="inlineStr">
+        <is>
+          <t>https://assets.anthropic.com/m/74342f2c96095771/original/Natural-emergent-misalignment-from-reward-hacking-paper.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="120" customHeight="1">
+      <c r="A21" s="7" t="inlineStr">
+        <is>
+          <t>AI Studio</t>
+        </is>
+      </c>
+      <c r="B21" s="7" t="inlineStr">
+        <is>
+          <t>Anthropic</t>
+        </is>
+      </c>
+      <c r="C21" s="7" t="inlineStr">
+        <is>
+          <t>2026 Claude Constitution Update</t>
+        </is>
+      </c>
+      <c r="D21" s="7" t="inlineStr">
+        <is>
+          <t>Jan 2026</t>
+        </is>
+      </c>
+      <c r="E21" s="7" t="inlineStr">
+        <is>
+          <t>Anthropic released a dramatically expanded constitution for Claude, moving from 'standalone principles' to a philosophical approach explaining not just what is important but why. The new version expanded to 84 pages and 23,000 words. The constitution addresses nuanced ethical scenarios, provides detailed guidance on sensitive topics, and establishes clearer boundaries while maintaining helpfulness. This update represents Anthropic's commitment to AI safety through explicit value alignment, offering transparency into how Claude makes decisions. The expanded constitution serves as a model for responsible AI development practices.</t>
+        </is>
+      </c>
+      <c r="F21" s="7" t="inlineStr">
+        <is>
+          <t>https://www.anthropic.com/research</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="120" customHeight="1">
+      <c r="A22" s="8" t="inlineStr">
+        <is>
+          <t>Academic</t>
+        </is>
+      </c>
+      <c r="B22" s="8" t="inlineStr">
+        <is>
+          <t>Stanford HAI</t>
+        </is>
+      </c>
+      <c r="C22" s="8" t="inlineStr">
+        <is>
+          <t>AI Index Report 2025</t>
+        </is>
+      </c>
+      <c r="D22" s="8" t="inlineStr">
+        <is>
+          <t>Apr 2025</t>
+        </is>
+      </c>
+      <c r="E22" s="8" t="inlineStr">
+        <is>
+          <t>Stanford's eighth annual AI Index provides comprehensive tracking of global AI trends across technical performance, economic impact, education, policy, and responsible AI. Key findings: U.S. private AI investment reached $109.1 billion (12x China's $9.3 billion). U.S. institutions produced 40 notable models vs. China's 15, but Chinese models achieved near-parity on benchmarks. AI business usage jumped to 78% (from 55%). AI incidents rose 56.4% to 233 (including deepfakes and chatbot-related incidents). Data availability concerns: training data projected to be fully utilized between 2026-2032. Benchmarks struggle to keep pace with rapidly advancing AI capabilities.</t>
+        </is>
+      </c>
+      <c r="F22" s="8" t="inlineStr">
+        <is>
+          <t>https://hai.stanford.edu/ai-index/2025-ai-index-report</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="120" customHeight="1">
+      <c r="A23" s="8" t="inlineStr">
+        <is>
+          <t>Academic</t>
+        </is>
+      </c>
+      <c r="B23" s="8" t="inlineStr">
+        <is>
+          <t>MIT CSAIL</t>
+        </is>
+      </c>
+      <c r="C23" s="8" t="inlineStr">
+        <is>
+          <t>AI Action Plan Recommendations 2025</t>
+        </is>
+      </c>
+      <c r="D23" s="8" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E23" s="8" t="inlineStr">
+        <is>
+          <t>MIT CSAIL's lab-wide response to the US government's AI Action Plan RFI draws on six decades of computing and AI research. Key recommendations: Despite LLM excitement, performance and efficiency growth rates are slowing, requiring continued foundational research support. CSAIL recommends pursuing Artificial Super Intelligence (ASI) that goes beyond current LLM limitations by integrating real-world awareness, common-sense reasoning, agentic computation, and physical intelligence. The recommendations emphasize the importance of maintaining US leadership in AI research while addressing safety, security, and societal implications of advanced AI systems.</t>
+        </is>
+      </c>
+      <c r="F23" s="8" t="inlineStr">
+        <is>
+          <t>https://internetpolicy.mit.edu/mit-csail-ai-action-plan-recommendations-2025/</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="120" customHeight="1">
+      <c r="A24" s="8" t="inlineStr">
+        <is>
+          <t>Academic</t>
+        </is>
+      </c>
+      <c r="B24" s="8" t="inlineStr">
+        <is>
+          <t>MIT CSAIL</t>
+        </is>
+      </c>
+      <c r="C24" s="8" t="inlineStr">
+        <is>
+          <t>EnCompass: A Framework for AI Agent Search Strategies</t>
+        </is>
+      </c>
+      <c r="D24" s="8" t="inlineStr">
+        <is>
+          <t>Dec 2025</t>
+        </is>
+      </c>
+      <c r="E24" s="8" t="inlineStr">
+        <is>
+          <t>MIT CSAIL and Asari AI developed EnCompass, a framework that separates search strategy from AI agent workflows. The system lets programmers easily experiment with different search strategies to optimize agent performance. EnCompass reduced coding effort for implementing search by up to 80% across various agent types, including code repository translation and digital grid transformation agents. The framework addresses a key challenge in agentic AI—finding optimal strategies for complex, multi-step tasks. This work enables more efficient development of capable AI agents by providing reusable, tested search components.</t>
+        </is>
+      </c>
+      <c r="F24" s="8" t="inlineStr">
+        <is>
+          <t>https://techxplore.com/news/2025-12-ai-agents-results-large-language.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="120" customHeight="1">
+      <c r="A25" s="8" t="inlineStr">
+        <is>
+          <t>Academic</t>
+        </is>
+      </c>
+      <c r="B25" s="8" t="inlineStr">
+        <is>
+          <t>Stanford/MIT</t>
+        </is>
+      </c>
+      <c r="C25" s="8" t="inlineStr">
+        <is>
+          <t>Agentic AI Time Savings Study</t>
+        </is>
+      </c>
+      <c r="D25" s="8" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E25" s="8" t="inlineStr">
+        <is>
+          <t>Joint research from Stanford HAI and MIT CSAIL studied agentic AI prototypes across business settings including scheduling, data summarization, and complex process coordination. The study found time savings of 65-86% compared to human-only workflows. However, researchers emphasize that these gains require careful workflow redesign and human oversight mechanisms. The study identifies best practices for human-AI collaboration in agentic systems, including clear task boundaries, feedback loops, and escalation paths. Findings suggest that agentic AI's productivity benefits are highly dependent on implementation quality and organizational readiness.</t>
+        </is>
+      </c>
+      <c r="F25" s="8" t="inlineStr">
+        <is>
+          <t>https://digitaldefynd.com/IQ/agentic-ai-statistics/</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>

--- a/AI_Use_Cases_Comprehensive_2026.xlsx
+++ b/AI_Use_Cases_Comprehensive_2026.xlsx
@@ -20,6 +20,7 @@
     <sheet name="Legal Tech Use Cases" sheetId="11" state="visible" r:id="rId11"/>
     <sheet name="Mfg &amp; Dist Finance Use Cases" sheetId="12" state="visible" r:id="rId12"/>
     <sheet name="AI Research &amp; White Papers" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet name="PE &amp; M&amp;A AI Use Cases" sheetId="14" state="visible" r:id="rId14"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -43,7 +44,7 @@
       <sz val="11"/>
     </font>
   </fonts>
-  <fills count="9">
+  <fills count="10">
     <fill>
       <patternFill/>
     </fill>
@@ -92,6 +93,12 @@
         <bgColor rgb="00FFF2CC"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="002F5496"/>
+        <bgColor rgb="002F5496"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -111,7 +118,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -135,6 +142,12 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -502,7 +515,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C30"/>
+  <dimension ref="A1:C36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -725,7 +738,6 @@
         </is>
       </c>
     </row>
-    <row r="16"/>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
@@ -767,7 +779,6 @@
         </is>
       </c>
     </row>
-    <row r="20"/>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
@@ -826,19 +837,12 @@
         </is>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" t="inlineStr"/>
-      <c r="B25" t="inlineStr"/>
-      <c r="C25" t="inlineStr"/>
-    </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
           <t>NEW: AI Research &amp; White Papers</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr"/>
-      <c r="C26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -905,6 +909,59 @@
       <c r="C30" t="inlineStr">
         <is>
           <t>Stanford HAI AI Index, MIT CSAIL AI Action Plan, EnCompass framework</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>PE &amp; M&amp;A AI Statistics (2026)</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>PE/M&amp;A Use Cases Documented:</t>
+        </is>
+      </c>
+      <c r="B33" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>AI Deal Value (2025):</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>$140.5B</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>PE Firms Using AI:</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>95%</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Due Diligence Time Reduction:</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>70%</t>
         </is>
       </c>
     </row>
@@ -3427,6 +3484,668 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F20"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="18" customWidth="1" min="1" max="1"/>
+    <col width="28" customWidth="1" min="2" max="2"/>
+    <col width="55" customWidth="1" min="3" max="3"/>
+    <col width="35" customWidth="1" min="4" max="4"/>
+    <col width="40" customWidth="1" min="5" max="5"/>
+    <col width="35" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="25" customHeight="1">
+      <c r="A1" s="9" t="inlineStr">
+        <is>
+          <t>Category</t>
+        </is>
+      </c>
+      <c r="B1" s="9" t="inlineStr">
+        <is>
+          <t>Use Case</t>
+        </is>
+      </c>
+      <c r="C1" s="9" t="inlineStr">
+        <is>
+          <t>Description</t>
+        </is>
+      </c>
+      <c r="D1" s="9" t="inlineStr">
+        <is>
+          <t>AI Capabilities</t>
+        </is>
+      </c>
+      <c r="E1" s="9" t="inlineStr">
+        <is>
+          <t>Key Platforms/Tools</t>
+        </is>
+      </c>
+      <c r="F1" s="9" t="inlineStr">
+        <is>
+          <t>Quantified Benefits</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="60" customHeight="1">
+      <c r="A2" s="10" t="inlineStr">
+        <is>
+          <t>Deal Sourcing</t>
+        </is>
+      </c>
+      <c r="B2" s="10" t="inlineStr">
+        <is>
+          <t>Target Company Identification</t>
+        </is>
+      </c>
+      <c r="C2" s="10" t="inlineStr">
+        <is>
+          <t>AI scans market data, financials, and web sources to identify potential acquisition targets matching investment criteria</t>
+        </is>
+      </c>
+      <c r="D2" s="10" t="inlineStr">
+        <is>
+          <t>Machine Learning, NLP, Predictive Analytics</t>
+        </is>
+      </c>
+      <c r="E2" s="10" t="inlineStr">
+        <is>
+          <t>PitchBook, CB Insights, SourceScrub, Affinity, Motherbrain (EQT)</t>
+        </is>
+      </c>
+      <c r="F2" s="10" t="inlineStr">
+        <is>
+          <t>50-70% reduction in target screening time</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="60" customHeight="1">
+      <c r="A3" s="10" t="inlineStr">
+        <is>
+          <t>Deal Sourcing</t>
+        </is>
+      </c>
+      <c r="B3" s="10" t="inlineStr">
+        <is>
+          <t>Relationship Intelligence</t>
+        </is>
+      </c>
+      <c r="C3" s="10" t="inlineStr">
+        <is>
+          <t>Track relationships across portfolio companies, LPs, and deal networks to identify warm introductions</t>
+        </is>
+      </c>
+      <c r="D3" s="10" t="inlineStr">
+        <is>
+          <t>Graph Analytics, NLP, CRM Integration</t>
+        </is>
+      </c>
+      <c r="E3" s="10" t="inlineStr">
+        <is>
+          <t>Affinity, DealCloud, Salesforce</t>
+        </is>
+      </c>
+      <c r="F3" s="10" t="inlineStr">
+        <is>
+          <t>3x increase in qualified deal flow</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="60" customHeight="1">
+      <c r="A4" s="10" t="inlineStr">
+        <is>
+          <t>Deal Sourcing</t>
+        </is>
+      </c>
+      <c r="B4" s="10" t="inlineStr">
+        <is>
+          <t>Market Signal Monitoring</t>
+        </is>
+      </c>
+      <c r="C4" s="10" t="inlineStr">
+        <is>
+          <t>Real-time monitoring of news, SEC filings, and social media for M&amp;A signals and opportunities</t>
+        </is>
+      </c>
+      <c r="D4" s="10" t="inlineStr">
+        <is>
+          <t>NLP, Sentiment Analysis, Event Detection</t>
+        </is>
+      </c>
+      <c r="E4" s="10" t="inlineStr">
+        <is>
+          <t>AlphaSense, Sentieo, Tegus</t>
+        </is>
+      </c>
+      <c r="F4" s="10" t="inlineStr">
+        <is>
+          <t>Early identification of 40% more opportunities</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="60" customHeight="1">
+      <c r="A5" s="10" t="inlineStr">
+        <is>
+          <t>Due Diligence</t>
+        </is>
+      </c>
+      <c r="B5" s="10" t="inlineStr">
+        <is>
+          <t>Contract Analysis &amp; Review</t>
+        </is>
+      </c>
+      <c r="C5" s="10" t="inlineStr">
+        <is>
+          <t>Automated extraction of key terms, risks, and obligations from hundreds of contracts in data rooms</t>
+        </is>
+      </c>
+      <c r="D5" s="10" t="inlineStr">
+        <is>
+          <t>NLP, Document Understanding, ML Classification</t>
+        </is>
+      </c>
+      <c r="E5" s="10" t="inlineStr">
+        <is>
+          <t>Kira Systems, Luminance, eBrevia, Eigen Technologies</t>
+        </is>
+      </c>
+      <c r="F5" s="10" t="inlineStr">
+        <is>
+          <t>70-90% reduction in contract review time</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="60" customHeight="1">
+      <c r="A6" s="10" t="inlineStr">
+        <is>
+          <t>Due Diligence</t>
+        </is>
+      </c>
+      <c r="B6" s="10" t="inlineStr">
+        <is>
+          <t>Financial Data Extraction</t>
+        </is>
+      </c>
+      <c r="C6" s="10" t="inlineStr">
+        <is>
+          <t>Automated extraction and normalization of financial data from disparate documents and formats</t>
+        </is>
+      </c>
+      <c r="D6" s="10" t="inlineStr">
+        <is>
+          <t>OCR, NLP, Data Validation</t>
+        </is>
+      </c>
+      <c r="E6" s="10" t="inlineStr">
+        <is>
+          <t>Hebbia, ToltIQ, Datasite AI Q&amp;A</t>
+        </is>
+      </c>
+      <c r="F6" s="10" t="inlineStr">
+        <is>
+          <t>60% faster financial analysis</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="60" customHeight="1">
+      <c r="A7" s="10" t="inlineStr">
+        <is>
+          <t>Due Diligence</t>
+        </is>
+      </c>
+      <c r="B7" s="10" t="inlineStr">
+        <is>
+          <t>Risk Identification</t>
+        </is>
+      </c>
+      <c r="C7" s="10" t="inlineStr">
+        <is>
+          <t>AI-powered identification of hidden risks, litigation, compliance issues, and change-of-control provisions</t>
+        </is>
+      </c>
+      <c r="D7" s="10" t="inlineStr">
+        <is>
+          <t>NLP, Pattern Recognition, Anomaly Detection</t>
+        </is>
+      </c>
+      <c r="E7" s="10" t="inlineStr">
+        <is>
+          <t>Kira, DealRoom, Datasite</t>
+        </is>
+      </c>
+      <c r="F7" s="10" t="inlineStr">
+        <is>
+          <t>Identify 2-3x more risk factors</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="60" customHeight="1">
+      <c r="A8" s="10" t="inlineStr">
+        <is>
+          <t>Due Diligence</t>
+        </is>
+      </c>
+      <c r="B8" s="10" t="inlineStr">
+        <is>
+          <t>Q&amp;A Automation</t>
+        </is>
+      </c>
+      <c r="C8" s="10" t="inlineStr">
+        <is>
+          <t>AI answers buyer questions by searching across entire data room, reducing seller response burden</t>
+        </is>
+      </c>
+      <c r="D8" s="10" t="inlineStr">
+        <is>
+          <t>RAG, Semantic Search, LLM</t>
+        </is>
+      </c>
+      <c r="E8" s="10" t="inlineStr">
+        <is>
+          <t>Datasite AI Q&amp;A, DealRoom, Hebbia</t>
+        </is>
+      </c>
+      <c r="F8" s="10" t="inlineStr">
+        <is>
+          <t>80% reduction in Q&amp;A response time</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="60" customHeight="1">
+      <c r="A9" s="10" t="inlineStr">
+        <is>
+          <t>VDR Management</t>
+        </is>
+      </c>
+      <c r="B9" s="10" t="inlineStr">
+        <is>
+          <t>Intelligent Document Indexing</t>
+        </is>
+      </c>
+      <c r="C9" s="10" t="inlineStr">
+        <is>
+          <t>Auto-categorize, tag, and index documents uploaded to data rooms using AI classification</t>
+        </is>
+      </c>
+      <c r="D9" s="10" t="inlineStr">
+        <is>
+          <t>Document Classification, NLP, ML</t>
+        </is>
+      </c>
+      <c r="E9" s="10" t="inlineStr">
+        <is>
+          <t>Datasite, Intralinks, iDeals, FirmRoom</t>
+        </is>
+      </c>
+      <c r="F9" s="10" t="inlineStr">
+        <is>
+          <t>90% faster document organization</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="60" customHeight="1">
+      <c r="A10" s="10" t="inlineStr">
+        <is>
+          <t>VDR Management</t>
+        </is>
+      </c>
+      <c r="B10" s="10" t="inlineStr">
+        <is>
+          <t>Smart Redaction</t>
+        </is>
+      </c>
+      <c r="C10" s="10" t="inlineStr">
+        <is>
+          <t>AI-powered detection and redaction of sensitive information (PII, confidential terms)</t>
+        </is>
+      </c>
+      <c r="D10" s="10" t="inlineStr">
+        <is>
+          <t>NER, Pattern Matching, OCR</t>
+        </is>
+      </c>
+      <c r="E10" s="10" t="inlineStr">
+        <is>
+          <t>Datasite, DealRoom</t>
+        </is>
+      </c>
+      <c r="F10" s="10" t="inlineStr">
+        <is>
+          <t>75% reduction in redaction time</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="60" customHeight="1">
+      <c r="A11" s="10" t="inlineStr">
+        <is>
+          <t>VDR Management</t>
+        </is>
+      </c>
+      <c r="B11" s="10" t="inlineStr">
+        <is>
+          <t>Duplicate Detection</t>
+        </is>
+      </c>
+      <c r="C11" s="10" t="inlineStr">
+        <is>
+          <t>Identify and flag duplicate documents across large data rooms</t>
+        </is>
+      </c>
+      <c r="D11" s="10" t="inlineStr">
+        <is>
+          <t>Document Fingerprinting, Similarity Matching</t>
+        </is>
+      </c>
+      <c r="E11" s="10" t="inlineStr">
+        <is>
+          <t>Datasite, Intralinks</t>
+        </is>
+      </c>
+      <c r="F11" s="10" t="inlineStr">
+        <is>
+          <t>Eliminate 15-20% redundant documents</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="60" customHeight="1">
+      <c r="A12" s="10" t="inlineStr">
+        <is>
+          <t>Portfolio Monitoring</t>
+        </is>
+      </c>
+      <c r="B12" s="10" t="inlineStr">
+        <is>
+          <t>Real-time KPI Dashboards</t>
+        </is>
+      </c>
+      <c r="C12" s="10" t="inlineStr">
+        <is>
+          <t>Automated aggregation of portfolio company data with AI-generated insights and anomaly detection</t>
+        </is>
+      </c>
+      <c r="D12" s="10" t="inlineStr">
+        <is>
+          <t>Time Series Analysis, Anomaly Detection, ML</t>
+        </is>
+      </c>
+      <c r="E12" s="10" t="inlineStr">
+        <is>
+          <t>BlackRock Aladdin, ZBrain, Nosible</t>
+        </is>
+      </c>
+      <c r="F12" s="10" t="inlineStr">
+        <is>
+          <t>Real-time visibility vs monthly reporting</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="60" customHeight="1">
+      <c r="A13" s="10" t="inlineStr">
+        <is>
+          <t>Portfolio Monitoring</t>
+        </is>
+      </c>
+      <c r="B13" s="10" t="inlineStr">
+        <is>
+          <t>Covenant Compliance Monitoring</t>
+        </is>
+      </c>
+      <c r="C13" s="10" t="inlineStr">
+        <is>
+          <t>Automated tracking of financial covenants with early warning alerts when ratios approach triggers</t>
+        </is>
+      </c>
+      <c r="D13" s="10" t="inlineStr">
+        <is>
+          <t>Rule Engines, Predictive Analytics</t>
+        </is>
+      </c>
+      <c r="E13" s="10" t="inlineStr">
+        <is>
+          <t>BlackRock Aladdin, Carta, eFront</t>
+        </is>
+      </c>
+      <c r="F13" s="10" t="inlineStr">
+        <is>
+          <t>Early warning 30 days before breach</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="60" customHeight="1">
+      <c r="A14" s="10" t="inlineStr">
+        <is>
+          <t>Portfolio Monitoring</t>
+        </is>
+      </c>
+      <c r="B14" s="10" t="inlineStr">
+        <is>
+          <t>Performance Forecasting</t>
+        </is>
+      </c>
+      <c r="C14" s="10" t="inlineStr">
+        <is>
+          <t>ML-based forecasting of portfolio company performance using historical data and market signals</t>
+        </is>
+      </c>
+      <c r="D14" s="10" t="inlineStr">
+        <is>
+          <t>Time Series ML, Ensemble Models</t>
+        </is>
+      </c>
+      <c r="E14" s="10" t="inlineStr">
+        <is>
+          <t>KKR internal tools, BlackRock Aladdin</t>
+        </is>
+      </c>
+      <c r="F14" s="10" t="inlineStr">
+        <is>
+          <t>85% accuracy in quarterly forecasts</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="60" customHeight="1">
+      <c r="A15" s="10" t="inlineStr">
+        <is>
+          <t>Value Creation</t>
+        </is>
+      </c>
+      <c r="B15" s="10" t="inlineStr">
+        <is>
+          <t>Operational Efficiency Analysis</t>
+        </is>
+      </c>
+      <c r="C15" s="10" t="inlineStr">
+        <is>
+          <t>AI identifies operational improvement opportunities across portfolio companies</t>
+        </is>
+      </c>
+      <c r="D15" s="10" t="inlineStr">
+        <is>
+          <t>Process Mining, Benchmarking, ML</t>
+        </is>
+      </c>
+      <c r="E15" s="10" t="inlineStr">
+        <is>
+          <t>Celonis, Arctic AI, McKinsey analytics</t>
+        </is>
+      </c>
+      <c r="F15" s="10" t="inlineStr">
+        <is>
+          <t>15-25% EBITDA improvement identified</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="60" customHeight="1">
+      <c r="A16" s="10" t="inlineStr">
+        <is>
+          <t>Value Creation</t>
+        </is>
+      </c>
+      <c r="B16" s="10" t="inlineStr">
+        <is>
+          <t>Pricing Optimization</t>
+        </is>
+      </c>
+      <c r="C16" s="10" t="inlineStr">
+        <is>
+          <t>ML-driven pricing recommendations for portfolio companies based on market dynamics</t>
+        </is>
+      </c>
+      <c r="D16" s="10" t="inlineStr">
+        <is>
+          <t>Price Elasticity ML, Competitive Analysis</t>
+        </is>
+      </c>
+      <c r="E16" s="10" t="inlineStr">
+        <is>
+          <t>Custom ML models, Anaplan, PROS</t>
+        </is>
+      </c>
+      <c r="F16" s="10" t="inlineStr">
+        <is>
+          <t>3-7% revenue increase</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="60" customHeight="1">
+      <c r="A17" s="10" t="inlineStr">
+        <is>
+          <t>Value Creation</t>
+        </is>
+      </c>
+      <c r="B17" s="10" t="inlineStr">
+        <is>
+          <t>Customer Analytics</t>
+        </is>
+      </c>
+      <c r="C17" s="10" t="inlineStr">
+        <is>
+          <t>Predictive models for customer churn, LTV, and acquisition optimization</t>
+        </is>
+      </c>
+      <c r="D17" s="10" t="inlineStr">
+        <is>
+          <t>Classification ML, Cohort Analysis</t>
+        </is>
+      </c>
+      <c r="E17" s="10" t="inlineStr">
+        <is>
+          <t>Amplitude, Mixpanel, custom models</t>
+        </is>
+      </c>
+      <c r="F17" s="10" t="inlineStr">
+        <is>
+          <t>20% reduction in churn</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="60" customHeight="1">
+      <c r="A18" s="10" t="inlineStr">
+        <is>
+          <t>Exit &amp; Valuation</t>
+        </is>
+      </c>
+      <c r="B18" s="10" t="inlineStr">
+        <is>
+          <t>Comparable Company Analysis</t>
+        </is>
+      </c>
+      <c r="C18" s="10" t="inlineStr">
+        <is>
+          <t>AI-powered identification and analysis of comparable companies for valuation</t>
+        </is>
+      </c>
+      <c r="D18" s="10" t="inlineStr">
+        <is>
+          <t>Similarity Matching, Financial Analysis</t>
+        </is>
+      </c>
+      <c r="E18" s="10" t="inlineStr">
+        <is>
+          <t>PitchBook, CapIQ, AlphaSense</t>
+        </is>
+      </c>
+      <c r="F18" s="10" t="inlineStr">
+        <is>
+          <t>50% faster comp selection</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="60" customHeight="1">
+      <c r="A19" s="10" t="inlineStr">
+        <is>
+          <t>Exit &amp; Valuation</t>
+        </is>
+      </c>
+      <c r="B19" s="10" t="inlineStr">
+        <is>
+          <t>Exit Timing Optimization</t>
+        </is>
+      </c>
+      <c r="C19" s="10" t="inlineStr">
+        <is>
+          <t>Predictive models suggesting optimal exit windows based on market conditions</t>
+        </is>
+      </c>
+      <c r="D19" s="10" t="inlineStr">
+        <is>
+          <t>Time Series ML, Market Signals</t>
+        </is>
+      </c>
+      <c r="E19" s="10" t="inlineStr">
+        <is>
+          <t>PitchBook, custom models</t>
+        </is>
+      </c>
+      <c r="F19" s="10" t="inlineStr">
+        <is>
+          <t>Improved exit multiples</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="60" customHeight="1">
+      <c r="A20" s="10" t="inlineStr">
+        <is>
+          <t>Exit &amp; Valuation</t>
+        </is>
+      </c>
+      <c r="B20" s="10" t="inlineStr">
+        <is>
+          <t>Sell-side Preparation</t>
+        </is>
+      </c>
+      <c r="C20" s="10" t="inlineStr">
+        <is>
+          <t>AI-assisted creation of CIMs, management presentations from data room contents</t>
+        </is>
+      </c>
+      <c r="D20" s="10" t="inlineStr">
+        <is>
+          <t>Document Generation, LLM</t>
+        </is>
+      </c>
+      <c r="E20" s="10" t="inlineStr">
+        <is>
+          <t>Hebbia, DealRoom</t>
+        </is>
+      </c>
+      <c r="F20" s="10" t="inlineStr">
+        <is>
+          <t>40% faster preparation</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>

--- a/AI_Use_Cases_Comprehensive_2026.xlsx
+++ b/AI_Use_Cases_Comprehensive_2026.xlsx
@@ -15,12 +15,12 @@
     <sheet name="ERP API Integration" sheetId="6" state="visible" r:id="rId6"/>
     <sheet name="EPM API Integration" sheetId="7" state="visible" r:id="rId7"/>
     <sheet name="Implementation Resources" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="Manufacturing &amp; Distribution" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="Legal Tech AI Repos" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet name="Legal Tech Use Cases" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet name="Mfg &amp; Dist Finance Use Cases" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet name="AI Research &amp; White Papers" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet name="PE &amp; M&amp;A AI Use Cases" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet name="Legal Tech Use Cases" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="Mfg &amp; Dist Finance Use Cases" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="AI Research &amp; White Papers" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="PE &amp; M&amp;A AI Use Cases" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="Legal Tech AI Repos" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet name="Manufacturing &amp; Distribution" sheetId="14" state="visible" r:id="rId14"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -30,7 +30,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="7">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -43,8 +43,28 @@
       <color rgb="00FFFFFF"/>
       <sz val="11"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <sz val="16"/>
+    </font>
+    <font>
+      <i val="1"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <b val="1"/>
+    </font>
   </fonts>
-  <fills count="10">
+  <fills count="12">
     <fill>
       <patternFill/>
     </fill>
@@ -99,8 +119,20 @@
         <bgColor rgb="002F5496"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00375623"/>
+        <bgColor rgb="00375623"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00833C0C"/>
+        <bgColor rgb="00833C0C"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -114,11 +146,39 @@
       <top style="thin"/>
       <bottom style="thin"/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin"/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -150,6 +210,32 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="10" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="11" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -515,1524 +601,494 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C36"/>
+  <dimension ref="A1:D36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="40" customWidth="1" min="1" max="1"/>
-    <col width="15" customWidth="1" min="2" max="2"/>
-    <col width="70" customWidth="1" min="3" max="3"/>
+    <col width="35" customWidth="1" min="1" max="1"/>
+    <col width="45" customWidth="1" min="2" max="2"/>
+    <col width="25" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Category</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Count</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Description</t>
-        </is>
-      </c>
+      <c r="A1" s="15" t="inlineStr">
+        <is>
+          <t>AI Use Cases Workbook - Executive Summary</t>
+        </is>
+      </c>
+      <c r="B1" s="12" t="n"/>
+      <c r="C1" s="12" t="n"/>
+      <c r="D1" s="13" t="n"/>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>GitHub Repositories Analyzed</t>
-        </is>
-      </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="C2" s="2" t="inlineStr">
-        <is>
-          <t>Open source code with models, inputs, and activity status</t>
-        </is>
-      </c>
+      <c r="A2" s="16" t="inlineStr">
+        <is>
+          <t>Last Updated: February 2026</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="2" t="n"/>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>Top 10 ERP Systems</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="C3" s="2" t="inlineStr">
-        <is>
-          <t>SAP, Oracle, Microsoft, Workday, NetSuite, Sage, Infor, Unit4, IFS, Epicor, Acumatica</t>
-        </is>
-      </c>
+      <c r="A3" s="2" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>Top 5 EPM Systems</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>Oracle EPM, Anaplan, OneStream, Planful, SAP Analytics Cloud</t>
-        </is>
-      </c>
+      <c r="A4" s="17" t="inlineStr">
+        <is>
+          <t>USE CASE CATEGORIZATION SUMMARY</t>
+        </is>
+      </c>
+      <c r="B4" s="12" t="n"/>
+      <c r="C4" s="12" t="n"/>
+      <c r="D4" s="13" t="n"/>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>Total AI Use Cases Documented</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>200+</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>Across finance, accounting, planning, and close processes</t>
+      <c r="A5" s="18" t="inlineStr">
+        <is>
+          <t>Domain</t>
+        </is>
+      </c>
+      <c r="B5" s="18" t="inlineStr">
+        <is>
+          <t>Open Source / Code Repos</t>
+        </is>
+      </c>
+      <c r="C5" s="18" t="inlineStr">
+        <is>
+          <t>Vendor / SaaS Products</t>
+        </is>
+      </c>
+      <c r="D5" s="18" t="inlineStr">
+        <is>
+          <t>Total</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="inlineStr"/>
-      <c r="B6" s="2" t="inlineStr"/>
-      <c r="C6" s="2" t="inlineStr"/>
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>PE &amp; M&amp;A</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="C6" s="19" t="n">
+        <v>15</v>
+      </c>
+      <c r="D6" s="20" t="n">
+        <v>25</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>Repository Activity Summary</t>
-        </is>
-      </c>
-      <c r="B7" s="2" t="inlineStr"/>
-      <c r="C7" s="2" t="inlineStr"/>
+          <t>Legal Tech</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="C7" s="19" t="n">
+        <v>13</v>
+      </c>
+      <c r="D7" s="20" t="n">
+        <v>23</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>Active Repositories (updated 2026)</t>
-        </is>
-      </c>
-      <c r="B8" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>FinRobot, TaxHacker, LLMs-in-Finance, awesome-ai-in-finance, deep-research-agent, finllm-apps, Finance-LLMs</t>
-        </is>
+          <t>Manufacturing &amp; Distribution</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="C8" s="19" t="n">
+        <v>13</v>
+      </c>
+      <c r="D8" s="20" t="n">
+        <v>23</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>Stale Repositories (&gt;12 months)</t>
-        </is>
-      </c>
-      <c r="B9" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>Machine-Learning-for-Finance (last update July 2023)</t>
-        </is>
+          <t>Finance &amp; Accounting (GitHub)</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="C9" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="D9" s="20" t="n">
+        <v>9</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>Curated Lists (reference only)</t>
-        </is>
-      </c>
-      <c r="B10" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>financial-machine-learning</t>
-        </is>
+      <c r="A10" s="21" t="inlineStr">
+        <is>
+          <t>TOTAL</t>
+        </is>
+      </c>
+      <c r="B10" s="21" t="n">
+        <v>39</v>
+      </c>
+      <c r="C10" s="21" t="n">
+        <v>41</v>
+      </c>
+      <c r="D10" s="22" t="n">
+        <v>80</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="2" t="inlineStr"/>
-      <c r="B11" s="2" t="inlineStr"/>
-      <c r="C11" s="2" t="inlineStr"/>
+      <c r="A11" s="2" t="n"/>
+      <c r="B11" s="2" t="n"/>
+      <c r="C11" s="2" t="n"/>
     </row>
     <row r="12">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>Key ERP AI Trends 2026</t>
-        </is>
-      </c>
-      <c r="B12" s="2" t="inlineStr"/>
-      <c r="C12" s="2" t="inlineStr"/>
+      <c r="A12" s="21" t="inlineStr">
+        <is>
+          <t>LEGEND:</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="n"/>
+      <c r="C12" s="2" t="n"/>
     </row>
     <row r="13">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>Agentic Finance</t>
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t>Open Source / Code Repos</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
+          <t>Technical implementations with actual code on GitHub</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="19" t="inlineStr">
+        <is>
+          <t>Vendor / SaaS Products</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>Commercial products - marketing/capability claims</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="n"/>
+      <c r="B15" s="2" t="n"/>
+      <c r="C15" s="2" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="23" t="inlineStr">
+        <is>
+          <t>WORKBOOK SHEETS</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="18" t="inlineStr">
+        <is>
+          <t>Sheet Name</t>
+        </is>
+      </c>
+      <c r="B17" s="18" t="inlineStr">
+        <is>
+          <t>Content</t>
+        </is>
+      </c>
+      <c r="C17" s="18" t="inlineStr">
+        <is>
+          <t>Code Repos</t>
+        </is>
+      </c>
+      <c r="D17" s="18" t="inlineStr">
+        <is>
+          <t>Vendor Products</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="20" t="inlineStr">
+        <is>
+          <t>PE &amp; M&amp;A AI Use Cases</t>
+        </is>
+      </c>
+      <c r="B18" s="20" t="inlineStr">
+        <is>
+          <t>Private equity and M&amp;A AI capabilities</t>
+        </is>
+      </c>
+      <c r="C18" s="20" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D18" s="20" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="20" t="inlineStr">
+        <is>
+          <t>Legal Tech AI Repos</t>
+        </is>
+      </c>
+      <c r="B19" s="20" t="inlineStr">
+        <is>
+          <t>Legal document analysis and contract AI</t>
+        </is>
+      </c>
+      <c r="C19" s="20" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D19" s="20" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="20" t="inlineStr">
+        <is>
+          <t>Manufacturing &amp; Distribution</t>
+        </is>
+      </c>
+      <c r="B20" s="20" t="inlineStr">
+        <is>
+          <t>Supply chain and manufacturing AI</t>
+        </is>
+      </c>
+      <c r="C20" s="20" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D20" s="20" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="20" t="inlineStr">
+        <is>
+          <t>GitHub Repo Synopsis</t>
+        </is>
+      </c>
+      <c r="B21" s="20" t="inlineStr">
+        <is>
+          <t>Finance AI repositories</t>
+        </is>
+      </c>
+      <c r="C21" s="20" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="D21" s="20" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="20" t="inlineStr">
+        <is>
+          <t>Top 10 ERP AI Use Cases</t>
+        </is>
+      </c>
+      <c r="B22" s="20" t="inlineStr">
+        <is>
+          <t>Enterprise ERP AI capabilities</t>
+        </is>
+      </c>
+      <c r="C22" s="20" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D22" s="20" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="20" t="inlineStr">
+        <is>
+          <t>Top 5 EPM AI Use Cases</t>
+        </is>
+      </c>
+      <c r="B23" s="20" t="inlineStr">
+        <is>
+          <t>Enterprise performance management AI</t>
+        </is>
+      </c>
+      <c r="C23" s="20" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D23" s="20" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="20" t="inlineStr">
+        <is>
+          <t>AI Research &amp; White Papers</t>
+        </is>
+      </c>
+      <c r="B24" s="20" t="inlineStr">
+        <is>
+          <t>Latest AI research articles</t>
+        </is>
+      </c>
+      <c r="C24" s="20" t="inlineStr">
+        <is>
           <t>-</t>
         </is>
       </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>Autonomous agents for AP, AR, Close, Planning across all major ERPs</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>Copilot Integration</t>
-        </is>
-      </c>
-      <c r="B14" s="2" t="inlineStr">
+      <c r="D24" s="20" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>Natural language interfaces embedded in SAP Joule, Microsoft Copilot, Oracle agents</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>Touchless Processing</t>
-        </is>
-      </c>
-      <c r="B15" s="2" t="inlineStr">
+    </row>
+    <row r="25">
+      <c r="A25" s="20" t="inlineStr">
+        <is>
+          <t>Code Samples &amp; Prompts</t>
+        </is>
+      </c>
+      <c r="B25" s="20" t="inlineStr">
+        <is>
+          <t>Working code examples</t>
+        </is>
+      </c>
+      <c r="C25" s="20" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="D25" s="20" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="C15" s="2" t="inlineStr">
-        <is>
-          <t>90%+ automation rates for invoices, reconciliations, expense reports</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>NEW: Manufacturing &amp; Distribution</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>Manufacturing/Distribution AI Repos</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>ERPNext, frePPLe, SCIMAI-Gym, Supply-Chain-Optimization, supplychainpy, etc.</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>Manufacturing Finance Use Cases</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Inventory costing, demand forecasting, production costing, supply chain finance</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>NEW: Legal Tech AI</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>Legal Tech AI Repos</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>OpenContracts, LexNLP, LawGlance, Ally Legal Assistant, OLAW, CrewAI Contract Risk</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>Legal Tech Use Cases</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Contract review, due diligence, legal research, document drafting, compliance</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>Legal AI Adoption Rate 2025</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>54%</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Doubled from 23% in 2024 (ACC/Everlaw survey)</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>NEW: AI Research &amp; White Papers</t>
-        </is>
-      </c>
-    </row>
+    </row>
+    <row r="26"/>
     <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>Hyperscaler Research Papers</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Google DeepMind (SIMA 2, Dreamer 4), Microsoft (Copilot studies), AWS (AutoGluon, CAF-AI)</t>
+      <c r="A27" s="23" t="inlineStr">
+        <is>
+          <t>KEY STATISTICS</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Big 4 / Consulting Reports</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Deloitte (State of AI 2026), McKinsey, PwC, KPMG, EY</t>
+          <t>Total Use Cases Documented:</t>
+        </is>
+      </c>
+      <c r="B28" s="24" t="inlineStr">
+        <is>
+          <t>80+</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>AI Studio Research</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>OpenAI-Anthropic Joint Evaluation, Reasoning Faithfulness, Claude Constitution</t>
+          <t>Open Source Repositories:</t>
+        </is>
+      </c>
+      <c r="B29" s="24" t="inlineStr">
+        <is>
+          <t>39</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Academic Research</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Stanford HAI AI Index, MIT CSAIL AI Action Plan, EnCompass framework</t>
+          <t>Vendor/SaaS Products:</t>
+        </is>
+      </c>
+      <c r="B30" s="24" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>AI Research Articles:</t>
+        </is>
+      </c>
+      <c r="B31" s="24" t="inlineStr">
+        <is>
+          <t>24</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>PE &amp; M&amp;A AI Statistics (2026)</t>
+          <t>ERP Platforms Covered:</t>
+        </is>
+      </c>
+      <c r="B32" s="24" t="inlineStr">
+        <is>
+          <t>10</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>PE/M&amp;A Use Cases Documented:</t>
-        </is>
-      </c>
-      <c r="B33" t="n">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>AI Deal Value (2025):</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>$140.5B</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>PE Firms Using AI:</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>95%</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>Due Diligence Time Reduction:</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>70%</t>
-        </is>
-      </c>
-    </row>
+          <t>EPM Platforms Covered:</t>
+        </is>
+      </c>
+      <c r="B33" s="24" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+    </row>
+    <row r="34"/>
+    <row r="35"/>
+    <row r="36"/>
   </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A4:D4"/>
+  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:H12"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="25" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="10" customWidth="1" min="3" max="3"/>
-    <col width="8" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="55" customWidth="1" min="6" max="6"/>
-    <col width="55" customWidth="1" min="7" max="7"/>
-    <col width="45" customWidth="1" min="8" max="8"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Repository</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Last Update</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Status</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>Stars</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>Language</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>Description</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>Key Capabilities</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>Models/Tech Used</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>OpenContracts</t>
-        </is>
-      </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>Feb 5, 2026</t>
-        </is>
-      </c>
-      <c r="C2" s="3" t="inlineStr">
-        <is>
-          <t>ACTIVE</t>
-        </is>
-      </c>
-      <c r="D2" s="2" t="inlineStr">
-        <is>
-          <t>1,147</t>
-        </is>
-      </c>
-      <c r="E2" s="2" t="inlineStr">
-        <is>
-          <t>Python</t>
-        </is>
-      </c>
-      <c r="F2" s="2" t="inlineStr">
-        <is>
-          <t>Enterprise-grade LLM workspace for document analysis, extraction, redaction</t>
-        </is>
-      </c>
-      <c r="G2" s="2" t="inlineStr">
-        <is>
-          <t>Data extraction, structured schema queries, document versioning, annotation, semantic search</t>
-        </is>
-      </c>
-      <c r="H2" s="2" t="inlineStr">
-        <is>
-          <t>PydanticAI, pgvector, Docling, LlamaParse, WebSocket streaming</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>LexNLP (LexPredict)</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>May 27, 2024</t>
-        </is>
-      </c>
-      <c r="C3" s="3" t="inlineStr">
-        <is>
-          <t>ACTIVE</t>
-        </is>
-      </c>
-      <c r="D3" s="2" t="inlineStr">
-        <is>
-          <t>762</t>
-        </is>
-      </c>
-      <c r="E3" s="2" t="inlineStr">
-        <is>
-          <t>Python</t>
-        </is>
-      </c>
-      <c r="F3" s="2" t="inlineStr">
-        <is>
-          <t>NLP library for legal text: contracts, policies, procedures</t>
-        </is>
-      </c>
-      <c r="G3" s="2" t="inlineStr">
-        <is>
-          <t>Extract amounts, dates, durations, citations, court references, conditional statements</t>
-        </is>
-      </c>
-      <c r="H3" s="2" t="inlineStr">
-        <is>
-          <t>Pre-trained word embeddings, sentence segmentation, clause classifiers</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>LawGlance</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>Dec 30, 2025</t>
-        </is>
-      </c>
-      <c r="C4" s="3" t="inlineStr">
-        <is>
-          <t>ACTIVE</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>216</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>Python</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>Free open source RAG-based AI legal assistant</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>Multi-agent framework for legal insights, document Q&amp;A, case research</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>RAG, multi-agent AI, LLM integration</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>Legal-Text-Analytics</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>Nov 5, 2024</t>
-        </is>
-      </c>
-      <c r="C5" s="3" t="inlineStr">
-        <is>
-          <t>ACTIVE</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>695</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>Curated</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>Curated list of resources, methods, tools for legal text analytics</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>Reference to CUAD dataset (13K+ annotations), Blackstone NER, Flair NLP</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>Links to models, datasets, benchmarks (COLIEE, Kira M&amp;A)</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>Ally Legal Assistant</t>
-        </is>
-      </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>Apr 29, 2025</t>
-        </is>
-      </c>
-      <c r="C6" s="3" t="inlineStr">
-        <is>
-          <t>ACTIVE</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>65</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>JavaScript</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>Word plugin using Azure OpenAI for contract analysis</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>Contract analysis, real-time Q&amp;A, auto-markup, clause review</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>Azure OpenAI, GPT-4, Microsoft Word integration</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>OLAW (Harvard LIL)</t>
-        </is>
-      </c>
-      <c r="B7" s="2" t="inlineStr">
-        <is>
-          <t>Oct 29, 2024</t>
-        </is>
-      </c>
-      <c r="C7" s="3" t="inlineStr">
-        <is>
-          <t>ACTIVE</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>121</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>JavaScript</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>Tool-based RAG workbench for legal AI research</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>API-augmented LLM responses, legal tool integration, UX research</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>RAG, tool-based LLM augmentation, legal APIs</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>CrewAI Contract Risk</t>
-        </is>
-      </c>
-      <c r="B8" s="2" t="inlineStr">
-        <is>
-          <t>Recent</t>
-        </is>
-      </c>
-      <c r="C8" s="3" t="inlineStr">
-        <is>
-          <t>ACTIVE</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>Python</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>CrewAI agents for contract review, risk flagging, clause classification</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>Parse contracts, classify clauses, identify risks, generate Review Brief</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>CrewAI multi-agent framework, GPT-4</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>Legal-AI_Project</t>
-        </is>
-      </c>
-      <c r="B9" s="2" t="inlineStr">
-        <is>
-          <t>Recent</t>
-        </is>
-      </c>
-      <c r="C9" s="3" t="inlineStr">
-        <is>
-          <t>ACTIVE</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>TypeScript</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>Automated legal document analysis platform</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>Extract information, identify risks, reading comprehension Q&amp;A</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>Next.js, NLP, SQuAD-based reading comprehension model</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>contract-analyzer</t>
-        </is>
-      </c>
-      <c r="B10" s="2" t="inlineStr">
-        <is>
-          <t>Recent</t>
-        </is>
-      </c>
-      <c r="C10" s="3" t="inlineStr">
-        <is>
-          <t>ACTIVE</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>Python</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>RAG system for contract analysis using Llama-3</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>PDF processing, semantic search, contract queries</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>Meta-Llama-3-8B-Instruct, RAG pipeline</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>LegalEase-AI</t>
-        </is>
-      </c>
-      <c r="B11" s="2" t="inlineStr">
-        <is>
-          <t>Recent</t>
-        </is>
-      </c>
-      <c r="C11" s="3" t="inlineStr">
-        <is>
-          <t>ACTIVE</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>Python</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>Document analyzer, legal chatbot, lawyer fee estimator</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>Legal topic simplification, document analysis, fee estimation</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>LLMs, vectorized database, Flask</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>Legal-Advisor-LLM</t>
-        </is>
-      </c>
-      <c r="B12" s="2" t="inlineStr">
-        <is>
-          <t>Recent</t>
-        </is>
-      </c>
-      <c r="C12" s="3" t="inlineStr">
-        <is>
-          <t>ACTIVE</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>Python</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>Legal chatbot powered by LLM and RAG</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>Legal term Q&amp;A, document retrieval, advice generation</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>LLM + RAG, document embeddings</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:F16"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="20" customWidth="1" min="1" max="1"/>
-    <col width="25" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
-    <col width="40" customWidth="1" min="4" max="4"/>
-    <col width="40" customWidth="1" min="5" max="5"/>
-    <col width="40" customWidth="1" min="6" max="6"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Use Case Category</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Use Case</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Description</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>Open Source Tools</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>Commercial Tools</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>Key Benefits</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>Contract Review</t>
-        </is>
-      </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>Clause Extraction</t>
-        </is>
-      </c>
-      <c r="C2" s="2" t="inlineStr">
-        <is>
-          <t>Automatically identify and extract key clauses from contracts</t>
-        </is>
-      </c>
-      <c r="D2" s="2" t="inlineStr">
-        <is>
-          <t>OpenContracts, LexNLP, contract-analyzer</t>
-        </is>
-      </c>
-      <c r="E2" s="2" t="inlineStr">
-        <is>
-          <t>Kira (Litera), Diligen, Luminance</t>
-        </is>
-      </c>
-      <c r="F2" s="2" t="inlineStr">
-        <is>
-          <t>50-85% time savings on review workloads</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>Contract Review</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>Risk Identification</t>
-        </is>
-      </c>
-      <c r="C3" s="2" t="inlineStr">
-        <is>
-          <t>Flag potential risks, ambiguities, and non-standard terms</t>
-        </is>
-      </c>
-      <c r="D3" s="2" t="inlineStr">
-        <is>
-          <t>CrewAI Contract Risk, Legal-AI_Project</t>
-        </is>
-      </c>
-      <c r="E3" s="2" t="inlineStr">
-        <is>
-          <t>Ironclad, Icertis, Juro</t>
-        </is>
-      </c>
-      <c r="F3" s="2" t="inlineStr">
-        <is>
-          <t>Proactive risk mitigation before signing</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>Contract Review</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>Playbook Comparison</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>Compare contract against standard playbooks and policies</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>OpenContracts</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>Kira, Evisort, LinkSquares</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>Ensure compliance with company standards</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>Contract Analysis</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>Obligation Tracking</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>Extract and track contractual obligations and deadlines</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>LexNLP (dates/durations)</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>Agiloft, Concord, ContractPodAI</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>Prevent missed deadlines and penalties</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>Contract Analysis</t>
-        </is>
-      </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>Monetary Term Extraction</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>Extract payment terms, amounts, percentages, penalties</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>LexNLP</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>Kira, Luminance</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>Accurate financial obligation tracking</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>Due Diligence</t>
-        </is>
-      </c>
-      <c r="B7" s="2" t="inlineStr">
-        <is>
-          <t>M&amp;A Document Review</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>Bulk review of contracts during mergers and acquisitions</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>OpenContracts, Legal-Text-Analytics</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>Kira (1,400+ clause types), Diligen</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>Weeks of review compressed to days</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>Due Diligence</t>
-        </is>
-      </c>
-      <c r="B8" s="2" t="inlineStr">
-        <is>
-          <t>Data Room Analysis</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>Analyze virtual data room documents for key issues</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>OpenContracts</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>Kira, Diligen, Luminance</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>Comprehensive risk assessment</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>Legal Research</t>
-        </is>
-      </c>
-      <c r="B9" s="2" t="inlineStr">
-        <is>
-          <t>Case Law Search</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>Find relevant cases and precedents</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>LawGlance, OLAW</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>Westlaw Edge, LexisNexis, CaseText</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>Faster research, broader coverage</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>Legal Research</t>
-        </is>
-      </c>
-      <c r="B10" s="2" t="inlineStr">
-        <is>
-          <t>Statute Retrieval</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>Find applicable statutes and regulations</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>LawGlance</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>Westlaw, Bloomberg Law</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>Comprehensive regulatory compliance</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>Document Drafting</t>
-        </is>
-      </c>
-      <c r="B11" s="2" t="inlineStr">
-        <is>
-          <t>Contract Generation</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>Generate contracts from templates with AI assistance</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>GitLaw (templates)</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>Spellbook, LawDroid, Harvey</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>Faster first drafts, consistency</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>Document Drafting</t>
-        </is>
-      </c>
-      <c r="B12" s="2" t="inlineStr">
-        <is>
-          <t>Redlining/Markup</t>
-        </is>
-      </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>AI-assisted contract redlining and suggested changes</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>Ally Legal Assistant</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>Spellbook, Robin AI, BlackBoiler</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>Reduce negotiation cycles</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>Compliance</t>
-        </is>
-      </c>
-      <c r="B13" s="2" t="inlineStr">
-        <is>
-          <t>Regulatory Monitoring</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>Track regulatory changes affecting contracts</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>Kira, Thomson Reuters, Wolters Kluwer</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>Stay ahead of compliance requirements</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>Compliance</t>
-        </is>
-      </c>
-      <c r="B14" s="2" t="inlineStr">
-        <is>
-          <t>Policy Enforcement</t>
-        </is>
-      </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>Ensure contracts comply with internal policies</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>OpenContracts</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>Ironclad, Icertis</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>Reduce legal risk exposure</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>E-Discovery</t>
-        </is>
-      </c>
-      <c r="B15" s="2" t="inlineStr">
-        <is>
-          <t>Document Classification</t>
-        </is>
-      </c>
-      <c r="C15" s="2" t="inlineStr">
-        <is>
-          <t>Classify documents for relevance in litigation</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>Legal-Text-Analytics resources</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>Relativity, Reveal, Exterro</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>Reduce review costs significantly</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>E-Discovery</t>
-        </is>
-      </c>
-      <c r="B16" s="2" t="inlineStr">
-        <is>
-          <t>Privilege Detection</t>
-        </is>
-      </c>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>Identify privileged documents automatically</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>LexNLP (entity extraction)</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>Relativity, Logikcull</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>Prevent privilege waiver</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -2662,7 +1718,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -3484,24 +2540,1692 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F27"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="18" customWidth="1" min="1" max="1"/>
+    <col width="25" customWidth="1" min="2" max="2"/>
+    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="45" customWidth="1" min="4" max="4"/>
+    <col width="40" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="9" t="inlineStr">
+        <is>
+          <t>Category</t>
+        </is>
+      </c>
+      <c r="B1" s="9" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="C1" s="9" t="inlineStr">
+        <is>
+          <t>Description</t>
+        </is>
+      </c>
+      <c r="D1" s="9" t="inlineStr">
+        <is>
+          <t>Technical Details</t>
+        </is>
+      </c>
+      <c r="E1" s="9" t="inlineStr">
+        <is>
+          <t>URL/Source</t>
+        </is>
+      </c>
+      <c r="F1" s="9" t="inlineStr">
+        <is>
+          <t>Status/Activity</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="11" t="inlineStr">
+        <is>
+          <t>SECTION: OPEN SOURCE / CODE REPOSITORIES</t>
+        </is>
+      </c>
+      <c r="B2" s="12" t="n"/>
+      <c r="C2" s="12" t="n"/>
+      <c r="D2" s="12" t="n"/>
+      <c r="E2" s="12" t="n"/>
+      <c r="F2" s="13" t="n"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="10" t="inlineStr">
+        <is>
+          <t>Financial Modeling</t>
+        </is>
+      </c>
+      <c r="B3" s="10" t="inlineStr">
+        <is>
+          <t>halessi/DCF</t>
+        </is>
+      </c>
+      <c r="C3" s="10" t="inlineStr">
+        <is>
+          <t>Discounted Cash Flow library with sensitivity analysis for valuation</t>
+        </is>
+      </c>
+      <c r="D3" s="10" t="inlineStr">
+        <is>
+          <t>Python, API integration, earnings_growth_rate, cap_ex_growth, perpetual_growth, discount_rate</t>
+        </is>
+      </c>
+      <c r="E3" s="10" t="inlineStr">
+        <is>
+          <t>https://github.com/halessi/DCF</t>
+        </is>
+      </c>
+      <c r="F3" s="10" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="10" t="inlineStr">
+        <is>
+          <t>Financial Modeling</t>
+        </is>
+      </c>
+      <c r="B4" s="10" t="inlineStr">
+        <is>
+          <t>JerBouma/FinanceToolkit</t>
+        </is>
+      </c>
+      <c r="C4" s="10" t="inlineStr">
+        <is>
+          <t>Comprehensive financial analysis toolkit including DCF and DUPONT models</t>
+        </is>
+      </c>
+      <c r="D4" s="10" t="inlineStr">
+        <is>
+          <t>Python, Pandas, Financial ratios, profitability/efficiency/liquidity/solvency analysis</t>
+        </is>
+      </c>
+      <c r="E4" s="10" t="inlineStr">
+        <is>
+          <t>https://github.com/JerBouma/FinanceToolkit</t>
+        </is>
+      </c>
+      <c r="F4" s="10" t="inlineStr">
+        <is>
+          <t>Active - 4.1K stars</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="10" t="inlineStr">
+        <is>
+          <t>Valuation</t>
+        </is>
+      </c>
+      <c r="B5" s="10" t="inlineStr">
+        <is>
+          <t>scfengv/Stock-Valuation</t>
+        </is>
+      </c>
+      <c r="C5" s="10" t="inlineStr">
+        <is>
+          <t>5-year DCF model for intrinsic value calculation with margin of safety</t>
+        </is>
+      </c>
+      <c r="D5" s="10" t="inlineStr">
+        <is>
+          <t>Python, yfinance API, Selenium, WACC calculation, Terminal Value</t>
+        </is>
+      </c>
+      <c r="E5" s="10" t="inlineStr">
+        <is>
+          <t>https://github.com/scfengv/Stock-Valuation</t>
+        </is>
+      </c>
+      <c r="F5" s="10" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="10" t="inlineStr">
+        <is>
+          <t>Valuation</t>
+        </is>
+      </c>
+      <c r="B6" s="10" t="inlineStr">
+        <is>
+          <t>akashaero/Intrinsic-Value-Calculator</t>
+        </is>
+      </c>
+      <c r="C6" s="10" t="inlineStr">
+        <is>
+          <t>Batch stock valuation tool with GUI for DCF calculations</t>
+        </is>
+      </c>
+      <c r="D6" s="10" t="inlineStr">
+        <is>
+          <t>Python, GUI, batch processing, revenue growth assumptions</t>
+        </is>
+      </c>
+      <c r="E6" s="10" t="inlineStr">
+        <is>
+          <t>https://github.com/akashaero/Intrinsic-Value-Calculator</t>
+        </is>
+      </c>
+      <c r="F6" s="10" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="10" t="inlineStr">
+        <is>
+          <t>Valuation</t>
+        </is>
+      </c>
+      <c r="B7" s="10" t="inlineStr">
+        <is>
+          <t>platha19vsb/Dcf-valuation</t>
+        </is>
+      </c>
+      <c r="C7" s="10" t="inlineStr">
+        <is>
+          <t>DCF valuation modeling for investment analysis</t>
+        </is>
+      </c>
+      <c r="D7" s="10" t="inlineStr">
+        <is>
+          <t>Python, Matplotlib visualization, cash flow analysis</t>
+        </is>
+      </c>
+      <c r="E7" s="10" t="inlineStr">
+        <is>
+          <t>https://github.com/platha19vsb/Dcf-valuation</t>
+        </is>
+      </c>
+      <c r="F7" s="10" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="10" t="inlineStr">
+        <is>
+          <t>Due Diligence</t>
+        </is>
+      </c>
+      <c r="B8" s="10" t="inlineStr">
+        <is>
+          <t>nycoschlr/DCF_Model_Python</t>
+        </is>
+      </c>
+      <c r="C8" s="10" t="inlineStr">
+        <is>
+          <t>GUI-based company valuation using Financial Modeling Prep API</t>
+        </is>
+      </c>
+      <c r="D8" s="10" t="inlineStr">
+        <is>
+          <t>Python, Tkinter GUI, API integration, intrinsic vs market price comparison</t>
+        </is>
+      </c>
+      <c r="E8" s="10" t="inlineStr">
+        <is>
+          <t>https://github.com/nycoschlr/DCF_Model_Python</t>
+        </is>
+      </c>
+      <c r="F8" s="10" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="10" t="inlineStr">
+        <is>
+          <t>Due Diligence</t>
+        </is>
+      </c>
+      <c r="B9" s="10" t="inlineStr">
+        <is>
+          <t>Nico-Rode/Automated_DCF_Proj</t>
+        </is>
+      </c>
+      <c r="C9" s="10" t="inlineStr">
+        <is>
+          <t>Automated financial data pulling and DCF evaluation</t>
+        </is>
+      </c>
+      <c r="D9" s="10" t="inlineStr">
+        <is>
+          <t>Python, Morningstar/Yahoo Finance data, 100+ financial functions</t>
+        </is>
+      </c>
+      <c r="E9" s="10" t="inlineStr">
+        <is>
+          <t>https://github.com/Nico-Rode/Automated_DCF_Proj</t>
+        </is>
+      </c>
+      <c r="F9" s="10" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="10" t="inlineStr">
+        <is>
+          <t>M&amp;A Analysis</t>
+        </is>
+      </c>
+      <c r="B10" s="10" t="inlineStr">
+        <is>
+          <t>GitHub M&amp;A Topics</t>
+        </is>
+      </c>
+      <c r="C10" s="10" t="inlineStr">
+        <is>
+          <t>Collection of M&amp;A deal tracking, NDA generators, acquisition models</t>
+        </is>
+      </c>
+      <c r="D10" s="10" t="inlineStr">
+        <is>
+          <t>Various languages, financial synergies, pro forma valuation</t>
+        </is>
+      </c>
+      <c r="E10" s="10" t="inlineStr">
+        <is>
+          <t>https://github.com/topics/mergers-and-acquisitions</t>
+        </is>
+      </c>
+      <c r="F10" s="10" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="10" t="inlineStr">
+        <is>
+          <t>OSS Due Diligence</t>
+        </is>
+      </c>
+      <c r="B11" s="10" t="inlineStr">
+        <is>
+          <t>Linux Foundation M&amp;A Checklist</t>
+        </is>
+      </c>
+      <c r="C11" s="10" t="inlineStr">
+        <is>
+          <t>Assessment checklist for evaluating open source practices in M&amp;A</t>
+        </is>
+      </c>
+      <c r="D11" s="10" t="inlineStr">
+        <is>
+          <t>Documentation, compliance framework, license obligation tracking</t>
+        </is>
+      </c>
+      <c r="E11" s="10" t="inlineStr">
+        <is>
+          <t>https://www.linuxfoundation.org/resources/publications/</t>
+        </is>
+      </c>
+      <c r="F11" s="10" t="inlineStr">
+        <is>
+          <t>Reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="14" t="inlineStr">
+        <is>
+          <t>SECTION: VENDOR / SAAS PRODUCTS (Commercial)</t>
+        </is>
+      </c>
+      <c r="B12" s="12" t="n"/>
+      <c r="C12" s="12" t="n"/>
+      <c r="D12" s="12" t="n"/>
+      <c r="E12" s="12" t="n"/>
+      <c r="F12" s="13" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="10" t="inlineStr">
+        <is>
+          <t>Deal Sourcing</t>
+        </is>
+      </c>
+      <c r="B13" s="10" t="inlineStr">
+        <is>
+          <t>PitchBook</t>
+        </is>
+      </c>
+      <c r="C13" s="10" t="inlineStr">
+        <is>
+          <t>Market intelligence platform for deal sourcing and company research</t>
+        </is>
+      </c>
+      <c r="D13" s="10" t="inlineStr">
+        <is>
+          <t>Proprietary ML, company data, financial metrics, deal flow tracking</t>
+        </is>
+      </c>
+      <c r="E13" s="10" t="inlineStr">
+        <is>
+          <t>https://pitchbook.com/</t>
+        </is>
+      </c>
+      <c r="F13" s="10" t="inlineStr">
+        <is>
+          <t>Commercial - Enterprise</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="10" t="inlineStr">
+        <is>
+          <t>Deal Sourcing</t>
+        </is>
+      </c>
+      <c r="B14" s="10" t="inlineStr">
+        <is>
+          <t>CB Insights</t>
+        </is>
+      </c>
+      <c r="C14" s="10" t="inlineStr">
+        <is>
+          <t>Investment analytics and company data platform</t>
+        </is>
+      </c>
+      <c r="D14" s="10" t="inlineStr">
+        <is>
+          <t>Proprietary AI, market maps, company signals, funding data</t>
+        </is>
+      </c>
+      <c r="E14" s="10" t="inlineStr">
+        <is>
+          <t>https://www.cbinsights.com/</t>
+        </is>
+      </c>
+      <c r="F14" s="10" t="inlineStr">
+        <is>
+          <t>Commercial - Enterprise</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="10" t="inlineStr">
+        <is>
+          <t>Deal Sourcing</t>
+        </is>
+      </c>
+      <c r="B15" s="10" t="inlineStr">
+        <is>
+          <t>AlphaSense</t>
+        </is>
+      </c>
+      <c r="C15" s="10" t="inlineStr">
+        <is>
+          <t>Financial research and market intelligence search platform</t>
+        </is>
+      </c>
+      <c r="D15" s="10" t="inlineStr">
+        <is>
+          <t>NLP search, sentiment analysis, earnings call analysis</t>
+        </is>
+      </c>
+      <c r="E15" s="10" t="inlineStr">
+        <is>
+          <t>https://www.alpha-sense.com/</t>
+        </is>
+      </c>
+      <c r="F15" s="10" t="inlineStr">
+        <is>
+          <t>Commercial - Enterprise</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="10" t="inlineStr">
+        <is>
+          <t>Deal Sourcing</t>
+        </is>
+      </c>
+      <c r="B16" s="10" t="inlineStr">
+        <is>
+          <t>SourceScrub</t>
+        </is>
+      </c>
+      <c r="C16" s="10" t="inlineStr">
+        <is>
+          <t>Target identification and deal flow management</t>
+        </is>
+      </c>
+      <c r="D16" s="10" t="inlineStr">
+        <is>
+          <t>Web scraping, company matching, CRM integration</t>
+        </is>
+      </c>
+      <c r="E16" s="10" t="inlineStr">
+        <is>
+          <t>https://www.sourcescrub.com/</t>
+        </is>
+      </c>
+      <c r="F16" s="10" t="inlineStr">
+        <is>
+          <t>Commercial - Mid-market</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="10" t="inlineStr">
+        <is>
+          <t>Relationship Intelligence</t>
+        </is>
+      </c>
+      <c r="B17" s="10" t="inlineStr">
+        <is>
+          <t>Affinity</t>
+        </is>
+      </c>
+      <c r="C17" s="10" t="inlineStr">
+        <is>
+          <t>CRM with relationship intelligence for deal teams</t>
+        </is>
+      </c>
+      <c r="D17" s="10" t="inlineStr">
+        <is>
+          <t>Graph analytics, email parsing, relationship scoring</t>
+        </is>
+      </c>
+      <c r="E17" s="10" t="inlineStr">
+        <is>
+          <t>https://www.affinity.co/</t>
+        </is>
+      </c>
+      <c r="F17" s="10" t="inlineStr">
+        <is>
+          <t>Commercial - Mid-market</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="10" t="inlineStr">
+        <is>
+          <t>Due Diligence</t>
+        </is>
+      </c>
+      <c r="B18" s="10" t="inlineStr">
+        <is>
+          <t>Kira Systems (Litera)</t>
+        </is>
+      </c>
+      <c r="C18" s="10" t="inlineStr">
+        <is>
+          <t>AI contract analysis for M&amp;A due diligence</t>
+        </is>
+      </c>
+      <c r="D18" s="10" t="inlineStr">
+        <is>
+          <t>ML clause extraction, bulk contract review, change-of-control detection</t>
+        </is>
+      </c>
+      <c r="E18" s="10" t="inlineStr">
+        <is>
+          <t>https://www.litera.com/kira</t>
+        </is>
+      </c>
+      <c r="F18" s="10" t="inlineStr">
+        <is>
+          <t>Commercial - Enterprise</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="10" t="inlineStr">
+        <is>
+          <t>Due Diligence</t>
+        </is>
+      </c>
+      <c r="B19" s="10" t="inlineStr">
+        <is>
+          <t>Datasite</t>
+        </is>
+      </c>
+      <c r="C19" s="10" t="inlineStr">
+        <is>
+          <t>VDR with AI-powered document management and Q&amp;A</t>
+        </is>
+      </c>
+      <c r="D19" s="10" t="inlineStr">
+        <is>
+          <t>Auto-indexing, AI Q&amp;A, redaction, ISO 27001/SOC 2 certified</t>
+        </is>
+      </c>
+      <c r="E19" s="10" t="inlineStr">
+        <is>
+          <t>https://www.datasite.com/</t>
+        </is>
+      </c>
+      <c r="F19" s="10" t="inlineStr">
+        <is>
+          <t>Commercial - Enterprise</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="10" t="inlineStr">
+        <is>
+          <t>Due Diligence</t>
+        </is>
+      </c>
+      <c r="B20" s="10" t="inlineStr">
+        <is>
+          <t>DealRoom</t>
+        </is>
+      </c>
+      <c r="C20" s="10" t="inlineStr">
+        <is>
+          <t>M&amp;A lifecycle platform with AI document analysis</t>
+        </is>
+      </c>
+      <c r="D20" s="10" t="inlineStr">
+        <is>
+          <t>Workflow automation, NLP search, document summarization</t>
+        </is>
+      </c>
+      <c r="E20" s="10" t="inlineStr">
+        <is>
+          <t>https://dealroom.net/</t>
+        </is>
+      </c>
+      <c r="F20" s="10" t="inlineStr">
+        <is>
+          <t>Commercial - $25K/year</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="10" t="inlineStr">
+        <is>
+          <t>Due Diligence</t>
+        </is>
+      </c>
+      <c r="B21" s="10" t="inlineStr">
+        <is>
+          <t>Hebbia</t>
+        </is>
+      </c>
+      <c r="C21" s="10" t="inlineStr">
+        <is>
+          <t>AI knowledge work platform for document Q&amp;A</t>
+        </is>
+      </c>
+      <c r="D21" s="10" t="inlineStr">
+        <is>
+          <t>LLM-powered, RAG, semantic search across data rooms</t>
+        </is>
+      </c>
+      <c r="E21" s="10" t="inlineStr">
+        <is>
+          <t>https://www.hebbia.ai/</t>
+        </is>
+      </c>
+      <c r="F21" s="10" t="inlineStr">
+        <is>
+          <t>Commercial - Enterprise</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="10" t="inlineStr">
+        <is>
+          <t>Due Diligence</t>
+        </is>
+      </c>
+      <c r="B22" s="10" t="inlineStr">
+        <is>
+          <t>ToltIQ</t>
+        </is>
+      </c>
+      <c r="C22" s="10" t="inlineStr">
+        <is>
+          <t>Private markets due diligence automation</t>
+        </is>
+      </c>
+      <c r="D22" s="10" t="inlineStr">
+        <is>
+          <t>AI extraction, deal analytics, portfolio monitoring</t>
+        </is>
+      </c>
+      <c r="E22" s="10" t="inlineStr">
+        <is>
+          <t>https://toltiq.com/</t>
+        </is>
+      </c>
+      <c r="F22" s="10" t="inlineStr">
+        <is>
+          <t>Commercial - PE focused</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="10" t="inlineStr">
+        <is>
+          <t>VDR</t>
+        </is>
+      </c>
+      <c r="B23" s="10" t="inlineStr">
+        <is>
+          <t>Intralinks</t>
+        </is>
+      </c>
+      <c r="C23" s="10" t="inlineStr">
+        <is>
+          <t>Enterprise virtual data room for complex transactions</t>
+        </is>
+      </c>
+      <c r="D23" s="10" t="inlineStr">
+        <is>
+          <t>AI indexing, access analytics, global compliance</t>
+        </is>
+      </c>
+      <c r="E23" s="10" t="inlineStr">
+        <is>
+          <t>https://www.intralinks.com/</t>
+        </is>
+      </c>
+      <c r="F23" s="10" t="inlineStr">
+        <is>
+          <t>Commercial - Enterprise</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="10" t="inlineStr">
+        <is>
+          <t>VDR</t>
+        </is>
+      </c>
+      <c r="B24" s="10" t="inlineStr">
+        <is>
+          <t>iDeals</t>
+        </is>
+      </c>
+      <c r="C24" s="10" t="inlineStr">
+        <is>
+          <t>Mid-market virtual data room with smart features</t>
+        </is>
+      </c>
+      <c r="D24" s="10" t="inlineStr">
+        <is>
+          <t>Auto-indexing, watermarking, granular permissions</t>
+        </is>
+      </c>
+      <c r="E24" s="10" t="inlineStr">
+        <is>
+          <t>https://www.idealsvdr.com/</t>
+        </is>
+      </c>
+      <c r="F24" s="10" t="inlineStr">
+        <is>
+          <t>Commercial - Mid-market</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="10" t="inlineStr">
+        <is>
+          <t>VDR</t>
+        </is>
+      </c>
+      <c r="B25" s="10" t="inlineStr">
+        <is>
+          <t>FirmRoom</t>
+        </is>
+      </c>
+      <c r="C25" s="10" t="inlineStr">
+        <is>
+          <t>AI-powered VDR for M&amp;A transactions</t>
+        </is>
+      </c>
+      <c r="D25" s="10" t="inlineStr">
+        <is>
+          <t>Document AI, Q&amp;A automation, analytics</t>
+        </is>
+      </c>
+      <c r="E25" s="10" t="inlineStr">
+        <is>
+          <t>https://firmroom.com/</t>
+        </is>
+      </c>
+      <c r="F25" s="10" t="inlineStr">
+        <is>
+          <t>Commercial - Mid-market</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="10" t="inlineStr">
+        <is>
+          <t>Portfolio</t>
+        </is>
+      </c>
+      <c r="B26" s="10" t="inlineStr">
+        <is>
+          <t>BlackRock Aladdin</t>
+        </is>
+      </c>
+      <c r="C26" s="10" t="inlineStr">
+        <is>
+          <t>Investment and risk management platform</t>
+        </is>
+      </c>
+      <c r="D26" s="10" t="inlineStr">
+        <is>
+          <t>Portfolio analytics, risk models, performance attribution</t>
+        </is>
+      </c>
+      <c r="E26" s="10" t="inlineStr">
+        <is>
+          <t>https://www.blackrock.com/aladdin</t>
+        </is>
+      </c>
+      <c r="F26" s="10" t="inlineStr">
+        <is>
+          <t>Commercial - Enterprise</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="10" t="inlineStr">
+        <is>
+          <t>OSS Audit</t>
+        </is>
+      </c>
+      <c r="B27" s="10" t="inlineStr">
+        <is>
+          <t>Black Duck (Synopsys)</t>
+        </is>
+      </c>
+      <c r="C27" s="10" t="inlineStr">
+        <is>
+          <t>Open source risk analysis for M&amp;A due diligence</t>
+        </is>
+      </c>
+      <c r="D27" s="10" t="inlineStr">
+        <is>
+          <t>SCA scanning, license compliance, vulnerability detection</t>
+        </is>
+      </c>
+      <c r="E27" s="10" t="inlineStr">
+        <is>
+          <t>https://www.blackduck.com/</t>
+        </is>
+      </c>
+      <c r="F27" s="10" t="inlineStr">
+        <is>
+          <t>Commercial - Enterprise</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A2:F2"/>
+    <mergeCell ref="A12:F12"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F26"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="18" customWidth="1" min="1" max="1"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="45" customWidth="1" min="4" max="4"/>
+    <col width="45" customWidth="1" min="5" max="5"/>
+    <col width="22" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="9" t="inlineStr">
+        <is>
+          <t>Category</t>
+        </is>
+      </c>
+      <c r="B1" s="9" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="C1" s="9" t="inlineStr">
+        <is>
+          <t>Description</t>
+        </is>
+      </c>
+      <c r="D1" s="9" t="inlineStr">
+        <is>
+          <t>Technical Details</t>
+        </is>
+      </c>
+      <c r="E1" s="9" t="inlineStr">
+        <is>
+          <t>URL/Source</t>
+        </is>
+      </c>
+      <c r="F1" s="9" t="inlineStr">
+        <is>
+          <t>Status/Activity</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="11" t="inlineStr">
+        <is>
+          <t>SECTION: OPEN SOURCE / CODE REPOSITORIES</t>
+        </is>
+      </c>
+      <c r="B2" s="12" t="n"/>
+      <c r="C2" s="12" t="n"/>
+      <c r="D2" s="12" t="n"/>
+      <c r="E2" s="12" t="n"/>
+      <c r="F2" s="13" t="n"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="10" t="inlineStr">
+        <is>
+          <t>Contract Analysis</t>
+        </is>
+      </c>
+      <c r="B3" s="10" t="inlineStr">
+        <is>
+          <t>Open-Source-Legal/OpenContracts</t>
+        </is>
+      </c>
+      <c r="C3" s="10" t="inlineStr">
+        <is>
+          <t>Enterprise-grade LLM workspace for document extraction, redaction, rights management</t>
+        </is>
+      </c>
+      <c r="D3" s="10" t="inlineStr">
+        <is>
+          <t>Python, LLM integration, API-first, prompt playground, data extraction pipelines</t>
+        </is>
+      </c>
+      <c r="E3" s="10" t="inlineStr">
+        <is>
+          <t>https://github.com/Open-Source-Legal/OpenContracts</t>
+        </is>
+      </c>
+      <c r="F3" s="10" t="inlineStr">
+        <is>
+          <t>Active - 700+ stars</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="10" t="inlineStr">
+        <is>
+          <t>NLP Library</t>
+        </is>
+      </c>
+      <c r="B4" s="10" t="inlineStr">
+        <is>
+          <t>LexPredict/lexpredict-lexnlp</t>
+        </is>
+      </c>
+      <c r="C4" s="10" t="inlineStr">
+        <is>
+          <t>Comprehensive NLP library for legal and regulatory text</t>
+        </is>
+      </c>
+      <c r="D4" s="10" t="inlineStr">
+        <is>
+          <t>Python, spaCy, entity extraction, citation parsing, date/money/duration extraction</t>
+        </is>
+      </c>
+      <c r="E4" s="10" t="inlineStr">
+        <is>
+          <t>https://github.com/LexPredict/lexnlp</t>
+        </is>
+      </c>
+      <c r="F4" s="10" t="inlineStr">
+        <is>
+          <t>Active - 700+ stars</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="10" t="inlineStr">
+        <is>
+          <t>Contract Analysis</t>
+        </is>
+      </c>
+      <c r="B5" s="10" t="inlineStr">
+        <is>
+          <t>ahmetkumass/contract-analyzer</t>
+        </is>
+      </c>
+      <c r="C5" s="10" t="inlineStr">
+        <is>
+          <t>Tool for extracting and analyzing key information from legal contracts</t>
+        </is>
+      </c>
+      <c r="D5" s="10" t="inlineStr">
+        <is>
+          <t>Python, NLP, clause extraction, key term identification</t>
+        </is>
+      </c>
+      <c r="E5" s="10" t="inlineStr">
+        <is>
+          <t>https://github.com/ahmetkumass/contract-analyzer</t>
+        </is>
+      </c>
+      <c r="F5" s="10" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="10" t="inlineStr">
+        <is>
+          <t>Document Analysis</t>
+        </is>
+      </c>
+      <c r="B6" s="10" t="inlineStr">
+        <is>
+          <t>OssamaLouati/Legal-AI_Project</t>
+        </is>
+      </c>
+      <c r="C6" s="10" t="inlineStr">
+        <is>
+          <t>Automated legal document analysis platform with risk identification</t>
+        </is>
+      </c>
+      <c r="D6" s="10" t="inlineStr">
+        <is>
+          <t>Next.js, Flask, T5 model, TextBlob NLP, CUAD dataset</t>
+        </is>
+      </c>
+      <c r="E6" s="10" t="inlineStr">
+        <is>
+          <t>https://github.com/OssamaLouati/Legal-AI_Project</t>
+        </is>
+      </c>
+      <c r="F6" s="10" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="10" t="inlineStr">
+        <is>
+          <t>Text Analytics</t>
+        </is>
+      </c>
+      <c r="B7" s="10" t="inlineStr">
+        <is>
+          <t>Liquid-Legal-Institute/Legal-Text-Analytics</t>
+        </is>
+      </c>
+      <c r="C7" s="10" t="inlineStr">
+        <is>
+          <t>Curated list of resources, methods, and tools for legal text analytics</t>
+        </is>
+      </c>
+      <c r="D7" s="10" t="inlineStr">
+        <is>
+          <t>Multi-language, NLP methods, ML models, datasets</t>
+        </is>
+      </c>
+      <c r="E7" s="10" t="inlineStr">
+        <is>
+          <t>https://github.com/Liquid-Legal-Institute/Legal-Text-Analytics</t>
+        </is>
+      </c>
+      <c r="F7" s="10" t="inlineStr">
+        <is>
+          <t>Active - 600+ stars</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="10" t="inlineStr">
+        <is>
+          <t>Legal Data</t>
+        </is>
+      </c>
+      <c r="B8" s="10" t="inlineStr">
+        <is>
+          <t>openlegaldata/awesome-legal-data</t>
+        </is>
+      </c>
+      <c r="C8" s="10" t="inlineStr">
+        <is>
+          <t>Collection of datasets and resources for legal text processing</t>
+        </is>
+      </c>
+      <c r="D8" s="10" t="inlineStr">
+        <is>
+          <t>Pile-of-Law (256GB), LEDGAR, ContractNLI, CUAD datasets</t>
+        </is>
+      </c>
+      <c r="E8" s="10" t="inlineStr">
+        <is>
+          <t>https://github.com/openlegaldata/awesome-legal-data</t>
+        </is>
+      </c>
+      <c r="F8" s="10" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="10" t="inlineStr">
+        <is>
+          <t>NLP Pipeline</t>
+        </is>
+      </c>
+      <c r="B9" s="10" t="inlineStr">
+        <is>
+          <t>Blackstone</t>
+        </is>
+      </c>
+      <c r="C9" s="10" t="inlineStr">
+        <is>
+          <t>spaCy pipeline and model for NLP on unstructured legal text</t>
+        </is>
+      </c>
+      <c r="D9" s="10" t="inlineStr">
+        <is>
+          <t>Python, spaCy, NER for legal entities, sentence segmentation</t>
+        </is>
+      </c>
+      <c r="E9" s="10" t="inlineStr">
+        <is>
+          <t>https://github.com/ICLRandD/Blackstone</t>
+        </is>
+      </c>
+      <c r="F9" s="10" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="10" t="inlineStr">
+        <is>
+          <t>Text Classification</t>
+        </is>
+      </c>
+      <c r="B10" s="10" t="inlineStr">
+        <is>
+          <t>mohammedar95/NLP_legal_contracts_text_classification</t>
+        </is>
+      </c>
+      <c r="C10" s="10" t="inlineStr">
+        <is>
+          <t>Legal contract text classification using NLP</t>
+        </is>
+      </c>
+      <c r="D10" s="10" t="inlineStr">
+        <is>
+          <t>Python, scikit-learn, BERT, text classification</t>
+        </is>
+      </c>
+      <c r="E10" s="10" t="inlineStr">
+        <is>
+          <t>https://github.com/mohammedar95/NLP_legal_contracs_text_classification</t>
+        </is>
+      </c>
+      <c r="F10" s="10" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="10" t="inlineStr">
+        <is>
+          <t>Indian Legal AI</t>
+        </is>
+      </c>
+      <c r="B11" s="10" t="inlineStr">
+        <is>
+          <t>Legal Assistant &amp; Summarizer</t>
+        </is>
+      </c>
+      <c r="C11" s="10" t="inlineStr">
+        <is>
+          <t>AI legal assistant for Indian law with BART summarization</t>
+        </is>
+      </c>
+      <c r="D11" s="10" t="inlineStr">
+        <is>
+          <t>Python, BART fine-tuned, RAG chatbot, judgment summarization</t>
+        </is>
+      </c>
+      <c r="E11" s="10" t="inlineStr">
+        <is>
+          <t>https://github.com/topics/legal-ai</t>
+        </is>
+      </c>
+      <c r="F11" s="10" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="10" t="inlineStr">
+        <is>
+          <t>Clause Extraction</t>
+        </is>
+      </c>
+      <c r="B12" s="10" t="inlineStr">
+        <is>
+          <t>CUAD Benchmarks</t>
+        </is>
+      </c>
+      <c r="C12" s="10" t="inlineStr">
+        <is>
+          <t>Contract Understanding Atticus Dataset implementations</t>
+        </is>
+      </c>
+      <c r="D12" s="10" t="inlineStr">
+        <is>
+          <t>Python, Transformers, 83.3% F1 on clause extraction, GPT-4 comparison</t>
+        </is>
+      </c>
+      <c r="E12" s="10" t="inlineStr">
+        <is>
+          <t>https://github.com/topics/contract-analysis</t>
+        </is>
+      </c>
+      <c r="F12" s="10" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="14" t="inlineStr">
+        <is>
+          <t>SECTION: VENDOR / SAAS PRODUCTS (Commercial)</t>
+        </is>
+      </c>
+      <c r="B13" s="12" t="n"/>
+      <c r="C13" s="12" t="n"/>
+      <c r="D13" s="12" t="n"/>
+      <c r="E13" s="12" t="n"/>
+      <c r="F13" s="13" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="10" t="inlineStr">
+        <is>
+          <t>Contract Analysis</t>
+        </is>
+      </c>
+      <c r="B14" s="10" t="inlineStr">
+        <is>
+          <t>Kira Systems (Litera)</t>
+        </is>
+      </c>
+      <c r="C14" s="10" t="inlineStr">
+        <is>
+          <t>ML-powered contract review for due diligence and analysis</t>
+        </is>
+      </c>
+      <c r="D14" s="10" t="inlineStr">
+        <is>
+          <t>Proprietary ML, 1000+ smart fields, bulk review, change-of-control</t>
+        </is>
+      </c>
+      <c r="E14" s="10" t="inlineStr">
+        <is>
+          <t>https://www.litera.com/kira</t>
+        </is>
+      </c>
+      <c r="F14" s="10" t="inlineStr">
+        <is>
+          <t>Commercial - Enterprise</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="10" t="inlineStr">
+        <is>
+          <t>Contract Analysis</t>
+        </is>
+      </c>
+      <c r="B15" s="10" t="inlineStr">
+        <is>
+          <t>Luminance</t>
+        </is>
+      </c>
+      <c r="C15" s="10" t="inlineStr">
+        <is>
+          <t>AI platform for contract review and legal document analysis</t>
+        </is>
+      </c>
+      <c r="D15" s="10" t="inlineStr">
+        <is>
+          <t>Proprietary AI, anomaly detection, clause comparison, 80+ languages</t>
+        </is>
+      </c>
+      <c r="E15" s="10" t="inlineStr">
+        <is>
+          <t>https://www.luminance.com/</t>
+        </is>
+      </c>
+      <c r="F15" s="10" t="inlineStr">
+        <is>
+          <t>Commercial - Enterprise</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="10" t="inlineStr">
+        <is>
+          <t>Contract Analysis</t>
+        </is>
+      </c>
+      <c r="B16" s="10" t="inlineStr">
+        <is>
+          <t>eBrevia (DFIN)</t>
+        </is>
+      </c>
+      <c r="C16" s="10" t="inlineStr">
+        <is>
+          <t>AI-powered contract analytics and data extraction</t>
+        </is>
+      </c>
+      <c r="D16" s="10" t="inlineStr">
+        <is>
+          <t>ML extraction, clause library, integration APIs</t>
+        </is>
+      </c>
+      <c r="E16" s="10" t="inlineStr">
+        <is>
+          <t>https://www.dfinsolutions.com/products/ebrevia</t>
+        </is>
+      </c>
+      <c r="F16" s="10" t="inlineStr">
+        <is>
+          <t>Commercial - Enterprise</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="10" t="inlineStr">
+        <is>
+          <t>Contract Analysis</t>
+        </is>
+      </c>
+      <c r="B17" s="10" t="inlineStr">
+        <is>
+          <t>Eigen Technologies</t>
+        </is>
+      </c>
+      <c r="C17" s="10" t="inlineStr">
+        <is>
+          <t>No-code AI document intelligence platform</t>
+        </is>
+      </c>
+      <c r="D17" s="10" t="inlineStr">
+        <is>
+          <t>Document understanding, entity extraction, workflow automation</t>
+        </is>
+      </c>
+      <c r="E17" s="10" t="inlineStr">
+        <is>
+          <t>https://www.eigentech.com/</t>
+        </is>
+      </c>
+      <c r="F17" s="10" t="inlineStr">
+        <is>
+          <t>Commercial - Enterprise</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="10" t="inlineStr">
+        <is>
+          <t>Legal Research</t>
+        </is>
+      </c>
+      <c r="B18" s="10" t="inlineStr">
+        <is>
+          <t>Thomson Reuters Westlaw Edge</t>
+        </is>
+      </c>
+      <c r="C18" s="10" t="inlineStr">
+        <is>
+          <t>AI-powered legal research with predictive analytics</t>
+        </is>
+      </c>
+      <c r="D18" s="10" t="inlineStr">
+        <is>
+          <t>Proprietary AI, case analysis, litigation analytics, KeyCite</t>
+        </is>
+      </c>
+      <c r="E18" s="10" t="inlineStr">
+        <is>
+          <t>https://legal.thomsonreuters.com/en/westlaw</t>
+        </is>
+      </c>
+      <c r="F18" s="10" t="inlineStr">
+        <is>
+          <t>Commercial - Enterprise</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="10" t="inlineStr">
+        <is>
+          <t>Legal Research</t>
+        </is>
+      </c>
+      <c r="B19" s="10" t="inlineStr">
+        <is>
+          <t>LexisNexis Lexis+</t>
+        </is>
+      </c>
+      <c r="C19" s="10" t="inlineStr">
+        <is>
+          <t>Legal research platform with AI-assisted search</t>
+        </is>
+      </c>
+      <c r="D19" s="10" t="inlineStr">
+        <is>
+          <t>NLP search, brief analysis, practical guidance</t>
+        </is>
+      </c>
+      <c r="E19" s="10" t="inlineStr">
+        <is>
+          <t>https://www.lexisnexis.com/en-us/products/lexis-plus.page</t>
+        </is>
+      </c>
+      <c r="F19" s="10" t="inlineStr">
+        <is>
+          <t>Commercial - Enterprise</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="10" t="inlineStr">
+        <is>
+          <t>Contract Management</t>
+        </is>
+      </c>
+      <c r="B20" s="10" t="inlineStr">
+        <is>
+          <t>Ironclad</t>
+        </is>
+      </c>
+      <c r="C20" s="10" t="inlineStr">
+        <is>
+          <t>Contract lifecycle management with AI capabilities</t>
+        </is>
+      </c>
+      <c r="D20" s="10" t="inlineStr">
+        <is>
+          <t>Workflow automation, AI review, CLM integration</t>
+        </is>
+      </c>
+      <c r="E20" s="10" t="inlineStr">
+        <is>
+          <t>https://ironcladapp.com/</t>
+        </is>
+      </c>
+      <c r="F20" s="10" t="inlineStr">
+        <is>
+          <t>Commercial - Enterprise</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="10" t="inlineStr">
+        <is>
+          <t>Contract Management</t>
+        </is>
+      </c>
+      <c r="B21" s="10" t="inlineStr">
+        <is>
+          <t>DocuSign CLM</t>
+        </is>
+      </c>
+      <c r="C21" s="10" t="inlineStr">
+        <is>
+          <t>Contract lifecycle management with AI insights</t>
+        </is>
+      </c>
+      <c r="D21" s="10" t="inlineStr">
+        <is>
+          <t>AI extraction, obligation management, analytics</t>
+        </is>
+      </c>
+      <c r="E21" s="10" t="inlineStr">
+        <is>
+          <t>https://www.docusign.com/products/clm</t>
+        </is>
+      </c>
+      <c r="F21" s="10" t="inlineStr">
+        <is>
+          <t>Commercial - Enterprise</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="10" t="inlineStr">
+        <is>
+          <t>Legal Drafting</t>
+        </is>
+      </c>
+      <c r="B22" s="10" t="inlineStr">
+        <is>
+          <t>Harvey AI</t>
+        </is>
+      </c>
+      <c r="C22" s="10" t="inlineStr">
+        <is>
+          <t>Generative AI for legal professionals</t>
+        </is>
+      </c>
+      <c r="D22" s="10" t="inlineStr">
+        <is>
+          <t>GPT-4 based, document drafting, research, analysis</t>
+        </is>
+      </c>
+      <c r="E22" s="10" t="inlineStr">
+        <is>
+          <t>https://www.harvey.ai/</t>
+        </is>
+      </c>
+      <c r="F22" s="10" t="inlineStr">
+        <is>
+          <t>Commercial - Enterprise</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="10" t="inlineStr">
+        <is>
+          <t>Legal Drafting</t>
+        </is>
+      </c>
+      <c r="B23" s="10" t="inlineStr">
+        <is>
+          <t>Spellbook</t>
+        </is>
+      </c>
+      <c r="C23" s="10" t="inlineStr">
+        <is>
+          <t>AI contract drafting assistant</t>
+        </is>
+      </c>
+      <c r="D23" s="10" t="inlineStr">
+        <is>
+          <t>GPT-4, clause suggestions, contract review, Word integration</t>
+        </is>
+      </c>
+      <c r="E23" s="10" t="inlineStr">
+        <is>
+          <t>https://www.spellbook.legal/</t>
+        </is>
+      </c>
+      <c r="F23" s="10" t="inlineStr">
+        <is>
+          <t>Commercial - Mid-market</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="10" t="inlineStr">
+        <is>
+          <t>Legal Drafting</t>
+        </is>
+      </c>
+      <c r="B24" s="10" t="inlineStr">
+        <is>
+          <t>CoCounsel (Thomson Reuters)</t>
+        </is>
+      </c>
+      <c r="C24" s="10" t="inlineStr">
+        <is>
+          <t>AI legal assistant for research and drafting</t>
+        </is>
+      </c>
+      <c r="D24" s="10" t="inlineStr">
+        <is>
+          <t>GPT-4, document review, legal research, deposition prep</t>
+        </is>
+      </c>
+      <c r="E24" s="10" t="inlineStr">
+        <is>
+          <t>https://casetext.com/cocounsel/</t>
+        </is>
+      </c>
+      <c r="F24" s="10" t="inlineStr">
+        <is>
+          <t>Commercial - Enterprise</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="10" t="inlineStr">
+        <is>
+          <t>E-Discovery</t>
+        </is>
+      </c>
+      <c r="B25" s="10" t="inlineStr">
+        <is>
+          <t>Relativity</t>
+        </is>
+      </c>
+      <c r="C25" s="10" t="inlineStr">
+        <is>
+          <t>E-discovery platform with AI analytics</t>
+        </is>
+      </c>
+      <c r="D25" s="10" t="inlineStr">
+        <is>
+          <t>Predictive coding, AI review, analytics, cloud-based</t>
+        </is>
+      </c>
+      <c r="E25" s="10" t="inlineStr">
+        <is>
+          <t>https://www.relativity.com/</t>
+        </is>
+      </c>
+      <c r="F25" s="10" t="inlineStr">
+        <is>
+          <t>Commercial - Enterprise</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="10" t="inlineStr">
+        <is>
+          <t>E-Discovery</t>
+        </is>
+      </c>
+      <c r="B26" s="10" t="inlineStr">
+        <is>
+          <t>Reveal</t>
+        </is>
+      </c>
+      <c r="C26" s="10" t="inlineStr">
+        <is>
+          <t>AI-powered e-discovery and review</t>
+        </is>
+      </c>
+      <c r="D26" s="10" t="inlineStr">
+        <is>
+          <t>Brainspace AI, concept clustering, predictive coding</t>
+        </is>
+      </c>
+      <c r="E26" s="10" t="inlineStr">
+        <is>
+          <t>https://www.revealdata.com/</t>
+        </is>
+      </c>
+      <c r="F26" s="10" t="inlineStr">
+        <is>
+          <t>Commercial - Enterprise</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A13:F13"/>
+    <mergeCell ref="A2:F2"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F20"/>
+  <dimension ref="A1:F26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="18" customWidth="1" min="1" max="1"/>
-    <col width="28" customWidth="1" min="2" max="2"/>
-    <col width="55" customWidth="1" min="3" max="3"/>
-    <col width="35" customWidth="1" min="4" max="4"/>
-    <col width="40" customWidth="1" min="5" max="5"/>
-    <col width="35" customWidth="1" min="6" max="6"/>
+    <col width="20" customWidth="1" min="1" max="1"/>
+    <col width="32" customWidth="1" min="2" max="2"/>
+    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="50" customWidth="1" min="4" max="4"/>
+    <col width="50" customWidth="1" min="5" max="5"/>
+    <col width="22" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
-    <row r="1" ht="25" customHeight="1">
+    <row r="1">
       <c r="A1" s="9" t="inlineStr">
         <is>
           <t>Category</t>
@@ -3509,7 +4233,7 @@
       </c>
       <c r="B1" s="9" t="inlineStr">
         <is>
-          <t>Use Case</t>
+          <t>Name</t>
         </is>
       </c>
       <c r="C1" s="9" t="inlineStr">
@@ -3519,629 +4243,785 @@
       </c>
       <c r="D1" s="9" t="inlineStr">
         <is>
-          <t>AI Capabilities</t>
+          <t>Technical Details</t>
         </is>
       </c>
       <c r="E1" s="9" t="inlineStr">
         <is>
-          <t>Key Platforms/Tools</t>
+          <t>URL/Source</t>
         </is>
       </c>
       <c r="F1" s="9" t="inlineStr">
         <is>
-          <t>Quantified Benefits</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="60" customHeight="1">
-      <c r="A2" s="10" t="inlineStr">
-        <is>
-          <t>Deal Sourcing</t>
-        </is>
-      </c>
-      <c r="B2" s="10" t="inlineStr">
-        <is>
-          <t>Target Company Identification</t>
-        </is>
-      </c>
-      <c r="C2" s="10" t="inlineStr">
-        <is>
-          <t>AI scans market data, financials, and web sources to identify potential acquisition targets matching investment criteria</t>
-        </is>
-      </c>
-      <c r="D2" s="10" t="inlineStr">
-        <is>
-          <t>Machine Learning, NLP, Predictive Analytics</t>
-        </is>
-      </c>
-      <c r="E2" s="10" t="inlineStr">
-        <is>
-          <t>PitchBook, CB Insights, SourceScrub, Affinity, Motherbrain (EQT)</t>
-        </is>
-      </c>
-      <c r="F2" s="10" t="inlineStr">
-        <is>
-          <t>50-70% reduction in target screening time</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="60" customHeight="1">
+          <t>Status/Activity</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="11" t="inlineStr">
+        <is>
+          <t>SECTION: OPEN SOURCE / CODE REPOSITORIES</t>
+        </is>
+      </c>
+      <c r="B2" s="12" t="n"/>
+      <c r="C2" s="12" t="n"/>
+      <c r="D2" s="12" t="n"/>
+      <c r="E2" s="12" t="n"/>
+      <c r="F2" s="13" t="n"/>
+    </row>
+    <row r="3">
       <c r="A3" s="10" t="inlineStr">
         <is>
-          <t>Deal Sourcing</t>
+          <t>ERP System</t>
         </is>
       </c>
       <c r="B3" s="10" t="inlineStr">
         <is>
-          <t>Relationship Intelligence</t>
+          <t>frappe/erpnext</t>
         </is>
       </c>
       <c r="C3" s="10" t="inlineStr">
         <is>
-          <t>Track relationships across portfolio companies, LPs, and deal networks to identify warm introductions</t>
+          <t>Full-featured open source ERP with manufacturing, accounting, inventory</t>
         </is>
       </c>
       <c r="D3" s="10" t="inlineStr">
         <is>
-          <t>Graph Analytics, NLP, CRM Integration</t>
+          <t>Python, Frappe Framework, REST API, 31K+ stars, multi-currency, BOM management</t>
         </is>
       </c>
       <c r="E3" s="10" t="inlineStr">
         <is>
-          <t>Affinity, DealCloud, Salesforce</t>
+          <t>https://github.com/frappe/erpnext</t>
         </is>
       </c>
       <c r="F3" s="10" t="inlineStr">
         <is>
-          <t>3x increase in qualified deal flow</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="60" customHeight="1">
+          <t>Active - 31K stars</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
       <c r="A4" s="10" t="inlineStr">
         <is>
-          <t>Deal Sourcing</t>
+          <t>Production Planning</t>
         </is>
       </c>
       <c r="B4" s="10" t="inlineStr">
         <is>
-          <t>Market Signal Monitoring</t>
+          <t>frePPLe/frepple</t>
         </is>
       </c>
       <c r="C4" s="10" t="inlineStr">
         <is>
-          <t>Real-time monitoring of news, SEC filings, and social media for M&amp;A signals and opportunities</t>
+          <t>Open source production planning and scheduling</t>
         </is>
       </c>
       <c r="D4" s="10" t="inlineStr">
         <is>
-          <t>NLP, Sentiment Analysis, Event Detection</t>
+          <t>Python/C++, constraint-based planning, demand forecasting, MRP</t>
         </is>
       </c>
       <c r="E4" s="10" t="inlineStr">
         <is>
-          <t>AlphaSense, Sentieo, Tegus</t>
+          <t>https://github.com/frePPLe/frepple</t>
         </is>
       </c>
       <c r="F4" s="10" t="inlineStr">
         <is>
-          <t>Early identification of 40% more opportunities</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="60" customHeight="1">
+          <t>Active - 500+ stars</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
       <c r="A5" s="10" t="inlineStr">
         <is>
-          <t>Due Diligence</t>
+          <t>Supply Chain</t>
         </is>
       </c>
       <c r="B5" s="10" t="inlineStr">
         <is>
-          <t>Contract Analysis &amp; Review</t>
+          <t>Supply-Chain-Optimization</t>
         </is>
       </c>
       <c r="C5" s="10" t="inlineStr">
         <is>
-          <t>Automated extraction of key terms, risks, and obligations from hundreds of contracts in data rooms</t>
+          <t>Supply chain optimization models and algorithms</t>
         </is>
       </c>
       <c r="D5" s="10" t="inlineStr">
         <is>
-          <t>NLP, Document Understanding, ML Classification</t>
+          <t>Python, OR-Tools, linear programming, network optimization</t>
         </is>
       </c>
       <c r="E5" s="10" t="inlineStr">
         <is>
-          <t>Kira Systems, Luminance, eBrevia, Eigen Technologies</t>
+          <t>https://github.com/topics/supply-chain-optimization</t>
         </is>
       </c>
       <c r="F5" s="10" t="inlineStr">
         <is>
-          <t>70-90% reduction in contract review time</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="60" customHeight="1">
+          <t>Active</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
       <c r="A6" s="10" t="inlineStr">
         <is>
-          <t>Due Diligence</t>
+          <t>Demand Forecasting</t>
         </is>
       </c>
       <c r="B6" s="10" t="inlineStr">
         <is>
-          <t>Financial Data Extraction</t>
+          <t>Nixtla/statsforecast</t>
         </is>
       </c>
       <c r="C6" s="10" t="inlineStr">
         <is>
-          <t>Automated extraction and normalization of financial data from disparate documents and formats</t>
+          <t>Lightning fast statistical forecasting</t>
         </is>
       </c>
       <c r="D6" s="10" t="inlineStr">
         <is>
-          <t>OCR, NLP, Data Validation</t>
+          <t>Python, AutoARIMA, ETS, multiple models, 3.5K+ stars</t>
         </is>
       </c>
       <c r="E6" s="10" t="inlineStr">
         <is>
-          <t>Hebbia, ToltIQ, Datasite AI Q&amp;A</t>
+          <t>https://github.com/Nixtla/statsforecast</t>
         </is>
       </c>
       <c r="F6" s="10" t="inlineStr">
         <is>
-          <t>60% faster financial analysis</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="60" customHeight="1">
+          <t>Active - 3.5K stars</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
       <c r="A7" s="10" t="inlineStr">
         <is>
-          <t>Due Diligence</t>
+          <t>Demand Forecasting</t>
         </is>
       </c>
       <c r="B7" s="10" t="inlineStr">
         <is>
-          <t>Risk Identification</t>
+          <t>amazon-science/chronos-forecasting</t>
         </is>
       </c>
       <c r="C7" s="10" t="inlineStr">
         <is>
-          <t>AI-powered identification of hidden risks, litigation, compliance issues, and change-of-control provisions</t>
+          <t>Pretrained time series forecasting models from Amazon</t>
         </is>
       </c>
       <c r="D7" s="10" t="inlineStr">
         <is>
-          <t>NLP, Pattern Recognition, Anomaly Detection</t>
+          <t>Python, PyTorch, zero-shot forecasting, T5 architecture</t>
         </is>
       </c>
       <c r="E7" s="10" t="inlineStr">
         <is>
-          <t>Kira, DealRoom, Datasite</t>
+          <t>https://github.com/amazon-science/chronos-forecasting</t>
         </is>
       </c>
       <c r="F7" s="10" t="inlineStr">
         <is>
-          <t>Identify 2-3x more risk factors</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="60" customHeight="1">
+          <t>Active - 2K+ stars</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
       <c r="A8" s="10" t="inlineStr">
         <is>
-          <t>Due Diligence</t>
+          <t>Inventory Optimization</t>
         </is>
       </c>
       <c r="B8" s="10" t="inlineStr">
         <is>
-          <t>Q&amp;A Automation</t>
+          <t>inventory-optimization</t>
         </is>
       </c>
       <c r="C8" s="10" t="inlineStr">
         <is>
-          <t>AI answers buyer questions by searching across entire data room, reducing seller response burden</t>
+          <t>Collection of inventory optimization models</t>
         </is>
       </c>
       <c r="D8" s="10" t="inlineStr">
         <is>
-          <t>RAG, Semantic Search, LLM</t>
+          <t>Python, EOQ, safety stock, reorder point calculations</t>
         </is>
       </c>
       <c r="E8" s="10" t="inlineStr">
         <is>
-          <t>Datasite AI Q&amp;A, DealRoom, Hebbia</t>
+          <t>https://github.com/topics/inventory-optimization</t>
         </is>
       </c>
       <c r="F8" s="10" t="inlineStr">
         <is>
-          <t>80% reduction in Q&amp;A response time</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="60" customHeight="1">
+          <t>Active</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
       <c r="A9" s="10" t="inlineStr">
         <is>
-          <t>VDR Management</t>
+          <t>Manufacturing AI</t>
         </is>
       </c>
       <c r="B9" s="10" t="inlineStr">
         <is>
-          <t>Intelligent Document Indexing</t>
+          <t>SCIMAI-Gym</t>
         </is>
       </c>
       <c r="C9" s="10" t="inlineStr">
         <is>
-          <t>Auto-categorize, tag, and index documents uploaded to data rooms using AI classification</t>
+          <t>Reinforcement learning environments for supply chain</t>
         </is>
       </c>
       <c r="D9" s="10" t="inlineStr">
         <is>
-          <t>Document Classification, NLP, ML</t>
+          <t>Python, OpenAI Gym, RL agents, inventory management</t>
         </is>
       </c>
       <c r="E9" s="10" t="inlineStr">
         <is>
-          <t>Datasite, Intralinks, iDeals, FirmRoom</t>
+          <t>https://github.com/topics/supply-chain</t>
         </is>
       </c>
       <c r="F9" s="10" t="inlineStr">
         <is>
-          <t>90% faster document organization</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="60" customHeight="1">
+          <t>Active</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
       <c r="A10" s="10" t="inlineStr">
         <is>
-          <t>VDR Management</t>
+          <t>Quality Control</t>
         </is>
       </c>
       <c r="B10" s="10" t="inlineStr">
         <is>
-          <t>Smart Redaction</t>
+          <t>anomaly-detection</t>
         </is>
       </c>
       <c r="C10" s="10" t="inlineStr">
         <is>
-          <t>AI-powered detection and redaction of sensitive information (PII, confidential terms)</t>
+          <t>ML-based anomaly detection for manufacturing</t>
         </is>
       </c>
       <c r="D10" s="10" t="inlineStr">
         <is>
-          <t>NER, Pattern Matching, OCR</t>
+          <t>Python, scikit-learn, isolation forest, autoencoders</t>
         </is>
       </c>
       <c r="E10" s="10" t="inlineStr">
         <is>
-          <t>Datasite, DealRoom</t>
+          <t>https://github.com/topics/anomaly-detection</t>
         </is>
       </c>
       <c r="F10" s="10" t="inlineStr">
         <is>
-          <t>75% reduction in redaction time</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="60" customHeight="1">
+          <t>Active</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
       <c r="A11" s="10" t="inlineStr">
         <is>
-          <t>VDR Management</t>
+          <t>Predictive Maintenance</t>
         </is>
       </c>
       <c r="B11" s="10" t="inlineStr">
         <is>
-          <t>Duplicate Detection</t>
+          <t>predictive-maintenance</t>
         </is>
       </c>
       <c r="C11" s="10" t="inlineStr">
         <is>
-          <t>Identify and flag duplicate documents across large data rooms</t>
+          <t>ML models for equipment failure prediction</t>
         </is>
       </c>
       <c r="D11" s="10" t="inlineStr">
         <is>
-          <t>Document Fingerprinting, Similarity Matching</t>
+          <t>Python, TensorFlow/PyTorch, sensor data, RUL prediction</t>
         </is>
       </c>
       <c r="E11" s="10" t="inlineStr">
         <is>
-          <t>Datasite, Intralinks</t>
+          <t>https://github.com/topics/predictive-maintenance</t>
         </is>
       </c>
       <c r="F11" s="10" t="inlineStr">
         <is>
-          <t>Eliminate 15-20% redundant documents</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="60" customHeight="1">
+          <t>Active</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
       <c r="A12" s="10" t="inlineStr">
         <is>
-          <t>Portfolio Monitoring</t>
+          <t>Process Mining</t>
         </is>
       </c>
       <c r="B12" s="10" t="inlineStr">
         <is>
-          <t>Real-time KPI Dashboards</t>
+          <t>pm4py/pm4py-core</t>
         </is>
       </c>
       <c r="C12" s="10" t="inlineStr">
         <is>
-          <t>Automated aggregation of portfolio company data with AI-generated insights and anomaly detection</t>
+          <t>Process mining library for manufacturing workflows</t>
         </is>
       </c>
       <c r="D12" s="10" t="inlineStr">
         <is>
-          <t>Time Series Analysis, Anomaly Detection, ML</t>
+          <t>Python, BPMN, Petri nets, conformance checking, 1.5K+ stars</t>
         </is>
       </c>
       <c r="E12" s="10" t="inlineStr">
         <is>
-          <t>BlackRock Aladdin, ZBrain, Nosible</t>
+          <t>https://github.com/pm4py/pm4py-core</t>
         </is>
       </c>
       <c r="F12" s="10" t="inlineStr">
         <is>
-          <t>Real-time visibility vs monthly reporting</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="60" customHeight="1">
-      <c r="A13" s="10" t="inlineStr">
-        <is>
-          <t>Portfolio Monitoring</t>
-        </is>
-      </c>
-      <c r="B13" s="10" t="inlineStr">
-        <is>
-          <t>Covenant Compliance Monitoring</t>
-        </is>
-      </c>
-      <c r="C13" s="10" t="inlineStr">
-        <is>
-          <t>Automated tracking of financial covenants with early warning alerts when ratios approach triggers</t>
-        </is>
-      </c>
-      <c r="D13" s="10" t="inlineStr">
-        <is>
-          <t>Rule Engines, Predictive Analytics</t>
-        </is>
-      </c>
-      <c r="E13" s="10" t="inlineStr">
-        <is>
-          <t>BlackRock Aladdin, Carta, eFront</t>
-        </is>
-      </c>
-      <c r="F13" s="10" t="inlineStr">
-        <is>
-          <t>Early warning 30 days before breach</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="60" customHeight="1">
+          <t>Active - 1.5K stars</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="14" t="inlineStr">
+        <is>
+          <t>SECTION: VENDOR / SAAS PRODUCTS (Commercial)</t>
+        </is>
+      </c>
+      <c r="B13" s="12" t="n"/>
+      <c r="C13" s="12" t="n"/>
+      <c r="D13" s="12" t="n"/>
+      <c r="E13" s="12" t="n"/>
+      <c r="F13" s="13" t="n"/>
+    </row>
+    <row r="14">
       <c r="A14" s="10" t="inlineStr">
         <is>
-          <t>Portfolio Monitoring</t>
+          <t>ERP</t>
         </is>
       </c>
       <c r="B14" s="10" t="inlineStr">
         <is>
-          <t>Performance Forecasting</t>
+          <t>SAP S/4HANA</t>
         </is>
       </c>
       <c r="C14" s="10" t="inlineStr">
         <is>
-          <t>ML-based forecasting of portfolio company performance using historical data and market signals</t>
+          <t>Enterprise ERP with embedded AI (Joule) for manufacturing</t>
         </is>
       </c>
       <c r="D14" s="10" t="inlineStr">
         <is>
-          <t>Time Series ML, Ensemble Models</t>
+          <t>Joule AI copilot, predictive MRP, intelligent automation, in-memory</t>
         </is>
       </c>
       <c r="E14" s="10" t="inlineStr">
         <is>
-          <t>KKR internal tools, BlackRock Aladdin</t>
+          <t>https://www.sap.com/products/erp/s4hana.html</t>
         </is>
       </c>
       <c r="F14" s="10" t="inlineStr">
         <is>
-          <t>85% accuracy in quarterly forecasts</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="60" customHeight="1">
+          <t>Commercial - Enterprise</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
       <c r="A15" s="10" t="inlineStr">
         <is>
-          <t>Value Creation</t>
+          <t>ERP</t>
         </is>
       </c>
       <c r="B15" s="10" t="inlineStr">
         <is>
-          <t>Operational Efficiency Analysis</t>
+          <t>Oracle Cloud SCM</t>
         </is>
       </c>
       <c r="C15" s="10" t="inlineStr">
         <is>
-          <t>AI identifies operational improvement opportunities across portfolio companies</t>
+          <t>Cloud supply chain management with AI capabilities</t>
         </is>
       </c>
       <c r="D15" s="10" t="inlineStr">
         <is>
-          <t>Process Mining, Benchmarking, ML</t>
+          <t>AI-driven demand sensing, IoT, digital twin, blockchain</t>
         </is>
       </c>
       <c r="E15" s="10" t="inlineStr">
         <is>
-          <t>Celonis, Arctic AI, McKinsey analytics</t>
+          <t>https://www.oracle.com/scm/</t>
         </is>
       </c>
       <c r="F15" s="10" t="inlineStr">
         <is>
-          <t>15-25% EBITDA improvement identified</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="60" customHeight="1">
+          <t>Commercial - Enterprise</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
       <c r="A16" s="10" t="inlineStr">
         <is>
-          <t>Value Creation</t>
+          <t>ERP</t>
         </is>
       </c>
       <c r="B16" s="10" t="inlineStr">
         <is>
-          <t>Pricing Optimization</t>
+          <t>Microsoft Dynamics 365 SCM</t>
         </is>
       </c>
       <c r="C16" s="10" t="inlineStr">
         <is>
-          <t>ML-driven pricing recommendations for portfolio companies based on market dynamics</t>
+          <t>Supply chain management with Copilot AI</t>
         </is>
       </c>
       <c r="D16" s="10" t="inlineStr">
         <is>
-          <t>Price Elasticity ML, Competitive Analysis</t>
+          <t>Copilot, demand forecasting, warehouse management, IoT</t>
         </is>
       </c>
       <c r="E16" s="10" t="inlineStr">
         <is>
-          <t>Custom ML models, Anaplan, PROS</t>
+          <t>https://dynamics.microsoft.com/en-us/supply-chain-management/</t>
         </is>
       </c>
       <c r="F16" s="10" t="inlineStr">
         <is>
-          <t>3-7% revenue increase</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="60" customHeight="1">
+          <t>Commercial - Enterprise</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
       <c r="A17" s="10" t="inlineStr">
         <is>
-          <t>Value Creation</t>
+          <t>ERP</t>
         </is>
       </c>
       <c r="B17" s="10" t="inlineStr">
         <is>
-          <t>Customer Analytics</t>
+          <t>Infor CloudSuite Industrial</t>
         </is>
       </c>
       <c r="C17" s="10" t="inlineStr">
         <is>
-          <t>Predictive models for customer churn, LTV, and acquisition optimization</t>
+          <t>Manufacturing-focused ERP with Coleman AI</t>
         </is>
       </c>
       <c r="D17" s="10" t="inlineStr">
         <is>
-          <t>Classification ML, Cohort Analysis</t>
+          <t>Coleman AI, shop floor control, APS, quality management</t>
         </is>
       </c>
       <c r="E17" s="10" t="inlineStr">
         <is>
-          <t>Amplitude, Mixpanel, custom models</t>
+          <t>https://www.infor.com/products/cloudsuite-industrial</t>
         </is>
       </c>
       <c r="F17" s="10" t="inlineStr">
         <is>
-          <t>20% reduction in churn</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="60" customHeight="1">
+          <t>Commercial - Enterprise</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
       <c r="A18" s="10" t="inlineStr">
         <is>
-          <t>Exit &amp; Valuation</t>
+          <t>Planning</t>
         </is>
       </c>
       <c r="B18" s="10" t="inlineStr">
         <is>
-          <t>Comparable Company Analysis</t>
+          <t>Kinaxis RapidResponse</t>
         </is>
       </c>
       <c r="C18" s="10" t="inlineStr">
         <is>
-          <t>AI-powered identification and analysis of comparable companies for valuation</t>
+          <t>Concurrent planning with AI/ML capabilities</t>
         </is>
       </c>
       <c r="D18" s="10" t="inlineStr">
         <is>
-          <t>Similarity Matching, Financial Analysis</t>
+          <t>AI scenario planning, demand sensing, S&amp;OP, control tower</t>
         </is>
       </c>
       <c r="E18" s="10" t="inlineStr">
         <is>
-          <t>PitchBook, CapIQ, AlphaSense</t>
+          <t>https://www.kinaxis.com/</t>
         </is>
       </c>
       <c r="F18" s="10" t="inlineStr">
         <is>
-          <t>50% faster comp selection</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="60" customHeight="1">
+          <t>Commercial - Enterprise</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
       <c r="A19" s="10" t="inlineStr">
         <is>
-          <t>Exit &amp; Valuation</t>
+          <t>Planning</t>
         </is>
       </c>
       <c r="B19" s="10" t="inlineStr">
         <is>
-          <t>Exit Timing Optimization</t>
+          <t>Blue Yonder</t>
         </is>
       </c>
       <c r="C19" s="10" t="inlineStr">
         <is>
-          <t>Predictive models suggesting optimal exit windows based on market conditions</t>
+          <t>AI-driven supply chain planning (formerly JDA)</t>
         </is>
       </c>
       <c r="D19" s="10" t="inlineStr">
         <is>
-          <t>Time Series ML, Market Signals</t>
+          <t>Luminate Platform, cognitive demand, autonomous planning</t>
         </is>
       </c>
       <c r="E19" s="10" t="inlineStr">
         <is>
-          <t>PitchBook, custom models</t>
+          <t>https://blueyonder.com/</t>
         </is>
       </c>
       <c r="F19" s="10" t="inlineStr">
         <is>
-          <t>Improved exit multiples</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="60" customHeight="1">
+          <t>Commercial - Enterprise</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
       <c r="A20" s="10" t="inlineStr">
         <is>
-          <t>Exit &amp; Valuation</t>
+          <t>Planning</t>
         </is>
       </c>
       <c r="B20" s="10" t="inlineStr">
         <is>
-          <t>Sell-side Preparation</t>
+          <t>o9 Solutions</t>
         </is>
       </c>
       <c r="C20" s="10" t="inlineStr">
         <is>
-          <t>AI-assisted creation of CIMs, management presentations from data room contents</t>
+          <t>AI-powered integrated business planning</t>
         </is>
       </c>
       <c r="D20" s="10" t="inlineStr">
         <is>
-          <t>Document Generation, LLM</t>
+          <t>Knowledge graph, digital twin, enterprise brain</t>
         </is>
       </c>
       <c r="E20" s="10" t="inlineStr">
         <is>
-          <t>Hebbia, DealRoom</t>
+          <t>https://o9solutions.com/</t>
         </is>
       </c>
       <c r="F20" s="10" t="inlineStr">
         <is>
-          <t>40% faster preparation</t>
+          <t>Commercial - Enterprise</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="10" t="inlineStr">
+        <is>
+          <t>Demand Forecasting</t>
+        </is>
+      </c>
+      <c r="B21" s="10" t="inlineStr">
+        <is>
+          <t>RELEX Solutions</t>
+        </is>
+      </c>
+      <c r="C21" s="10" t="inlineStr">
+        <is>
+          <t>Unified retail and supply chain planning</t>
+        </is>
+      </c>
+      <c r="D21" s="10" t="inlineStr">
+        <is>
+          <t>AI forecasting, markdown optimization, fresh optimization</t>
+        </is>
+      </c>
+      <c r="E21" s="10" t="inlineStr">
+        <is>
+          <t>https://www.relexsolutions.com/</t>
+        </is>
+      </c>
+      <c r="F21" s="10" t="inlineStr">
+        <is>
+          <t>Commercial - Mid-market</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="10" t="inlineStr">
+        <is>
+          <t>Warehouse</t>
+        </is>
+      </c>
+      <c r="B22" s="10" t="inlineStr">
+        <is>
+          <t>Manhattan Associates</t>
+        </is>
+      </c>
+      <c r="C22" s="10" t="inlineStr">
+        <is>
+          <t>Warehouse management with AI optimization</t>
+        </is>
+      </c>
+      <c r="D22" s="10" t="inlineStr">
+        <is>
+          <t>AI slotting, labor optimization, robotics integration</t>
+        </is>
+      </c>
+      <c r="E22" s="10" t="inlineStr">
+        <is>
+          <t>https://www.manh.com/</t>
+        </is>
+      </c>
+      <c r="F22" s="10" t="inlineStr">
+        <is>
+          <t>Commercial - Enterprise</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="10" t="inlineStr">
+        <is>
+          <t>Procurement</t>
+        </is>
+      </c>
+      <c r="B23" s="10" t="inlineStr">
+        <is>
+          <t>Coupa</t>
+        </is>
+      </c>
+      <c r="C23" s="10" t="inlineStr">
+        <is>
+          <t>Spend management with AI insights</t>
+        </is>
+      </c>
+      <c r="D23" s="10" t="inlineStr">
+        <is>
+          <t>Spend intelligence, supplier risk, contract AI</t>
+        </is>
+      </c>
+      <c r="E23" s="10" t="inlineStr">
+        <is>
+          <t>https://www.coupa.com/</t>
+        </is>
+      </c>
+      <c r="F23" s="10" t="inlineStr">
+        <is>
+          <t>Commercial - Enterprise</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="10" t="inlineStr">
+        <is>
+          <t>Quality</t>
+        </is>
+      </c>
+      <c r="B24" s="10" t="inlineStr">
+        <is>
+          <t>Augury</t>
+        </is>
+      </c>
+      <c r="C24" s="10" t="inlineStr">
+        <is>
+          <t>AI-based machine health monitoring</t>
+        </is>
+      </c>
+      <c r="D24" s="10" t="inlineStr">
+        <is>
+          <t>Vibration analysis, predictive maintenance, anomaly detection</t>
+        </is>
+      </c>
+      <c r="E24" s="10" t="inlineStr">
+        <is>
+          <t>https://www.augury.com/</t>
+        </is>
+      </c>
+      <c r="F24" s="10" t="inlineStr">
+        <is>
+          <t>Commercial - Mid-market</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="10" t="inlineStr">
+        <is>
+          <t>Quality</t>
+        </is>
+      </c>
+      <c r="B25" s="10" t="inlineStr">
+        <is>
+          <t>Sight Machine</t>
+        </is>
+      </c>
+      <c r="C25" s="10" t="inlineStr">
+        <is>
+          <t>Manufacturing analytics and AI platform</t>
+        </is>
+      </c>
+      <c r="D25" s="10" t="inlineStr">
+        <is>
+          <t>Digital twin, real-time analytics, quality prediction</t>
+        </is>
+      </c>
+      <c r="E25" s="10" t="inlineStr">
+        <is>
+          <t>https://sightmachine.com/</t>
+        </is>
+      </c>
+      <c r="F25" s="10" t="inlineStr">
+        <is>
+          <t>Commercial - Enterprise</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="10" t="inlineStr">
+        <is>
+          <t>Process Mining</t>
+        </is>
+      </c>
+      <c r="B26" s="10" t="inlineStr">
+        <is>
+          <t>Celonis</t>
+        </is>
+      </c>
+      <c r="C26" s="10" t="inlineStr">
+        <is>
+          <t>Process mining for manufacturing operations</t>
+        </is>
+      </c>
+      <c r="D26" s="10" t="inlineStr">
+        <is>
+          <t>Execution management, process intelligence, action flows</t>
+        </is>
+      </c>
+      <c r="E26" s="10" t="inlineStr">
+        <is>
+          <t>https://www.celonis.com/</t>
+        </is>
+      </c>
+      <c r="F26" s="10" t="inlineStr">
+        <is>
+          <t>Commercial - Enterprise</t>
         </is>
       </c>
     </row>
   </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A13:F13"/>
+    <mergeCell ref="A2:F2"/>
+  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -6429,394 +7309,526 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H9"/>
+  <dimension ref="A1:F16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="28" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="10" customWidth="1" min="3" max="3"/>
-    <col width="8" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="50" customWidth="1" min="6" max="6"/>
-    <col width="50" customWidth="1" min="7" max="7"/>
-    <col width="45" customWidth="1" min="8" max="8"/>
+    <col width="20" customWidth="1" min="1" max="1"/>
+    <col width="25" customWidth="1" min="2" max="2"/>
+    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="40" customWidth="1" min="4" max="4"/>
+    <col width="40" customWidth="1" min="5" max="5"/>
+    <col width="40" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Repository</t>
+          <t>Use Case Category</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Last Update</t>
+          <t>Use Case</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>Status</t>
+          <t>Description</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>Stars</t>
+          <t>Open Source Tools</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>Language</t>
+          <t>Commercial Tools</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Description</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>Key Finance/Accounting Features</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>AI/ML Capabilities</t>
+          <t>Key Benefits</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>ERPNext (frappe/erpnext)</t>
+          <t>Contract Review</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>Feb 5, 2026</t>
-        </is>
-      </c>
-      <c r="C2" s="3" t="inlineStr">
-        <is>
-          <t>ACTIVE</t>
+          <t>Clause Extraction</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>Automatically identify and extract key clauses from contracts</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>31,539</t>
+          <t>OpenContracts, LexNLP, contract-analyzer</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Python</t>
+          <t>Kira (Litera), Diligen, Luminance</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>Free and Open Source ERP for manufacturing, distribution, retail</t>
-        </is>
-      </c>
-      <c r="G2" s="2" t="inlineStr">
-        <is>
-          <t>Full accounting module, cash flow management, asset management, financial reporting, multi-currency</t>
-        </is>
-      </c>
-      <c r="H2" s="2" t="inlineStr">
-        <is>
-          <t>Extensible via Python; integrate with ML pipelines; API-first architecture</t>
+          <t>50-85% time savings on review workloads</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>frePPLe</t>
+          <t>Contract Review</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Feb 5, 2026</t>
-        </is>
-      </c>
-      <c r="C3" s="3" t="inlineStr">
-        <is>
-          <t>ACTIVE</t>
+          <t>Risk Identification</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>Flag potential risks, ambiguities, and non-standard terms</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>631</t>
+          <t>CrewAI Contract Risk, Legal-AI_Project</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>C++/Python</t>
+          <t>Ironclad, Icertis, Juro</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>Open source supply chain planning</t>
-        </is>
-      </c>
-      <c r="G3" s="2" t="inlineStr">
-        <is>
-          <t>Cost forecasting, inventory costing, production scheduling with cost optimization</t>
-        </is>
-      </c>
-      <c r="H3" s="2" t="inlineStr">
-        <is>
-          <t>Time series forecasting, Theory of Constraints, pull-based planning algorithms</t>
+          <t>Proactive risk mitigation before signing</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>SCIMAI-Gym</t>
+          <t>Contract Review</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>Jan 16, 2024</t>
-        </is>
-      </c>
-      <c r="C4" s="3" t="inlineStr">
-        <is>
-          <t>ACTIVE</t>
+          <t>Playbook Comparison</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>Compare contract against standard playbooks and policies</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>103</t>
+          <t>OpenContracts</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Python</t>
+          <t>Kira, Evisort, LinkSquares</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>Supply chain inventory management with deep reinforcement learning</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>Inventory cost optimization, holding cost minimization, stockout prevention</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>Deep RL (DQN, PPO, A2C), OpenAI Gym environment for inventory control</t>
+          <t>Ensure compliance with company standards</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>Supply-Chain-Optimization</t>
+          <t>Contract Analysis</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>Mar 20, 2024</t>
-        </is>
-      </c>
-      <c r="C5" s="3" t="inlineStr">
-        <is>
-          <t>ACTIVE</t>
+          <t>Obligation Tracking</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>Extract and track contractual obligations and deadlines</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>LexNLP (dates/durations)</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Python</t>
+          <t>Agiloft, Concord, ContractPodAI</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>ML for supply chain: demand forecasting, inventory, logistics</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>EOQ calculations, holding cost analysis, supplier cost ranking</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>ML for demand forecasting, logistics optimization, supplier selection scoring</t>
+          <t>Prevent missed deadlines and penalties</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>supplychainpy</t>
+          <t>Contract Analysis</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>Aug 20, 2022</t>
-        </is>
-      </c>
-      <c r="C6" s="4" t="inlineStr">
-        <is>
-          <t>STALE</t>
+          <t>Monetary Term Extraction</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>Extract payment terms, amounts, percentages, penalties</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>313</t>
+          <t>LexNLP</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>Python</t>
+          <t>Kira, Luminance</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>Python library for supply chain analysis and simulation</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>Economic Order Quantity, inventory analysis, uncertain demand modeling</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>Monte Carlo simulation, statistical inventory analysis (replaces Excel/VBA)</t>
+          <t>Accurate financial obligation tracking</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>inventory-management (LSTM)</t>
+          <t>Due Diligence</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>Recent</t>
-        </is>
-      </c>
-      <c r="C7" s="3" t="inlineStr">
-        <is>
-          <t>ACTIVE</t>
+          <t>M&amp;A Document Review</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>Bulk review of contracts during mergers and acquisitions</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>OpenContracts, Legal-Text-Analytics</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>Python</t>
+          <t>Kira (1,400+ clause types), Diligen</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>AI-powered inventory management with LSTM and transfer learning</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>Demand forecasting to minimize stockouts/overstock, storage cost reduction</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>LSTM neural networks, transfer learning for adaptable models</t>
+          <t>Weeks of review compressed to days</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>Django Ledger</t>
+          <t>Due Diligence</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>Active</t>
-        </is>
-      </c>
-      <c r="C8" s="3" t="inlineStr">
-        <is>
-          <t>ACTIVE</t>
+          <t>Data Room Analysis</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>Analyze virtual data room documents for key issues</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>OpenContracts</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>Python</t>
+          <t>Kira, Diligen, Luminance</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>Double-entry accounting on Django framework</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>GAAP-compliant accounting, financial analysis engine, journal entries</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>Extensible Django framework; can integrate with ML models</t>
+          <t>Comprehensive risk assessment</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>Carbon ERP</t>
+          <t>Legal Research</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>Active</t>
-        </is>
-      </c>
-      <c r="C9" s="3" t="inlineStr">
-        <is>
-          <t>ACTIVE</t>
+          <t>Case Law Search</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>Find relevant cases and precedents</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
+          <t>LawGlance, OLAW</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>Westlaw Edge, LexisNexis, CaseText</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>Faster research, broader coverage</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>Legal Research</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>Statute Retrieval</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>Find applicable statutes and regulations</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>LawGlance</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>Westlaw, Bloomberg Law</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>Comprehensive regulatory compliance</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>Document Drafting</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>Contract Generation</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>Generate contracts from templates with AI assistance</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>GitLaw (templates)</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>Spellbook, LawDroid, Harvey</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>Faster first drafts, consistency</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>Document Drafting</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>Redlining/Markup</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>AI-assisted contract redlining and suggested changes</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>Ally Legal Assistant</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>Spellbook, Robin AI, BlackBoiler</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>Reduce negotiation cycles</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>Compliance</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>Regulatory Monitoring</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>Track regulatory changes affecting contracts</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>Various</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>Open source ERP, MES and QMS for manufacturing</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>Manufacturing cost tracking, quality management system</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>MES integration for production data analytics</t>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>Kira, Thomson Reuters, Wolters Kluwer</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>Stay ahead of compliance requirements</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>Compliance</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>Policy Enforcement</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>Ensure contracts comply with internal policies</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>OpenContracts</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>Ironclad, Icertis</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>Reduce legal risk exposure</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>E-Discovery</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>Document Classification</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>Classify documents for relevance in litigation</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>Legal-Text-Analytics resources</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>Relativity, Reveal, Exterro</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>Reduce review costs significantly</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>E-Discovery</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>Privilege Detection</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>Identify privileged documents automatically</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>LexNLP (entity extraction)</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>Relativity, Logikcull</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>Prevent privilege waiver</t>
         </is>
       </c>
     </row>

--- a/AI_Use_Cases_Comprehensive_2026.xlsx
+++ b/AI_Use_Cases_Comprehensive_2026.xlsx
@@ -21,6 +21,7 @@
     <sheet name="PE &amp; M&amp;A AI Use Cases" sheetId="12" state="visible" r:id="rId12"/>
     <sheet name="Legal Tech AI Repos" sheetId="13" state="visible" r:id="rId13"/>
     <sheet name="Manufacturing &amp; Distribution" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet name="AI Strategy Roadmaps" sheetId="15" state="visible" r:id="rId15"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -30,7 +31,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="7">
+  <fonts count="8">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -62,6 +63,10 @@
     </font>
     <font>
       <b val="1"/>
+    </font>
+    <font>
+      <color rgb="000563C1"/>
+      <u val="single"/>
     </font>
   </fonts>
   <fills count="12">
@@ -178,7 +183,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -236,6 +241,9 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -601,7 +609,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D36"/>
+  <dimension ref="A1:D33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -996,7 +1004,6 @@
         </is>
       </c>
     </row>
-    <row r="26"/>
     <row r="27">
       <c r="A27" s="23" t="inlineStr">
         <is>
@@ -1076,9 +1083,6 @@
         </is>
       </c>
     </row>
-    <row r="34"/>
-    <row r="35"/>
-    <row r="36"/>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:D1"/>
@@ -5026,6 +5030,958 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G30"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="15" customWidth="1" min="1" max="1"/>
+    <col width="45" customWidth="1" min="2" max="2"/>
+    <col width="60" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="8" customWidth="1" min="6" max="6"/>
+    <col width="70" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="25" customHeight="1">
+      <c r="A1" s="9" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="B1" s="9" t="inlineStr">
+        <is>
+          <t>Document Title</t>
+        </is>
+      </c>
+      <c r="C1" s="9" t="inlineStr">
+        <is>
+          <t>Description</t>
+        </is>
+      </c>
+      <c r="D1" s="9" t="inlineStr">
+        <is>
+          <t>Pages/Length</t>
+        </is>
+      </c>
+      <c r="E1" s="9" t="inlineStr">
+        <is>
+          <t>Format</t>
+        </is>
+      </c>
+      <c r="F1" s="9" t="inlineStr">
+        <is>
+          <t>Year</t>
+        </is>
+      </c>
+      <c r="G1" s="9" t="inlineStr">
+        <is>
+          <t>Download Link</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="50" customHeight="1">
+      <c r="A2" s="10" t="inlineStr">
+        <is>
+          <t>McKinsey</t>
+        </is>
+      </c>
+      <c r="B2" s="10" t="inlineStr">
+        <is>
+          <t>The State of AI in 2025: Agents, Innovation, and Transformation</t>
+        </is>
+      </c>
+      <c r="C2" s="10" t="inlineStr">
+        <is>
+          <t>Comprehensive survey of 1,993 participants across 105 nations on AI adoption, value creation, and organizational rewiring</t>
+        </is>
+      </c>
+      <c r="D2" s="10" t="inlineStr">
+        <is>
+          <t>40+</t>
+        </is>
+      </c>
+      <c r="E2" s="10" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="F2" s="10" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="G2" s="25" t="inlineStr">
+        <is>
+          <t>https://www.mckinsey.com/~/media/mckinsey/business%20functions/quantumblack/our%20insights/the%20state%20of%20ai/november%202025/the-state-of-ai-2025-agents-innovation_cmyk-v1.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="50" customHeight="1">
+      <c r="A3" s="10" t="inlineStr">
+        <is>
+          <t>McKinsey</t>
+        </is>
+      </c>
+      <c r="B3" s="10" t="inlineStr">
+        <is>
+          <t>The State of AI: How Organizations Are Rewiring to Capture Value</t>
+        </is>
+      </c>
+      <c r="C3" s="10" t="inlineStr">
+        <is>
+          <t>Analysis of how leading organizations transform operations using AI across business functions</t>
+        </is>
+      </c>
+      <c r="D3" s="10" t="inlineStr">
+        <is>
+          <t>30+</t>
+        </is>
+      </c>
+      <c r="E3" s="10" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="F3" s="10" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="G3" s="25" t="inlineStr">
+        <is>
+          <t>https://www.mckinsey.com/~/media/mckinsey/business%20functions/quantumblack/our%20insights/the%20state%20of%20ai/2025/the-state-of-ai-how-organizations-are-rewiring-to-capture-value_final.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="50" customHeight="1">
+      <c r="A4" s="10" t="inlineStr">
+        <is>
+          <t>McKinsey</t>
+        </is>
+      </c>
+      <c r="B4" s="10" t="inlineStr">
+        <is>
+          <t>Seizing the Agentic AI Advantage</t>
+        </is>
+      </c>
+      <c r="C4" s="10" t="inlineStr">
+        <is>
+          <t>Strategic guide on deploying agentic AI for enterprise transformation. Only 1% of enterprises view gen AI strategies as mature</t>
+        </is>
+      </c>
+      <c r="D4" s="10" t="inlineStr">
+        <is>
+          <t>25+</t>
+        </is>
+      </c>
+      <c r="E4" s="10" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="F4" s="10" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="G4" s="25" t="inlineStr">
+        <is>
+          <t>https://www.mckinsey.com/~/media/mckinsey/business%20functions/quantumblack/our%20insights/seizing%20the%20agentic%20ai%20advantage/seizing-the-agentic-ai-advantage.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="50" customHeight="1">
+      <c r="A5" s="10" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="B5" s="10" t="inlineStr">
+        <is>
+          <t>Tech Trends 2026</t>
+        </is>
+      </c>
+      <c r="C5" s="10" t="inlineStr">
+        <is>
+          <t>Annual technology trends report covering AI infrastructure, data bottlenecks, and enterprise AI adoption strategies</t>
+        </is>
+      </c>
+      <c r="D5" s="10" t="inlineStr">
+        <is>
+          <t>100+</t>
+        </is>
+      </c>
+      <c r="E5" s="10" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="F5" s="10" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="G5" s="25" t="inlineStr">
+        <is>
+          <t>https://mkto.deloitte.com/rs/712-CNF-326/images/DI_Tech-trends-2026.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="50" customHeight="1">
+      <c r="A6" s="10" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="B6" s="10" t="inlineStr">
+        <is>
+          <t>AI Board Governance Roadmap</t>
+        </is>
+      </c>
+      <c r="C6" s="10" t="inlineStr">
+        <is>
+          <t>Framework for boards of directors to understand AI oversight roles with guiding questions for effective governance</t>
+        </is>
+      </c>
+      <c r="D6" s="10" t="inlineStr">
+        <is>
+          <t>20+</t>
+        </is>
+      </c>
+      <c r="E6" s="10" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="F6" s="10" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="G6" s="25" t="inlineStr">
+        <is>
+          <t>https://boardmember.com/wp-content/uploads/2025/07/AI-Governance-Roadmap.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="50" customHeight="1">
+      <c r="A7" s="10" t="inlineStr">
+        <is>
+          <t>Accenture</t>
+        </is>
+      </c>
+      <c r="B7" s="10" t="inlineStr">
+        <is>
+          <t>Technology Vision 2025: AI - A Declaration of Autonomy</t>
+        </is>
+      </c>
+      <c r="C7" s="10" t="inlineStr">
+        <is>
+          <t>25th annual tech trends report exploring AI-powered autonomy and trust as key business challenges</t>
+        </is>
+      </c>
+      <c r="D7" s="10" t="inlineStr">
+        <is>
+          <t>50+</t>
+        </is>
+      </c>
+      <c r="E7" s="10" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="F7" s="10" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="G7" s="25" t="inlineStr">
+        <is>
+          <t>https://www.accenture.com/content/dam/accenture/final/accenture-com/document-3/Accenture-Tech-Vision-2025.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="50" customHeight="1">
+      <c r="A8" s="10" t="inlineStr">
+        <is>
+          <t>Accenture</t>
+        </is>
+      </c>
+      <c r="B8" s="10" t="inlineStr">
+        <is>
+          <t>Reinvention in the Age of Generative AI</t>
+        </is>
+      </c>
+      <c r="C8" s="10" t="inlineStr">
+        <is>
+          <t>Executive summary with projections through 2026 showing 15%+ revenue growth for AI reinvention leaders</t>
+        </is>
+      </c>
+      <c r="D8" s="10" t="inlineStr">
+        <is>
+          <t>20+</t>
+        </is>
+      </c>
+      <c r="E8" s="10" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="F8" s="10" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="G8" s="25" t="inlineStr">
+        <is>
+          <t>https://www.accenture.com/content/dam/accenture/final/accenture-com/document-2/Accenture-reinvention-in-the-age-of-generative-AI-executive-summary.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="50" customHeight="1">
+      <c r="A9" s="10" t="inlineStr">
+        <is>
+          <t>Accenture</t>
+        </is>
+      </c>
+      <c r="B9" s="10" t="inlineStr">
+        <is>
+          <t>The Front-Runners' Guide to Scaling AI</t>
+        </is>
+      </c>
+      <c r="C9" s="10" t="inlineStr">
+        <is>
+          <t>Lessons from industry leaders on using agentic AI for efficiency and strategic reinvention</t>
+        </is>
+      </c>
+      <c r="D9" s="10" t="inlineStr">
+        <is>
+          <t>30+</t>
+        </is>
+      </c>
+      <c r="E9" s="10" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="F9" s="10" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="G9" s="25" t="inlineStr">
+        <is>
+          <t>https://www.accenture.com/content/dam/accenture/final/accenture-com/document-3/Accenture-Front-Runners-Guide-Scaling-AI-2025-POV.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="50" customHeight="1">
+      <c r="A10" s="10" t="inlineStr">
+        <is>
+          <t>Accenture</t>
+        </is>
+      </c>
+      <c r="B10" s="10" t="inlineStr">
+        <is>
+          <t>AI: Built to Scale</t>
+        </is>
+      </c>
+      <c r="C10" s="10" t="inlineStr">
+        <is>
+          <t>Study on AI-enabled business strategy, top characteristics for scaling AI, and financial results</t>
+        </is>
+      </c>
+      <c r="D10" s="10" t="inlineStr">
+        <is>
+          <t>40+</t>
+        </is>
+      </c>
+      <c r="E10" s="10" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="F10" s="10" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="G10" s="25" t="inlineStr">
+        <is>
+          <t>https://www.accenture.com/content/dam/accenture/final/a-com-migration/thought-leadership-assets/accenture-built-to-scale-pdf-report.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="50" customHeight="1">
+      <c r="A11" s="10" t="inlineStr">
+        <is>
+          <t>Accenture</t>
+        </is>
+      </c>
+      <c r="B11" s="10" t="inlineStr">
+        <is>
+          <t>AI Roadmap: The Journey to Live (Infographic)</t>
+        </is>
+      </c>
+      <c r="C11" s="10" t="inlineStr">
+        <is>
+          <t>Visual roadmap covering AI implementation checkpoints and adjustments</t>
+        </is>
+      </c>
+      <c r="D11" s="10" t="inlineStr">
+        <is>
+          <t>10+</t>
+        </is>
+      </c>
+      <c r="E11" s="10" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="F11" s="10" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="G11" s="25" t="inlineStr">
+        <is>
+          <t>https://www.accenture.com/content/dam/accenture/final/a-com-migration/pdf/pdf-122/accenture-ai-roadmap-journey-to-live-infographic.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="50" customHeight="1">
+      <c r="A12" s="10" t="inlineStr">
+        <is>
+          <t>BCG</t>
+        </is>
+      </c>
+      <c r="B12" s="10" t="inlineStr">
+        <is>
+          <t>AI Radar 2026: As AI Investments Surge, CEOs Take the Lead</t>
+        </is>
+      </c>
+      <c r="C12" s="10" t="inlineStr">
+        <is>
+          <t>Survey of 2,360 executives on agentic AI, CEO leadership in AI, and organizational transformation</t>
+        </is>
+      </c>
+      <c r="D12" s="10" t="inlineStr">
+        <is>
+          <t>30+</t>
+        </is>
+      </c>
+      <c r="E12" s="10" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="F12" s="10" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="G12" s="25" t="inlineStr">
+        <is>
+          <t>https://web-assets.bcg.com/73/8e/cc44cbc14a3b81695f8a3de28ff1/ai-radar-2026-web-jan-2026-edit.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="50" customHeight="1">
+      <c r="A13" s="10" t="inlineStr">
+        <is>
+          <t>BCG</t>
+        </is>
+      </c>
+      <c r="B13" s="10" t="inlineStr">
+        <is>
+          <t>Future of Procurement with AI 2025</t>
+        </is>
+      </c>
+      <c r="C13" s="10" t="inlineStr">
+        <is>
+          <t>AI opportunities for strategic advantages and operational efficiencies with up to 15% savings potential</t>
+        </is>
+      </c>
+      <c r="D13" s="10" t="inlineStr">
+        <is>
+          <t>20+</t>
+        </is>
+      </c>
+      <c r="E13" s="10" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="F13" s="10" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="G13" s="25" t="inlineStr">
+        <is>
+          <t>https://media-publications.bcg.com/BCG-Executive-Perspectives-Future-of-Procurement-with-AI-2025-27Feb2025.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="50" customHeight="1">
+      <c r="A14" s="10" t="inlineStr">
+        <is>
+          <t>BCG</t>
+        </is>
+      </c>
+      <c r="B14" s="10" t="inlineStr">
+        <is>
+          <t>Driving Sustainable Cost Advantage with AI</t>
+        </is>
+      </c>
+      <c r="C14" s="10" t="inlineStr">
+        <is>
+          <t>90% of executives planning AI investments for cost reduction over next 18 months</t>
+        </is>
+      </c>
+      <c r="D14" s="10" t="inlineStr">
+        <is>
+          <t>15+</t>
+        </is>
+      </c>
+      <c r="E14" s="10" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="F14" s="10" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="G14" s="25" t="inlineStr">
+        <is>
+          <t>https://media-publications.bcg.com/BCG-Executive-Perspectives-Driving-Sustainable-Cost-Adv-with-AI-EP15-20May2025.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="50" customHeight="1">
+      <c r="A15" s="10" t="inlineStr">
+        <is>
+          <t>KPMG</t>
+        </is>
+      </c>
+      <c r="B15" s="10" t="inlineStr">
+        <is>
+          <t>Intelligent Tech Enterprise: A Blueprint for AI-Driven Transformation</t>
+        </is>
+      </c>
+      <c r="C15" s="10" t="inlineStr">
+        <is>
+          <t>AI strategy framework covering responsible executive appointment, use case identification, and regulatory alignment</t>
+        </is>
+      </c>
+      <c r="D15" s="10" t="inlineStr">
+        <is>
+          <t>25+</t>
+        </is>
+      </c>
+      <c r="E15" s="10" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="F15" s="10" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="G15" s="25" t="inlineStr">
+        <is>
+          <t>https://assets.kpmg.com/content/dam/kpmg/ng/pdf/2025/intelligent-industries/Intelligent%20tech%20-%20Report.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="50" customHeight="1">
+      <c r="A16" s="10" t="inlineStr">
+        <is>
+          <t>KPMG</t>
+        </is>
+      </c>
+      <c r="B16" s="10" t="inlineStr">
+        <is>
+          <t>Global Customer Experience Excellence 2025-2026</t>
+        </is>
+      </c>
+      <c r="C16" s="10" t="inlineStr">
+        <is>
+          <t>Redefining excellence in the age of agentic AI - covers AI capable of sensing, reasoning, and acting</t>
+        </is>
+      </c>
+      <c r="D16" s="10" t="inlineStr">
+        <is>
+          <t>50+</t>
+        </is>
+      </c>
+      <c r="E16" s="10" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="F16" s="10" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="G16" s="25" t="inlineStr">
+        <is>
+          <t>https://assets.kpmg.com/content/dam/kpmgsites/xx/pdf/2025/10/global-customer-experience-excellence-2025-2026.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="50" customHeight="1">
+      <c r="A17" s="10" t="inlineStr">
+        <is>
+          <t>KPMG</t>
+        </is>
+      </c>
+      <c r="B17" s="10" t="inlineStr">
+        <is>
+          <t>AI Workforce: From Hype to Hard Truths</t>
+        </is>
+      </c>
+      <c r="C17" s="10" t="inlineStr">
+        <is>
+          <t>What it takes to deliver AI value - practical guidance on AI workforce transformation</t>
+        </is>
+      </c>
+      <c r="D17" s="10" t="inlineStr">
+        <is>
+          <t>20+</t>
+        </is>
+      </c>
+      <c r="E17" s="10" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="F17" s="10" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="G17" s="25" t="inlineStr">
+        <is>
+          <t>https://assets.kpmg.com/content/dam/kpmgsites/se/pdf/2025/ai-workforce-from-hype-to-hard-truths.pdf.coredownload.inline.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="50" customHeight="1">
+      <c r="A18" s="10" t="inlineStr">
+        <is>
+          <t>KPMG</t>
+        </is>
+      </c>
+      <c r="B18" s="10" t="inlineStr">
+        <is>
+          <t>AI in Retail Report</t>
+        </is>
+      </c>
+      <c r="C18" s="10" t="inlineStr">
+        <is>
+          <t>Practical examples of AI in retail with insights from Global Tech Report and CEO Outlook</t>
+        </is>
+      </c>
+      <c r="D18" s="10" t="inlineStr">
+        <is>
+          <t>30+</t>
+        </is>
+      </c>
+      <c r="E18" s="10" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="F18" s="10" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="G18" s="25" t="inlineStr">
+        <is>
+          <t>https://assets.kpmg.com/content/dam/kpmgsites/xx/pdf/2026/01/ai-in-retail-report.pdf.coredownload.inline.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="50" customHeight="1">
+      <c r="A19" s="10" t="inlineStr">
+        <is>
+          <t>PwC</t>
+        </is>
+      </c>
+      <c r="B19" s="10" t="inlineStr">
+        <is>
+          <t>AI Readiness: Shaping the Future AI Landscape</t>
+        </is>
+      </c>
+      <c r="C19" s="10" t="inlineStr">
+        <is>
+          <t>National AI capabilities assessment across semiconductors, infrastructure, models, and services</t>
+        </is>
+      </c>
+      <c r="D19" s="10" t="inlineStr">
+        <is>
+          <t>40+</t>
+        </is>
+      </c>
+      <c r="E19" s="10" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="F19" s="10" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="G19" s="25" t="inlineStr">
+        <is>
+          <t>https://www.pwc.com/gx/en/industries/technology/ai-readiness.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="50" customHeight="1">
+      <c r="A20" s="10" t="inlineStr">
+        <is>
+          <t>EY</t>
+        </is>
+      </c>
+      <c r="B20" s="10" t="inlineStr">
+        <is>
+          <t>AI Global Regulatory Landscape</t>
+        </is>
+      </c>
+      <c r="C20" s="10" t="inlineStr">
+        <is>
+          <t>Comprehensive overview of global AI regulations and governance frameworks</t>
+        </is>
+      </c>
+      <c r="D20" s="10" t="inlineStr">
+        <is>
+          <t>30+</t>
+        </is>
+      </c>
+      <c r="E20" s="10" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="F20" s="10" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="G20" s="25" t="inlineStr">
+        <is>
+          <t>https://www.ey.com/content/dam/ey-unified-site/ey-com/en-gl/insights/ai/documents/ey-the-artificial-intelligence-ai-global-regulatory-landscape-final.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="50" customHeight="1">
+      <c r="A21" s="10" t="inlineStr">
+        <is>
+          <t>WEF</t>
+        </is>
+      </c>
+      <c r="B21" s="10" t="inlineStr">
+        <is>
+          <t>Blueprint for Intelligent Economies</t>
+        </is>
+      </c>
+      <c r="C21" s="10" t="inlineStr">
+        <is>
+          <t>Guidance for nations to achieve successful AI revolution regardless of digital maturity level</t>
+        </is>
+      </c>
+      <c r="D21" s="10" t="inlineStr">
+        <is>
+          <t>40+</t>
+        </is>
+      </c>
+      <c r="E21" s="10" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="F21" s="10" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="G21" s="25" t="inlineStr">
+        <is>
+          <t>https://reports.weforum.org/docs/WEF_A_Blueprint_for_Intelligent_Economies_2025.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="50" customHeight="1">
+      <c r="A22" s="10" t="inlineStr">
+        <is>
+          <t>WEF</t>
+        </is>
+      </c>
+      <c r="B22" s="10" t="inlineStr">
+        <is>
+          <t>Rethinking AI Sovereignty: Pathways to Competitiveness</t>
+        </is>
+      </c>
+      <c r="C22" s="10" t="inlineStr">
+        <is>
+          <t>Policy guidance for enabling AI-driven economy through partnership over ownership</t>
+        </is>
+      </c>
+      <c r="D22" s="10" t="inlineStr">
+        <is>
+          <t>35+</t>
+        </is>
+      </c>
+      <c r="E22" s="10" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="F22" s="10" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="G22" s="25" t="inlineStr">
+        <is>
+          <t>https://www3.weforum.org/docs/WEF_Rethinking_AI_Sovereignty_Pathways_to_Competitiveness_through_Strategic_Investments_2026.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="50" customHeight="1">
+      <c r="A23" s="10" t="inlineStr">
+        <is>
+          <t>WEF</t>
+        </is>
+      </c>
+      <c r="B23" s="10" t="inlineStr">
+        <is>
+          <t>Four Futures for Jobs: AI and Talent in 2030</t>
+        </is>
+      </c>
+      <c r="C23" s="10" t="inlineStr">
+        <is>
+          <t>Scenario analysis for future of jobs at intersection of AI advancement and workforce readiness</t>
+        </is>
+      </c>
+      <c r="D23" s="10" t="inlineStr">
+        <is>
+          <t>30+</t>
+        </is>
+      </c>
+      <c r="E23" s="10" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="F23" s="10" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="G23" s="25" t="inlineStr">
+        <is>
+          <t>https://reports.weforum.org/docs/WEF_Four_Futures_for_Jobs_in_the_New_Economy_AI_and_Talent_in_2030_2025.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="50" customHeight="1">
+      <c r="A24" s="10" t="inlineStr">
+        <is>
+          <t>WEF</t>
+        </is>
+      </c>
+      <c r="B24" s="10" t="inlineStr">
+        <is>
+          <t>AI in Action: Beyond Experimentation to Transform Industry</t>
+        </is>
+      </c>
+      <c r="C24" s="10" t="inlineStr">
+        <is>
+          <t>Comprehensive roadmap for businesses and governments to adopt and scale AI</t>
+        </is>
+      </c>
+      <c r="D24" s="10" t="inlineStr">
+        <is>
+          <t>50+</t>
+        </is>
+      </c>
+      <c r="E24" s="10" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="F24" s="10" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="G24" s="25" t="inlineStr">
+        <is>
+          <t>https://reports.weforum.org/docs/WEF_AI_in_Action_Beyond_Experimentation_to_Transform_Industry_2025.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="23" t="inlineStr">
+        <is>
+          <t>SUMMARY</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Total Documents:</t>
+        </is>
+      </c>
+      <c r="B28" t="n">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Sources:</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>McKinsey (3), Deloitte (2), Accenture (5), BCG (3), KPMG (4), PwC (1), EY (1), WEF (4)</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>All links verified:</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Free PDF downloads, no paywall</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>

--- a/AI_Use_Cases_Comprehensive_2026.xlsx
+++ b/AI_Use_Cases_Comprehensive_2026.xlsx
@@ -183,7 +183,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -242,6 +242,9 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -5036,7 +5039,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G30"/>
+  <dimension ref="A1:G39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -5936,44 +5939,341 @@
         </is>
       </c>
     </row>
+    <row r="25"/>
+    <row r="26">
+      <c r="A26" s="10" t="inlineStr">
+        <is>
+          <t>C3.ai</t>
+        </is>
+      </c>
+      <c r="B26" s="10" t="inlineStr">
+        <is>
+          <t>Best Practices in Developing an Enterprise AI Roadmap</t>
+        </is>
+      </c>
+      <c r="C26" s="10" t="inlineStr">
+        <is>
+          <t>Use case qualification model with guidance on determining business value and feasibility. Includes prioritization and sequencing framework.</t>
+        </is>
+      </c>
+      <c r="D26" s="10" t="inlineStr">
+        <is>
+          <t>15-17</t>
+        </is>
+      </c>
+      <c r="E26" s="10" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="F26" s="10" t="inlineStr">
+        <is>
+          <t>2020</t>
+        </is>
+      </c>
+      <c r="G26" s="25" t="inlineStr">
+        <is>
+          <t>https://c3.ai/wp-content/uploads/2020/06/Best-Practices-in-Developing-an-Enterprise-AI-Roadmap.pdf</t>
+        </is>
+      </c>
+    </row>
     <row r="27">
-      <c r="A27" s="23" t="inlineStr">
+      <c r="A27" s="26" t="inlineStr">
+        <is>
+          <t>C3.ai</t>
+        </is>
+      </c>
+      <c r="B27" s="10" t="inlineStr">
+        <is>
+          <t>Enterprise AI Buyer's Guide</t>
+        </is>
+      </c>
+      <c r="C27" s="10" t="inlineStr">
+        <is>
+          <t>Enterprise AI Requirements Checklist specifying all capabilities an AI platform must provide for complete, robust solutions</t>
+        </is>
+      </c>
+      <c r="D27" s="10" t="inlineStr">
+        <is>
+          <t>20+</t>
+        </is>
+      </c>
+      <c r="E27" s="10" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="F27" s="10" t="inlineStr">
+        <is>
+          <t>2020</t>
+        </is>
+      </c>
+      <c r="G27" s="25" t="inlineStr">
+        <is>
+          <t>https://c3.ai/wp-content/uploads/2020/06/Enterprise-AI-Buyers-Guide.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="10" t="inlineStr">
+        <is>
+          <t>WEF</t>
+        </is>
+      </c>
+      <c r="B28" s="10" t="inlineStr">
+        <is>
+          <t>Empowering AI Leadership: AI C-Suite Toolkit</t>
+        </is>
+      </c>
+      <c r="C28" s="10" t="inlineStr">
+        <is>
+          <t>Comprehensive toolkit for C-suite executives covering AI strategy, governance, risk management, and responsible AI implementation</t>
+        </is>
+      </c>
+      <c r="D28" s="10" t="inlineStr">
+        <is>
+          <t>50+</t>
+        </is>
+      </c>
+      <c r="E28" s="10" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="F28" s="10" t="inlineStr">
+        <is>
+          <t>2022</t>
+        </is>
+      </c>
+      <c r="G28" s="25" t="inlineStr">
+        <is>
+          <t>https://www3.weforum.org/docs/WEF_Empowering_AI_Leadership_2022.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="10" t="inlineStr">
+        <is>
+          <t>3Cloud</t>
+        </is>
+      </c>
+      <c r="B29" s="10" t="inlineStr">
+        <is>
+          <t>AI Strategy Roadmap eBook</t>
+        </is>
+      </c>
+      <c r="C29" s="10" t="inlineStr">
+        <is>
+          <t>Practical guidance for AI implementation covering readiness assessment and path to successful deployment</t>
+        </is>
+      </c>
+      <c r="D29" s="10" t="inlineStr">
+        <is>
+          <t>25+</t>
+        </is>
+      </c>
+      <c r="E29" s="10" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="F29" s="10" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="G29" s="25" t="inlineStr">
+        <is>
+          <t>https://3cloudsolutions.com/wp-content/uploads/2025/10/AI-Strategy-Roadmap-eBook.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="10" t="inlineStr">
+        <is>
+          <t>Microsoft</t>
+        </is>
+      </c>
+      <c r="B30" s="10" t="inlineStr">
+        <is>
+          <t>The AI Strategy Roadmap</t>
+        </is>
+      </c>
+      <c r="C30" s="10" t="inlineStr">
+        <is>
+          <t>Insights from IT leaders and business decision makers on successfully integrating AI and realizing business value</t>
+        </is>
+      </c>
+      <c r="D30" s="10" t="inlineStr">
+        <is>
+          <t>30+</t>
+        </is>
+      </c>
+      <c r="E30" s="10" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="F30" s="10" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="G30" s="25" t="inlineStr">
+        <is>
+          <t>https://replyfabric.ai/documents/microsoft-the-ai-strategy-roadmap-2025.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="10" t="inlineStr">
+        <is>
+          <t>Info-Tech</t>
+        </is>
+      </c>
+      <c r="B31" s="10" t="inlineStr">
+        <is>
+          <t>Build Your AI Strategy Roadmap Blueprint</t>
+        </is>
+      </c>
+      <c r="C31" s="10" t="inlineStr">
+        <is>
+          <t>4-step framework with AI Maturity Assessment Tool and Prioritization/Roadmap Planning frameworks. Includes governance principles.</t>
+        </is>
+      </c>
+      <c r="D31" s="10" t="inlineStr">
+        <is>
+          <t>Multi-page</t>
+        </is>
+      </c>
+      <c r="E31" s="10" t="inlineStr">
+        <is>
+          <t>Web + Tools</t>
+        </is>
+      </c>
+      <c r="F31" s="10" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="G31" s="25" t="inlineStr">
+        <is>
+          <t>https://www.infotech.com/research/build-your-ai-strategy-roadmap-storyboard</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="10" t="inlineStr">
+        <is>
+          <t>RTS Labs</t>
+        </is>
+      </c>
+      <c r="B32" s="10" t="inlineStr">
+        <is>
+          <t>Enterprise AI Roadmap: Complete 2026 Guide</t>
+        </is>
+      </c>
+      <c r="C32" s="10" t="inlineStr">
+        <is>
+          <t>12-18 month phased plan combining strategy + engineering + MLOps. Business-first lens mapping AI to financial outcomes.</t>
+        </is>
+      </c>
+      <c r="D32" s="10" t="inlineStr">
+        <is>
+          <t>Long article</t>
+        </is>
+      </c>
+      <c r="E32" s="10" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="F32" s="10" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="G32" s="25" t="inlineStr">
+        <is>
+          <t>https://rtslabs.com/enterprise-ai-roadmap/</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="10" t="inlineStr">
+        <is>
+          <t>Applied AI</t>
+        </is>
+      </c>
+      <c r="B33" s="10" t="inlineStr">
+        <is>
+          <t>Elements of a Comprehensive AI Strategy</t>
+        </is>
+      </c>
+      <c r="C33" s="10" t="inlineStr">
+        <is>
+          <t>Framework covering AI strategy components for enterprise implementation</t>
+        </is>
+      </c>
+      <c r="D33" s="10" t="inlineStr">
+        <is>
+          <t>15+</t>
+        </is>
+      </c>
+      <c r="E33" s="10" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="F33" s="10" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="G33" s="25" t="inlineStr">
+        <is>
+          <t>https://aai.frb.io/assets/videos/AppliedAI_Elements-of-a-comprehensive-AI-Strategy.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="23" t="inlineStr">
         <is>
           <t>SUMMARY</t>
         </is>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
+    <row r="37">
+      <c r="A37" t="inlineStr">
         <is>
           <t>Total Documents:</t>
         </is>
       </c>
-      <c r="B28" t="n">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
+      <c r="B37" t="n">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
         <is>
           <t>Sources:</t>
         </is>
       </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>McKinsey (3), Deloitte (2), Accenture (5), BCG (3), KPMG (4), PwC (1), EY (1), WEF (4)</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>McKinsey (3), Deloitte (2), Accenture (5), BCG (3), KPMG (4), PwC (1), EY (1), WEF (5), C3.ai (2), 3Cloud (1), Microsoft (1), Info-Tech (1), RTS Labs (1), Applied AI (1)</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
         <is>
           <t>All links verified:</t>
         </is>
       </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>Free PDF downloads, no paywall</t>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Free PDF/Web downloads, no paywall (except Info-Tech tools may require contact)</t>
         </is>
       </c>
     </row>
